--- a/Con_Law_Outline_Consolidated.xlsx
+++ b/Con_Law_Outline_Consolidated.xlsx
@@ -31,9 +31,12 @@
     <sheet name="Week 9 - Class" sheetId="23" state="visible" r:id="rId23"/>
     <sheet name="Week 10 - Reading" sheetId="24" state="visible" r:id="rId24"/>
     <sheet name="Week 10 - Class" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="Midterm questions &amp; answers" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="Cases by Doctrine" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="Midterm questions &amp; answers" sheetId="27" state="visible" r:id="rId27"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="25" hidden="1">'Cases by Doctrine'!$A$1:$K$161</definedName>
+  </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -662,7 +665,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="116">
+  <cellXfs count="117">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -997,6 +1000,9 @@
     <xf numFmtId="0" fontId="12" fillId="51" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="46" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -10734,6 +10740,8917 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:K161"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="55" customWidth="1" min="9" max="9"/>
+    <col width="70" customWidth="1" min="10" max="10"/>
+    <col width="45" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="116" t="inlineStr">
+        <is>
+          <t>Doctrine</t>
+        </is>
+      </c>
+      <c r="B1" s="116" t="inlineStr">
+        <is>
+          <t>Also in</t>
+        </is>
+      </c>
+      <c r="C1" s="116" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="D1" s="116" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E1" s="116" t="inlineStr">
+        <is>
+          <t>Case / Document</t>
+        </is>
+      </c>
+      <c r="F1" s="116" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="G1" s="116" t="inlineStr">
+        <is>
+          <t>Key facts</t>
+        </is>
+      </c>
+      <c r="H1" s="116" t="inlineStr">
+        <is>
+          <t>Holding</t>
+        </is>
+      </c>
+      <c r="I1" s="116" t="inlineStr">
+        <is>
+          <t>Rule / what it stands for</t>
+        </is>
+      </c>
+      <c r="J1" s="116" t="inlineStr">
+        <is>
+          <t>Likely multiple-choice points</t>
+        </is>
+      </c>
+      <c r="K1" s="116" t="inlineStr">
+        <is>
+          <t>Short-answer use</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="105" t="inlineStr">
+        <is>
+          <t>Foundations &amp; interpretation</t>
+        </is>
+      </c>
+      <c r="B2" s="99" t="inlineStr">
+        <is>
+          <t>Judicial review &amp; federal jurisdiction</t>
+        </is>
+      </c>
+      <c r="C2" s="99" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E2" s="100" t="inlineStr">
+        <is>
+          <t>Calder v. Bull (1798)</t>
+        </is>
+      </c>
+      <c r="F2" s="99" t="inlineStr">
+        <is>
+          <t>Unenumerated rights; review</t>
+        </is>
+      </c>
+      <c r="G2" s="99" t="inlineStr">
+        <is>
+          <t>Connecticut's legislature set aside a probate decree and granted a new hearing; on rehearing the will was approved.</t>
+        </is>
+      </c>
+      <c r="H2" s="99" t="inlineStr">
+        <is>
+          <t>The holding (Ex Post Facto Clause) is not tested; the seriatim dicta of Chase and Iredell are.</t>
+        </is>
+      </c>
+      <c r="I2" s="99" t="inlineStr">
+        <is>
+          <t>Chase: a legislative act contrary to the "great first principles of the social compact" is not rightful authority even without express limits. Iredell: courts may void only acts violating written constitutional provisions, not acts contrary to natural justice.</t>
+        </is>
+      </c>
+      <c r="J2" s="99" t="inlineStr">
+        <is>
+          <t>• Chase's four examples: punishing an act innocent when done; impairing lawful contracts; making a man judge in his own cause; taking property from A and giving it to B
+• Iredell: natural justice has "no fixed standard"; void only in a "clear and urgent case"
+• Both would void a law plainly within an express prohibition
+• Seriatim opinions, no majority opinion</t>
+        </is>
+      </c>
+      <c r="K2" s="99" t="inlineStr">
+        <is>
+          <t>Frames the unenumerated-rights debate (natural law vs. written text) and the limits of judicial review; Iredell anticipates textualist restraint.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="105" t="inlineStr">
+        <is>
+          <t>Foundations &amp; interpretation</t>
+        </is>
+      </c>
+      <c r="B3" s="101" t="n"/>
+      <c r="C3" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="101" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="E3" s="102" t="inlineStr">
+        <is>
+          <t>Federalist No. 1 (1787)</t>
+        </is>
+      </c>
+      <c r="F3" s="101" t="inlineStr">
+        <is>
+          <t>Ratification: purpose</t>
+        </is>
+      </c>
+      <c r="G3" s="101" t="inlineStr">
+        <is>
+          <t>Hamilton, as Publius, opens the series urging ratification of the Constitution.</t>
+        </is>
+      </c>
+      <c r="H3" s="101" t="inlineStr">
+        <is>
+          <t>Americans must decide whether societies can establish good government "from reflection and choice" or must depend on "accident and force."</t>
+        </is>
+      </c>
+      <c r="I3" s="101" t="inlineStr">
+        <is>
+          <t>Frames ratification as a test of whether government can rest on deliberate choice.</t>
+        </is>
+      </c>
+      <c r="J3" s="101" t="inlineStr">
+        <is>
+          <t>• "Reflection and choice" vs. "accident and force" is the reserved question
+• Hamilton wrote it as "Publius"</t>
+        </is>
+      </c>
+      <c r="K3" s="101" t="inlineStr">
+        <is>
+          <t>Use as the framing for constitutional design as a deliberate choice by the people.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="105" t="inlineStr">
+        <is>
+          <t>Foundations &amp; interpretation</t>
+        </is>
+      </c>
+      <c r="B4" s="101" t="inlineStr">
+        <is>
+          <t>Tenth Amendment &amp; federalism</t>
+        </is>
+      </c>
+      <c r="C4" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="101" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="E4" s="102" t="inlineStr">
+        <is>
+          <t>Federalist No. 15 (1787)</t>
+        </is>
+      </c>
+      <c r="F4" s="101" t="inlineStr">
+        <is>
+          <t>Federalism: Articles' defects</t>
+        </is>
+      </c>
+      <c r="G4" s="101" t="inlineStr">
+        <is>
+          <t>Hamilton's critique of the Articles of Confederation, under which Congress acted through requisitions on the states.</t>
+        </is>
+      </c>
+      <c r="H4" s="101" t="inlineStr">
+        <is>
+          <t>The "great and radical vice" of the Confederation is legislation for states in their collective capacities rather than for individuals.</t>
+        </is>
+      </c>
+      <c r="I4" s="101" t="inlineStr">
+        <is>
+          <t>A law needs a sanction; against states the only sanction is arms, so a government must act directly on individuals to be enforceable through courts.</t>
+        </is>
+      </c>
+      <c r="J4" s="101" t="inlineStr">
+        <is>
+          <t>• Vice = legislating for STATES, not individuals
+• Requisitions were "mere recommendations" states obeyed at their option
+• Two sanctions: coercion of the magistracy (courts) or coercion of arms; against states every breach means war</t>
+        </is>
+      </c>
+      <c r="K4" s="101" t="inlineStr">
+        <is>
+          <t>Supports why the Constitution gives the national government power over individuals; contrast Brutus's consolidation fears.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="105" t="inlineStr">
+        <is>
+          <t>Foundations &amp; interpretation</t>
+        </is>
+      </c>
+      <c r="B5" s="101" t="inlineStr">
+        <is>
+          <t>Tenth Amendment &amp; federalism; Necessary &amp; Proper / implied powers</t>
+        </is>
+      </c>
+      <c r="C5" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="101" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="E5" s="102" t="inlineStr">
+        <is>
+          <t>Brutus No. 1 (1787)</t>
+        </is>
+      </c>
+      <c r="F5" s="101" t="inlineStr">
+        <is>
+          <t>Anti-Federalist: consolidation</t>
+        </is>
+      </c>
+      <c r="G5" s="101" t="inlineStr">
+        <is>
+          <t>Anti-Federalist essay asking whether the 13 states should be reduced to one great republic.</t>
+        </is>
+      </c>
+      <c r="H5" s="101" t="inlineStr">
+        <is>
+          <t>The Constitution approaches so near consolidation that it must "certainly and infallibly terminate in it."</t>
+        </is>
+      </c>
+      <c r="I5" s="101" t="inlineStr">
+        <is>
+          <t>A government of the proposed scope will absorb the states.</t>
+        </is>
+      </c>
+      <c r="J5" s="101" t="inlineStr">
+        <is>
+          <t>• Not a perfect consolidation, but it will end in one
+• Counterpoint to Federalist No. 45</t>
+        </is>
+      </c>
+      <c r="K5" s="101" t="inlineStr">
+        <is>
+          <t>Use as the counterpoint to Madison's few-and-defined federal powers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="105" t="inlineStr">
+        <is>
+          <t>Foundations &amp; interpretation</t>
+        </is>
+      </c>
+      <c r="B6" s="101" t="inlineStr">
+        <is>
+          <t>Tenth Amendment &amp; federalism; Necessary &amp; Proper / implied powers</t>
+        </is>
+      </c>
+      <c r="C6" s="101" t="n">
+        <v>8</v>
+      </c>
+      <c r="D6" s="101" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="E6" s="102" t="inlineStr">
+        <is>
+          <t>Brutus No. 1 (1787)</t>
+        </is>
+      </c>
+      <c r="F6" s="101" t="inlineStr">
+        <is>
+          <t>Anti-Federalist critique</t>
+        </is>
+      </c>
+      <c r="G6" s="101" t="inlineStr">
+        <is>
+          <t>Anti-Federalist essay in the New York Journal asking whether the States should be consolidated into one great republic.</t>
+        </is>
+      </c>
+      <c r="H6" s="101" t="inlineStr">
+        <is>
+          <t>No holding; argues the Constitution approaches so near consolidation that it "must, if executed, certainly and infallibly terminate in it."</t>
+        </is>
+      </c>
+      <c r="I6" s="101" t="inlineStr">
+        <is>
+          <t>The Necessary and Proper and Supremacy Clauses make the government "a complete one, and not a confederation"; the clause "may receive a construction to justify the passing almost any law" and could "entirely abolish the State legislatures."</t>
+        </is>
+      </c>
+      <c r="J6" s="101" t="inlineStr">
+        <is>
+          <t>• Objected to the breadth of federal power, not its weakness
+• Example: Congress could repeal a state revenue law as obstructing a federal tax it deems necessary
+• Predicted that powers reserved to the States would "very soon be annihilated"
+• Willett's Bonner concurrence invokes Brutus's fear of expansion by implication</t>
+        </is>
+      </c>
+      <c r="K6" s="101" t="inlineStr">
+        <is>
+          <t>The Anti-Federalist prediction against which to test McCulloch and the modern commerce cases; cite it for the argument that implied powers lead to consolidation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="105" t="inlineStr">
+        <is>
+          <t>Foundations &amp; interpretation</t>
+        </is>
+      </c>
+      <c r="B7" s="101" t="inlineStr">
+        <is>
+          <t>Tenth Amendment &amp; federalism</t>
+        </is>
+      </c>
+      <c r="C7" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="101" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="E7" s="102" t="inlineStr">
+        <is>
+          <t>Federalist No. 45 (1788)</t>
+        </is>
+      </c>
+      <c r="F7" s="101" t="inlineStr">
+        <is>
+          <t>Federalism: enumerated powers</t>
+        </is>
+      </c>
+      <c r="G7" s="101" t="inlineStr">
+        <is>
+          <t>Madison answers fears that the new government will swallow the states.</t>
+        </is>
+      </c>
+      <c r="H7" s="101" t="inlineStr">
+        <is>
+          <t>Federal powers are "few and defined"; state powers are "numerous and indefinite."</t>
+        </is>
+      </c>
+      <c r="I7" s="101" t="inlineStr">
+        <is>
+          <t>Federal power operates mainly on external objects (war, peace, foreign commerce); states govern lives, liberties and property and internal order.</t>
+        </is>
+      </c>
+      <c r="J7" s="101" t="inlineStr">
+        <is>
+          <t>• Change is less the addition of NEW powers than invigoration of ORIGINAL powers
+• Commerce regulation is the one new power, which few oppose
+• Federal government most important in war; states in peace</t>
+        </is>
+      </c>
+      <c r="K7" s="101" t="inlineStr">
+        <is>
+          <t>Cite for the limited-enumerated-powers view of federalism; Brutus No. 1 is the counterpoint predicting consolidation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="105" t="inlineStr">
+        <is>
+          <t>Foundations &amp; interpretation</t>
+        </is>
+      </c>
+      <c r="B8" s="101" t="n"/>
+      <c r="C8" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="101" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="E8" s="102" t="inlineStr">
+        <is>
+          <t>Federalist No. 84 (1788)</t>
+        </is>
+      </c>
+      <c r="F8" s="101" t="inlineStr">
+        <is>
+          <t>Bill of rights debate</t>
+        </is>
+      </c>
+      <c r="G8" s="101" t="inlineStr">
+        <is>
+          <t>Hamilton responds to Anti-Federalist demands for a bill of rights.</t>
+        </is>
+      </c>
+      <c r="H8" s="101" t="inlineStr">
+        <is>
+          <t>A bill of rights is unnecessary and dangerous.</t>
+        </is>
+      </c>
+      <c r="I8" s="101" t="inlineStr">
+        <is>
+          <t>Listing exceptions to powers never granted gives a "colourable pretext" to claim more power than was granted.</t>
+        </is>
+      </c>
+      <c r="J8" s="101" t="inlineStr">
+        <is>
+          <t>• "Why declare that things shall not be done which there is no power to do?"
+• Example: liberty of the press, whose security rests on public opinion</t>
+        </is>
+      </c>
+      <c r="K8" s="101" t="inlineStr">
+        <is>
+          <t>Use for the enumerated-powers logic that ungranted powers need no prohibition.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="105" t="inlineStr">
+        <is>
+          <t>Foundations &amp; interpretation</t>
+        </is>
+      </c>
+      <c r="B9" s="103" t="n"/>
+      <c r="C9" s="103" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="103" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+      <c r="E9" s="104" t="inlineStr">
+        <is>
+          <t>Declaration of Independence (1776)</t>
+        </is>
+      </c>
+      <c r="F9" s="103" t="inlineStr">
+        <is>
+          <t>Founding principles</t>
+        </is>
+      </c>
+      <c r="G9" s="103" t="inlineStr">
+        <is>
+          <t>Statement of grievances and principles justifying independence.</t>
+        </is>
+      </c>
+      <c r="H9" s="103" t="inlineStr">
+        <is>
+          <t>Governments derive "their just powers from the consent of the governed."</t>
+        </is>
+      </c>
+      <c r="I9" s="103" t="inlineStr">
+        <is>
+          <t>Popular sovereignty and the right to "alter or to abolish" a government destructive of its ends.</t>
+        </is>
+      </c>
+      <c r="J9" s="103" t="inlineStr">
+        <is>
+          <t>• Consent of the governed is the key phrase
+• Unalienable rights: "Life, Liberty and the pursuit of Happiness"</t>
+        </is>
+      </c>
+      <c r="K9" s="103" t="inlineStr">
+        <is>
+          <t>Use for popular-sovereignty arguments (e.g., Wilson and Jay in Chisholm; Marshall in McCulloch that the government "proceeds directly from the people").</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="105" t="inlineStr">
+        <is>
+          <t>Foundations &amp; interpretation</t>
+        </is>
+      </c>
+      <c r="B10" s="103" t="inlineStr">
+        <is>
+          <t>Tenth Amendment &amp; federalism</t>
+        </is>
+      </c>
+      <c r="C10" s="103" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="103" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+      <c r="E10" s="104" t="inlineStr">
+        <is>
+          <t>Articles of Confederation (1781)</t>
+        </is>
+      </c>
+      <c r="F10" s="103" t="inlineStr">
+        <is>
+          <t>Founding structure</t>
+        </is>
+      </c>
+      <c r="G10" s="103" t="inlineStr">
+        <is>
+          <t>The first national charter: a league of sovereign states with a weak Congress.</t>
+        </is>
+      </c>
+      <c r="H10" s="103" t="inlineStr">
+        <is>
+          <t>Each state keeps its sovereignty and every power not "expressly delegated" (Art. II).</t>
+        </is>
+      </c>
+      <c r="I10" s="103" t="inlineStr">
+        <is>
+          <t>A "firm league of friendship"; one vote per state; Congress could not tax (states raised money); major acts needed nine states; amendment required unanimity.</t>
+        </is>
+      </c>
+      <c r="J10" s="103" t="inlineStr">
+        <is>
+          <t>• "Expressly delegated" in Art. II is the word the Tenth Amendment OMITS (McCulloch's point)
+• No federal taxing power and legislation for states, not individuals, is Federalist 15's "radical vice"
+• Unanimity for amendments</t>
+        </is>
+      </c>
+      <c r="K10" s="103" t="inlineStr">
+        <is>
+          <t>Background for why the Constitution was needed (Federalist 15) and for McCulloch's reading of the Tenth Amendment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="105" t="inlineStr">
+        <is>
+          <t>Foundations &amp; interpretation</t>
+        </is>
+      </c>
+      <c r="B11" s="103" t="n"/>
+      <c r="C11" s="103" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="103" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+      <c r="E11" s="104" t="inlineStr">
+        <is>
+          <t>Course reader timeline</t>
+        </is>
+      </c>
+      <c r="F11" s="103" t="inlineStr">
+        <is>
+          <t>Background dates</t>
+        </is>
+      </c>
+      <c r="G11" s="103" t="inlineStr">
+        <is>
+          <t>A one-page chronology from the Articles (1781) through recent cases.</t>
+        </is>
+      </c>
+      <c r="H11" s="103" t="inlineStr">
+        <is>
+          <t>Places the readings in order.</t>
+        </is>
+      </c>
+      <c r="I11" s="103" t="inlineStr">
+        <is>
+          <t>Use for sequence, not memorization: Articles (1781) → Convention (1787) → government begins and Judiciary Act (1789) → Bank and Bill of Rights (1791) → Marbury (1803) → McCulloch (1819) → Gibbons (1824) → Reconstruction Amendments (1865-1870) → 1937 switch → Wickard (1942) → Lopez (1995).</t>
+        </is>
+      </c>
+      <c r="J11" s="103" t="inlineStr">
+        <is>
+          <t>• Know the order of events where it matters to an argument (e.g., Chisholm 1793 before the Eleventh Amendment; McCulloch before Gibbons)
+• Dates alone are rarely tested</t>
+        </is>
+      </c>
+      <c r="K11" s="103" t="inlineStr">
+        <is>
+          <t>Helps frame 'then vs. now' answers (Federalist 45 then; Wickard/Raich now).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="105" t="inlineStr">
+        <is>
+          <t>Foundations &amp; interpretation</t>
+        </is>
+      </c>
+      <c r="B12" s="103" t="n"/>
+      <c r="C12" s="103" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="103" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+      <c r="E12" s="104" t="inlineStr">
+        <is>
+          <t>CRS, Modes of Constitutional Interpretation (R45129)</t>
+        </is>
+      </c>
+      <c r="F12" s="103" t="inlineStr">
+        <is>
+          <t>Interpretation methods</t>
+        </is>
+      </c>
+      <c r="G12" s="103" t="inlineStr">
+        <is>
+          <t>A CRS report describing how courts interpret the Constitution.</t>
+        </is>
+      </c>
+      <c r="H12" s="103" t="inlineStr">
+        <is>
+          <t>Lists eight modes of interpretation.</t>
+        </is>
+      </c>
+      <c r="I12" s="103" t="inlineStr">
+        <is>
+          <t>Textualism; original meaning; judicial precedent (the most commonly cited); pragmatism; moral reasoning; national identity ("ethos"); structuralism; historical practices.</t>
+        </is>
+      </c>
+      <c r="J12" s="103" t="inlineStr">
+        <is>
+          <t>• Textualism looks to the text's plain meaning; original meaning looks to how the public understood it at the Founding
+• Precedent is "the most commonly cited source"
+• Structuralism draws inferences from separation of powers and federalism (e.g., McCulloch, Alden)
+• Historical practices matter most when the text is unclear</t>
+        </is>
+      </c>
+      <c r="K12" s="103" t="inlineStr">
+        <is>
+          <t>Name the mode an opinion uses (e.g., Thomas in Lopez: original meaning; Kennedy in Lopez: precedent; Alden and Torres: structure and history).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="105" t="inlineStr">
+        <is>
+          <t>Separation of powers</t>
+        </is>
+      </c>
+      <c r="B13" s="101" t="n"/>
+      <c r="C13" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="101" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="E13" s="102" t="inlineStr">
+        <is>
+          <t>Federalist No. 47 (1788)</t>
+        </is>
+      </c>
+      <c r="F13" s="101" t="inlineStr">
+        <is>
+          <t>Separation of powers</t>
+        </is>
+      </c>
+      <c r="G13" s="101" t="inlineStr">
+        <is>
+          <t>Madison defends the Constitution's separation of powers.</t>
+        </is>
+      </c>
+      <c r="H13" s="101" t="inlineStr">
+        <is>
+          <t>Accumulating legislative, executive and judicial power in the same hands is "the very definition of tyranny."</t>
+        </is>
+      </c>
+      <c r="I13" s="101" t="inlineStr">
+        <is>
+          <t>Tyranny exists whether the concentrated power is held by one, a few or many, hereditary, self-appointed or elective.</t>
+        </is>
+      </c>
+      <c r="J13" s="101" t="inlineStr">
+        <is>
+          <t>• "Very definition of tyranny" = all three powers in the same hands
+• Applied in hypos: one body that writes rules, prosecutes and adjudicates without court review is the accumulation Madison condemned</t>
+        </is>
+      </c>
+      <c r="K13" s="101" t="inlineStr">
+        <is>
+          <t>Use with No. 51 to attack any arrangement that merges rulemaking, enforcement and adjudication.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="105" t="inlineStr">
+        <is>
+          <t>Separation of powers</t>
+        </is>
+      </c>
+      <c r="B14" s="101" t="n"/>
+      <c r="C14" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="101" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="E14" s="102" t="inlineStr">
+        <is>
+          <t>Federalist No. 51 (1788)</t>
+        </is>
+      </c>
+      <c r="F14" s="101" t="inlineStr">
+        <is>
+          <t>Separation of powers: checks</t>
+        </is>
+      </c>
+      <c r="G14" s="101" t="inlineStr">
+        <is>
+          <t>Madison explains how the Constitution's structure keeps each branch in its place.</t>
+        </is>
+      </c>
+      <c r="H14" s="101" t="inlineStr">
+        <is>
+          <t>Each department gets the constitutional means and personal motives to resist encroachment: "Ambition must be made to counteract ambition."</t>
+        </is>
+      </c>
+      <c r="I14" s="101" t="inlineStr">
+        <is>
+          <t>Interior structure, not paper barriers, maintains separation; a "double security" divides power between federal and state governments and then among departments.</t>
+        </is>
+      </c>
+      <c r="J14" s="101" t="inlineStr">
+        <is>
+          <t>• "If men were angels, no government would be necessary"
+• Double security = federal/state split, then separate departments
+• Legislature predominates; remedy is to divide it into branches
+• Minority protected by an extended republic of many interests and sects; "Justice is the end of government"</t>
+        </is>
+      </c>
+      <c r="K14" s="101" t="inlineStr">
+        <is>
+          <t>Core text for structural arguments in separation-of-powers and federalism essays; pair with No. 47.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="105" t="inlineStr">
+        <is>
+          <t>Separation of powers</t>
+        </is>
+      </c>
+      <c r="B15" s="101" t="n"/>
+      <c r="C15" s="101" t="n">
+        <v>5</v>
+      </c>
+      <c r="D15" s="101" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="E15" s="102" t="inlineStr">
+        <is>
+          <t>The Federalist Nos. 51 and 71 (1788)</t>
+        </is>
+      </c>
+      <c r="F15" s="101" t="inlineStr">
+        <is>
+          <t>Separation of powers</t>
+        </is>
+      </c>
+      <c r="G15" s="101" t="inlineStr">
+        <is>
+          <t>Assigned excerpts: Madison on legislative predominance and Hamilton on the executive's duty to the public.</t>
+        </is>
+      </c>
+      <c r="H15" s="101" t="inlineStr">
+        <is>
+          <t>Not a decision.</t>
+        </is>
+      </c>
+      <c r="I15" s="101" t="inlineStr">
+        <is>
+          <t>Fed. 51: 'In republican government the legislative authority, necessarily, predominates.' Fed. 71: the 'deliberate sense of the community' should govern, not 'every sudden breese of passion.'</t>
+        </is>
+      </c>
+      <c r="J15" s="101" t="inlineStr">
+        <is>
+          <t>• Fed. 71: officials should 'withstand the temporary delusion' to allow 'more cool and sedate reflection'
+• The people 'commonly intend the PUBLIC GOOD' but sometimes err about the means</t>
+        </is>
+      </c>
+      <c r="K15" s="101" t="inlineStr">
+        <is>
+          <t>Use for the theme that the Constitution filters popular passion, for example when defending deliberate political checks over courts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="105" t="inlineStr">
+        <is>
+          <t>Separation of powers</t>
+        </is>
+      </c>
+      <c r="B16" s="101" t="inlineStr">
+        <is>
+          <t>Treaties &amp; executive agreements</t>
+        </is>
+      </c>
+      <c r="C16" s="101" t="n">
+        <v>9</v>
+      </c>
+      <c r="D16" s="101" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="E16" s="102" t="inlineStr">
+        <is>
+          <t>Circular 175 Procedure (11 FAM 720)</t>
+        </is>
+      </c>
+      <c r="F16" s="101" t="inlineStr">
+        <is>
+          <t>Treaties vs. executive agreements: State Dept. criteria</t>
+        </is>
+      </c>
+      <c r="G16" s="101" t="inlineStr">
+        <is>
+          <t>State Department rules (Foreign Affairs Manual) for negotiating and concluding international agreements.</t>
+        </is>
+      </c>
+      <c r="H16" s="101" t="inlineStr">
+        <is>
+          <t>N/A.</t>
+        </is>
+      </c>
+      <c r="I16" s="101" t="inlineStr">
+        <is>
+          <t>Two constitutional routes: TREATY (2/3 Senate advice and consent; any subject genuinely of concern in foreign relations, if consistent with the Constitution) or AGREEMENT OTHER THAN A TREATY, based on (1) a treaty, (2) legislation, or (3) the President's own constitutional authority (foreign affairs representative, receiving ambassadors/recognition, Commander in Chief, Take Care). Factors for choosing: commitments/risks to the nation as a whole; effect on state law; need for implementing legislation; past practice; Congress's preference; formality; duration/urgency; international practice.</t>
+        </is>
+      </c>
+      <c r="J16" s="101" t="inlineStr">
+        <is>
+          <t>• 'Sole executive agreement' = only on the President's own authority, and can't conflict with a statute
+• Case-Zablocki Act: non-treaty agreements must be sent to Congress within 60 days
+• Goal: avoid 'invasion or compromise' of the powers of the President, Senate and Congress</t>
+        </is>
+      </c>
+      <c r="K16" s="101" t="inlineStr">
+        <is>
+          <t>Use the eight factors to argue whether a given agreement should have gone to the Senate as a treaty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="105" t="inlineStr">
+        <is>
+          <t>Separation of powers</t>
+        </is>
+      </c>
+      <c r="B17" s="103" t="n"/>
+      <c r="C17" s="103" t="n">
+        <v>5</v>
+      </c>
+      <c r="D17" s="103" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+      <c r="E17" s="104" t="inlineStr">
+        <is>
+          <t>Types of Legislation (Senate website)</t>
+        </is>
+      </c>
+      <c r="F17" s="103" t="inlineStr">
+        <is>
+          <t>Legislative process</t>
+        </is>
+      </c>
+      <c r="G17" s="103" t="inlineStr">
+        <is>
+          <t>The Senate's description of bills and resolutions.</t>
+        </is>
+      </c>
+      <c r="H17" s="103" t="inlineStr">
+        <is>
+          <t>Only bills and joint resolutions (other than proposed amendments) need the President's signature and have the force of law.</t>
+        </is>
+      </c>
+      <c r="I17" s="103" t="inlineStr">
+        <is>
+          <t>Bills (H.R./S.) and joint resolutions (H.J.Res./S.J.Res.): both houses plus President; joint resolutions are used for continuing or emergency appropriations. Joint resolutions proposing amendments: two-thirds of both houses and three-fourths of the States, no President. Concurrent resolutions (H.Con.Res./S.Con.Res.): both houses, no President, no force of law; used for adjournment, joint rules, and the budget resolution. Simple resolutions (H.Res./S.Res.): one house only.</t>
+        </is>
+      </c>
+      <c r="J17" s="103" t="inlineStr">
+        <is>
+          <t>• "Con" = both houses, no President
+• "J" = like a bill
+• Plain "Res" = one house
+• Setting adjournment is a concurrent resolution</t>
+        </is>
+      </c>
+      <c r="K17" s="103" t="inlineStr">
+        <is>
+          <t>Background for bicameralism and presentment arguments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="105" t="inlineStr">
+        <is>
+          <t>Separation of powers</t>
+        </is>
+      </c>
+      <c r="B18" s="103" t="inlineStr">
+        <is>
+          <t>Treaties &amp; executive agreements</t>
+        </is>
+      </c>
+      <c r="C18" s="103" t="n">
+        <v>9</v>
+      </c>
+      <c r="D18" s="103" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+      <c r="E18" s="104" t="inlineStr">
+        <is>
+          <t>About Treaties (U.S. Senate website)</t>
+        </is>
+      </c>
+      <c r="F18" s="103" t="inlineStr">
+        <is>
+          <t>Treaties: Senate process</t>
+        </is>
+      </c>
+      <c r="G18" s="103" t="inlineStr">
+        <is>
+          <t>Senate explanation of its role in treaty-making.</t>
+        </is>
+      </c>
+      <c r="H18" s="103" t="inlineStr">
+        <is>
+          <t>N/A.</t>
+        </is>
+      </c>
+      <c r="I18" s="103" t="inlineStr">
+        <is>
+          <t>The President makes treaties with the advice and consent of 2/3 of Senators present. The Senate does NOT ratify treaties: after Foreign Relations Committee review it approves or rejects a resolution of ratification, and ratification happens when instruments are exchanged.</t>
+        </is>
+      </c>
+      <c r="J18" s="103" t="inlineStr">
+        <is>
+          <t>• Common trap: 'the Senate ratifies' (wrong: it consents; the President ratifies)
+• Treaties lacking support may simply never get a vote and are withdrawn; pending treaties carry over between Congresses
+• Executive agreements bypass the Senate but are still binding internationally</t>
+        </is>
+      </c>
+      <c r="K18" s="103" t="inlineStr">
+        <is>
+          <t>Use for the mechanics of advice and consent and the rise of executive agreements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="105" t="inlineStr">
+        <is>
+          <t>Separation of powers</t>
+        </is>
+      </c>
+      <c r="B19" s="106" t="inlineStr">
+        <is>
+          <t>Major questions &amp; nondelegation</t>
+        </is>
+      </c>
+      <c r="C19" s="106" t="n">
+        <v>5</v>
+      </c>
+      <c r="D19" s="106" t="inlineStr">
+        <is>
+          <t>Doctrine note</t>
+        </is>
+      </c>
+      <c r="E19" s="107" t="inlineStr">
+        <is>
+          <t>"Major questions" doctrine (and nondelegation)</t>
+        </is>
+      </c>
+      <c r="F19" s="106" t="inlineStr">
+        <is>
+          <t>Statutory canon; separation of powers</t>
+        </is>
+      </c>
+      <c r="G19" s="106" t="inlineStr">
+        <is>
+          <t>NOT a single reader case. The reader raises it in Study Question 27 ("a canon of statutory interpretation... what it has to do with the non-delegation doctrine") and covers nondelegation in the Week 5 CRS report (Gundy's "intelligible principle") and Schechter's separate delegation issue. The case examples in this row (West Virginia v. EPA, Biden v. Nebraska) are from OUTSIDE the reader.</t>
+        </is>
+      </c>
+      <c r="H19" s="106" t="inlineStr">
+        <is>
+          <t>Outside-the-reader anchor: West Virginia v. EPA (2022) rejected EPA's reading of the Clean Air Act to allow a sector-wide shift away from coal power. In 'extraordinary cases' of vast economic and political significance, an agency needs 'clear congressional authorization,' not a broad or vague grant. Biden v. Nebraska (2023) applied it to the student-loan forgiveness program.</t>
+        </is>
+      </c>
+      <c r="I19" s="106" t="inlineStr">
+        <is>
+          <t>MAJOR QUESTIONS: a canon of statutory interpretation. Courts presume Congress makes major policy decisions itself, so they won't read ambiguous or general statutory language to give an agency power over a question of vast economic and political significance without clear authorization. NONDELEGATION: a constitutional rule. Congress can't hand its legislative power to another branch; it must give an 'intelligible principle' (CRS; Gundy). Schechter is one of the rare cases striking a statute on that ground. LINK: the canon is a nondelegation-flavored tool that works by narrowing the STATUTE, not by striking it. It avoids the constitutional question while protecting the same value: Congress, not agencies, makes the big policy calls.</t>
+        </is>
+      </c>
+      <c r="J19" s="106" t="inlineStr">
+        <is>
+          <t>• It's a rule of STATUTORY interpretation, not a constitutional holding
+• Nondelegation = constitutional; asks whether Congress gave an 'intelligible principle' (Gundy, via CRS)
+• Major questions works by reading the statute narrowly; nondelegation would strike the statute down
+• Trigger: vast economic and political significance + agency claiming new power from old or vague text
+• Fix: Congress can always grant the power with clear authorization
+• Schechter: delegation issue is separate from its Commerce Clause holding</t>
+        </is>
+      </c>
+      <c r="K19" s="106" t="inlineStr">
+        <is>
+          <t>Study Q27 answer frame: (1) define the canon (clear authorization needed for major questions); (2) define nondelegation (intelligible principle; Schechter); (3) connect them: the canon enforces nondelegation values through interpretation, sending big policy choices back to Congress. Tie to separation of powers (Federalist 47/51).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="105" t="inlineStr">
+        <is>
+          <t>Judicial review &amp; federal jurisdiction</t>
+        </is>
+      </c>
+      <c r="B20" s="99" t="inlineStr">
+        <is>
+          <t>Foundations &amp; interpretation</t>
+        </is>
+      </c>
+      <c r="C20" s="99" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E20" s="100" t="inlineStr">
+        <is>
+          <t>Calder v. Bull (1798)</t>
+        </is>
+      </c>
+      <c r="F20" s="99" t="inlineStr">
+        <is>
+          <t>Unenumerated rights; review</t>
+        </is>
+      </c>
+      <c r="G20" s="99" t="inlineStr">
+        <is>
+          <t>Connecticut's legislature set aside a probate decree and granted a new hearing; on rehearing the will was approved.</t>
+        </is>
+      </c>
+      <c r="H20" s="99" t="inlineStr">
+        <is>
+          <t>The holding (Ex Post Facto Clause) is not tested; the seriatim dicta of Chase and Iredell are.</t>
+        </is>
+      </c>
+      <c r="I20" s="99" t="inlineStr">
+        <is>
+          <t>Chase: a legislative act contrary to the "great first principles of the social compact" is not rightful authority even without express limits. Iredell: courts may void only acts violating written constitutional provisions, not acts contrary to natural justice.</t>
+        </is>
+      </c>
+      <c r="J20" s="99" t="inlineStr">
+        <is>
+          <t>• Chase's four examples: punishing an act innocent when done; impairing lawful contracts; making a man judge in his own cause; taking property from A and giving it to B
+• Iredell: natural justice has "no fixed standard"; void only in a "clear and urgent case"
+• Both would void a law plainly within an express prohibition
+• Seriatim opinions, no majority opinion</t>
+        </is>
+      </c>
+      <c r="K20" s="99" t="inlineStr">
+        <is>
+          <t>Frames the unenumerated-rights debate (natural law vs. written text) and the limits of judicial review; Iredell anticipates textualist restraint.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="105" t="inlineStr">
+        <is>
+          <t>Judicial review &amp; federal jurisdiction</t>
+        </is>
+      </c>
+      <c r="B21" s="99" t="n"/>
+      <c r="C21" s="99" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E21" s="100" t="inlineStr">
+        <is>
+          <t>Marbury v. Madison (1803)</t>
+        </is>
+      </c>
+      <c r="F21" s="99" t="inlineStr">
+        <is>
+          <t>Judicial review; original jurisdiction</t>
+        </is>
+      </c>
+      <c r="G21" s="99" t="inlineStr">
+        <is>
+          <t>Marbury, appointed a D.C. justice of the peace for five years, sued in the Supreme Court for mandamus ordering Secretary Madison to deliver his signed and sealed commission.</t>
+        </is>
+      </c>
+      <c r="H21" s="99" t="inlineStr">
+        <is>
+          <t>Marbury had a right and a remedy, but Sec. 13 unconstitutionally expanded the Court's original jurisdiction, so the rule was discharged.</t>
+        </is>
+      </c>
+      <c r="I21" s="99" t="inlineStr">
+        <is>
+          <t>"It is emphatically the province and duty of the judicial department to say what the law is"; a law repugnant to the Constitution is void. Art. III's list of original jurisdiction is exclusive, and courts may review ministerial (not political) executive acts affecting individual rights.</t>
+        </is>
+      </c>
+      <c r="J21" s="99" t="inlineStr">
+        <is>
+          <t>• Three questions: right, remedy, mandamus from this Court
+• Appointment complete when President signs, commission when sealed; delivery not required; five-year term made it irrevocable
+• "Nature of the thing to be done," not the office, decides reviewability; political acts are only politically examinable
+• Textual supports: arising under clause, treason two-witness rule, judicial oath, Supremacy Clause's "in pursuance"; Sec. 13 could plausibly have been read to avoid the conflict</t>
+        </is>
+      </c>
+      <c r="K21" s="99" t="inlineStr">
+        <is>
+          <t>Foundation of judicial review; contrast McBain's "who shall determine" critique and Brutus No. 15. Lujan later quotes Marbury that courts decide "the rights of individuals."</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="105" t="inlineStr">
+        <is>
+          <t>Judicial review &amp; federal jurisdiction</t>
+        </is>
+      </c>
+      <c r="B22" s="99" t="n"/>
+      <c r="C22" s="99" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E22" s="100" t="inlineStr">
+        <is>
+          <t>Ex parte McCardle (1869)</t>
+        </is>
+      </c>
+      <c r="F22" s="99" t="inlineStr">
+        <is>
+          <t>Congress's control of jurisdiction</t>
+        </is>
+      </c>
+      <c r="G22" s="99" t="inlineStr">
+        <is>
+          <t>A Mississippi editor held for military trial under Reconstruction appealed a habeas denial under the 1867 Habeas Act; after argument, Congress repealed that appellate jurisdiction over Johnson's veto.</t>
+        </is>
+      </c>
+      <c r="H22" s="99" t="inlineStr">
+        <is>
+          <t>The Court lacked jurisdiction and dismissed the appeal.</t>
+        </is>
+      </c>
+      <c r="I22" s="99" t="inlineStr">
+        <is>
+          <t>Appellate jurisdiction exists "with such exceptions and under such regulations as Congress shall make"; Congress may withdraw it even in a pending case, and the Court will not inquire into motive.</t>
+        </is>
+      </c>
+      <c r="J22" s="99" t="inlineStr">
+        <is>
+          <t>• "We are not at liberty to inquire into the motives of the legislature"
+• Without jurisdiction the only function is "announcing the fact and dismissing the cause"
+• Repeal reached only 1867-Act appeals, not earlier habeas jurisdiction (see Yerger)
+• Context: Milligan barred military trials of civilians where courts operated; Johnson's veto warned repeal could "sweep away every check"; Klein (1871) was the first to strike down a jurisdiction-limiting statute</t>
+        </is>
+      </c>
+      <c r="K22" s="99" t="inlineStr">
+        <is>
+          <t>Leading case for congressional power over appellate jurisdiction (Exceptions Clause); counterpoints are Yerger's narrow reading and Klein.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="105" t="inlineStr">
+        <is>
+          <t>Judicial review &amp; federal jurisdiction</t>
+        </is>
+      </c>
+      <c r="B23" s="99" t="n"/>
+      <c r="C23" s="99" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E23" s="100" t="inlineStr">
+        <is>
+          <t>Ex parte Yerger (1869)</t>
+        </is>
+      </c>
+      <c r="F23" s="99" t="inlineStr">
+        <is>
+          <t>Habeas jurisdiction survives</t>
+        </is>
+      </c>
+      <c r="G23" s="99" t="inlineStr">
+        <is>
+          <t>After the McCardle repeal, a civilian in military custody sought Supreme Court habeas aided by certiorari, relying on pre-1867 authority.</t>
+        </is>
+      </c>
+      <c r="H23" s="99" t="inlineStr">
+        <is>
+          <t>The Court had jurisdiction: the 1868 repeal reached only appeals under the 1867 Act, leaving 1789 Act habeas intact.</t>
+        </is>
+      </c>
+      <c r="I23" s="99" t="inlineStr">
+        <is>
+          <t>"Repeals by implication are not favored"; jurisdiction-stripping statutes are read narrowly.</t>
+        </is>
+      </c>
+      <c r="J23" s="99" t="inlineStr">
+        <is>
+          <t>• Habeas "aided by the writ of certiorari" under Sec. 14 of the 1789 Act
+• Chase called the 1868 Act unusual legislation justified only by an "imperious public exigency"
+• Reaffirms Marbury that Sec. 13 mandamus is appellate and Congress cannot extend original jurisdiction</t>
+        </is>
+      </c>
+      <c r="K23" s="99" t="inlineStr">
+        <is>
+          <t>Use with McCardle: Congress can strip jurisdiction expressly, but courts read repeals narrowly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="105" t="inlineStr">
+        <is>
+          <t>Judicial review &amp; federal jurisdiction</t>
+        </is>
+      </c>
+      <c r="B24" s="101" t="n"/>
+      <c r="C24" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="101" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="E24" s="102" t="inlineStr">
+        <is>
+          <t>Federalist No. 78 (1788)</t>
+        </is>
+      </c>
+      <c r="F24" s="101" t="inlineStr">
+        <is>
+          <t>Judicial review: defense</t>
+        </is>
+      </c>
+      <c r="G24" s="101" t="inlineStr">
+        <is>
+          <t>Hamilton defends the federal judiciary, life tenure and judicial review.</t>
+        </is>
+      </c>
+      <c r="H24" s="101" t="inlineStr">
+        <is>
+          <t>Courts must void acts contrary to the Constitution because the people's will in the Constitution is superior to the legislature's.</t>
+        </is>
+      </c>
+      <c r="I24" s="101" t="inlineStr">
+        <is>
+          <t>Judicial review does not make judges superior to the legislature; it supposes the power of the people is superior to both. Courts are an intermediate body keeping the legislature within its limits.</t>
+        </is>
+      </c>
+      <c r="J24" s="101" t="inlineStr">
+        <is>
+          <t>• "Least dangerous" branch: "neither FORCE nor WILL, but merely judgment"
+• Agency argument: the deputy is not greater than his principal
+• Courts must exercise JUDGMENT, not WILL
+• Life tenure (good behavior); periodic appointment would breed complaisance or popularity-seeking</t>
+        </is>
+      </c>
+      <c r="K24" s="101" t="inlineStr">
+        <is>
+          <t>Anchor for the legitimacy of judicial review and Marbury; Brutus Nos. 11 and 15 and Martineau are the counterpoints.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="105" t="inlineStr">
+        <is>
+          <t>Judicial review &amp; federal jurisdiction</t>
+        </is>
+      </c>
+      <c r="B25" s="101" t="n"/>
+      <c r="C25" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" s="101" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="E25" s="102" t="inlineStr">
+        <is>
+          <t>Brutus No. 11 (1788)</t>
+        </is>
+      </c>
+      <c r="F25" s="101" t="inlineStr">
+        <is>
+          <t>Anti-Federalist: judicial power</t>
+        </is>
+      </c>
+      <c r="G25" s="101" t="inlineStr">
+        <is>
+          <t>Anti-Federalist critique of Article III's grant of judicial power.</t>
+        </is>
+      </c>
+      <c r="H25" s="101" t="inlineStr">
+        <is>
+          <t>Federal courts will construe the Constitution by its "reason and spirit" and silently subvert the states' powers.</t>
+        </is>
+      </c>
+      <c r="I25" s="101" t="inlineStr">
+        <is>
+          <t>Because "arising under this constitution" must differ from cases under the laws, judges gain power to construe the Constitution, with no appeal from their errors.</t>
+        </is>
+      </c>
+      <c r="J25" s="101" t="inlineStr">
+        <is>
+          <t>• Two reasons judges will expand federal power: general, indefinite terms (necessary and proper clause, preamble) invite equitable construction; judges' self-interest in power and pay
+• "Silent and imperceptible" subversion of state governments
+• NOT a claim that judges are elected by Congress</t>
+        </is>
+      </c>
+      <c r="K25" s="101" t="inlineStr">
+        <is>
+          <t>Use as the Anti-Federalist critique of judicial review and judicial expansion of federal power.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="105" t="inlineStr">
+        <is>
+          <t>Judicial review &amp; federal jurisdiction</t>
+        </is>
+      </c>
+      <c r="B26" s="101" t="n"/>
+      <c r="C26" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="101" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="E26" s="102" t="inlineStr">
+        <is>
+          <t>Brutus No. 15 (1788)</t>
+        </is>
+      </c>
+      <c r="F26" s="101" t="inlineStr">
+        <is>
+          <t>Anti-Federalist: judicial supremacy</t>
+        </is>
+      </c>
+      <c r="G26" s="101" t="inlineStr">
+        <is>
+          <t>Anti-Federalist essay on the Supreme Court's lack of accountability.</t>
+        </is>
+      </c>
+      <c r="H26" s="101" t="inlineStr">
+        <is>
+          <t>The Supreme Court will be "exalted above all other power in the government, and subject to no controul."</t>
+        </is>
+      </c>
+      <c r="I26" s="101" t="inlineStr">
+        <is>
+          <t>Constitutional construction should rest with the legislature, which voters can remove; unlike England, no law explaining the Constitution will bind the judges.</t>
+        </is>
+      </c>
+      <c r="J26" s="101" t="inlineStr">
+        <is>
+          <t>• "The judges are supreme"; English Parliament could correct its judges, Congress cannot
+• Courts will abolish the states gradually, "by insensible degrees"
+• Agrees courts will have review power but treats it as a defect (vs. Hamilton in No. 78)</t>
+        </is>
+      </c>
+      <c r="K26" s="101" t="inlineStr">
+        <is>
+          <t>Pair with Federalist No. 78 for the judicial review debate; supports departmentalist critiques like McBain's.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="105" t="inlineStr">
+        <is>
+          <t>Judicial review &amp; federal jurisdiction</t>
+        </is>
+      </c>
+      <c r="B27" s="101" t="n"/>
+      <c r="C27" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="101" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="E27" s="102" t="inlineStr">
+        <is>
+          <t>Judiciary Acts of 1789 and 1801; D.C. Act (1801)</t>
+        </is>
+      </c>
+      <c r="F27" s="101" t="inlineStr">
+        <is>
+          <t>Federal courts: statutes</t>
+        </is>
+      </c>
+      <c r="G27" s="101" t="inlineStr">
+        <is>
+          <t>Statutes organizing the federal courts, background to Marbury.</t>
+        </is>
+      </c>
+      <c r="H27" s="101" t="inlineStr">
+        <is>
+          <t>The 1789 Act set up a six-justice Court and, in Sec. 13, authorized mandamus to persons holding office under the United States.</t>
+        </is>
+      </c>
+      <c r="I27" s="101" t="inlineStr">
+        <is>
+          <t>Sec. 25 allowed Supreme Court review of state high court judgments rejecting federal claims; Sec. 14 authorized habeas. The 1802 repeal of the 1801 Act left the D.C. Act's five-year justice-of-the-peace posts intact.</t>
+        </is>
+      </c>
+      <c r="J27" s="101" t="inlineStr">
+        <is>
+          <t>• Sec. 13 mandamus language is what Marbury struck down as applied
+• D.C. Act: justices of the peace serve FIVE years, which made Marbury's office irrevocable
+• 1801 Act would shrink the Court to five at the next vacancy; 1802 Act repealed it but not the D.C. Act
+• Sec. 14 habeas is the basis Yerger relied on</t>
+        </is>
+      </c>
+      <c r="K27" s="101" t="inlineStr">
+        <is>
+          <t>Use to explain why Marbury's commission vested a right and why Congress controls jurisdiction by statute (McCardle, Yerger).</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="105" t="inlineStr">
+        <is>
+          <t>Judicial review &amp; federal jurisdiction</t>
+        </is>
+      </c>
+      <c r="B28" s="101" t="n"/>
+      <c r="C28" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" s="101" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="E28" s="102" t="inlineStr">
+        <is>
+          <t>Organization of federal courts / binding authority</t>
+        </is>
+      </c>
+      <c r="F28" s="101" t="inlineStr">
+        <is>
+          <t>Precedent: binding rules</t>
+        </is>
+      </c>
+      <c r="G28" s="101" t="inlineStr">
+        <is>
+          <t>Reader's rules on which decisions bind which courts (13 courts of appeals, 94 district courts; Illinois is in the Seventh Circuit).</t>
+        </is>
+      </c>
+      <c r="H28" s="101" t="inlineStr">
+        <is>
+          <t>Supreme Court decisions bind all courts until the Court overrules them; circuit decisions bind district courts within the circuit only.</t>
+        </is>
+      </c>
+      <c r="I28" s="101" t="inlineStr">
+        <is>
+          <t>Rule 1: Supreme Court binds until it overrules (exception: Congress amends the interpreted statute). Rule 2: courts of appeals bind their own district courts. Rule 3: district court decisions bind no one. Rule 4: only Supreme Court decisions on federal law bind state courts.</t>
+        </is>
+      </c>
+      <c r="J28" s="101" t="inlineStr">
+        <is>
+          <t>• Other circuits (e.g., Eighth) get only "respectful consideration" (Glaser)
+• Intervening Supreme Court decision irreconcilable with circuit precedent controls
+• Lower federal decisions are only persuasive in state courts
+• Statutory decision no longer controls after Congress amends the statute</t>
+        </is>
+      </c>
+      <c r="K28" s="101" t="inlineStr">
+        <is>
+          <t>Use to identify controlling authority in any hypo set in a particular court.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="105" t="inlineStr">
+        <is>
+          <t>Judicial review &amp; federal jurisdiction</t>
+        </is>
+      </c>
+      <c r="B29" s="103" t="n"/>
+      <c r="C29" s="103" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" s="103" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+      <c r="E29" s="104" t="inlineStr">
+        <is>
+          <t>Martineau, Society in America (1837)</t>
+        </is>
+      </c>
+      <c r="F29" s="103" t="inlineStr">
+        <is>
+          <t>Critique of judicial tenure</t>
+        </is>
+      </c>
+      <c r="G29" s="103" t="inlineStr">
+        <is>
+          <t>An English observer's view of American institutions.</t>
+        </is>
+      </c>
+      <c r="H29" s="103" t="inlineStr">
+        <is>
+          <t>Life-tenured judges hold a "virtually irresponsible office," an inconsistency in a republic.</t>
+        </is>
+      </c>
+      <c r="I29" s="103" t="inlineStr">
+        <is>
+          <t>The judiciary is "not republican at all"; the House is mainly republican, the Senate only partly.</t>
+        </is>
+      </c>
+      <c r="J29" s="103" t="inlineStr">
+        <is>
+          <t>• Her critique is about accountability of life tenure
+• Pairs with Brutus 15 (judges independent of the people)</t>
+        </is>
+      </c>
+      <c r="K29" s="103" t="inlineStr">
+        <is>
+          <t>Counterpoint to Federalist 78's defense of life tenure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="105" t="inlineStr">
+        <is>
+          <t>Judicial review &amp; federal jurisdiction</t>
+        </is>
+      </c>
+      <c r="B30" s="103" t="inlineStr">
+        <is>
+          <t>Standing</t>
+        </is>
+      </c>
+      <c r="C30" s="103" t="n">
+        <v>4</v>
+      </c>
+      <c r="D30" s="103" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+      <c r="E30" s="104" t="inlineStr">
+        <is>
+          <t>Article III, Section 2 (text)</t>
+        </is>
+      </c>
+      <c r="F30" s="103" t="inlineStr">
+        <is>
+          <t>Judicial power: text</t>
+        </is>
+      </c>
+      <c r="G30" s="103" t="inlineStr">
+        <is>
+          <t>The constitutional text listing the cases and controversies federal courts may hear.</t>
+        </is>
+      </c>
+      <c r="H30" s="103" t="inlineStr">
+        <is>
+          <t>Extends the judicial power to listed controversies, including those "between a State and Citizens of another State."</t>
+        </is>
+      </c>
+      <c r="I30" s="103" t="inlineStr">
+        <is>
+          <t>Gives the Supreme Court original jurisdiction in cases involving States and ambassadors, and appellate jurisdiction "with such Exceptions, and under such Regulations as the Congress shall make."</t>
+        </is>
+      </c>
+      <c r="J30" s="103" t="inlineStr">
+        <is>
+          <t>• The state-citizen clause is what Chisholm applied and the Eleventh Amendment cut back
+• The Exceptions Clause is the basis for McCardle
+• Marbury: Congress can't add to original jurisdiction</t>
+        </is>
+      </c>
+      <c r="K30" s="103" t="inlineStr">
+        <is>
+          <t>Anchor text for Chisholm, Hans, McCardle and Marbury.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="105" t="inlineStr">
+        <is>
+          <t>Advisory opinions</t>
+        </is>
+      </c>
+      <c r="B31" s="101" t="n"/>
+      <c r="C31" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" s="101" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="E31" s="102" t="inlineStr">
+        <is>
+          <t>Jefferson letter (July 18, 1793)</t>
+        </is>
+      </c>
+      <c r="F31" s="101" t="inlineStr">
+        <is>
+          <t>Advisory opinions: request</t>
+        </is>
+      </c>
+      <c r="G31" s="101" t="inlineStr">
+        <is>
+          <t>Secretary of State Jefferson, for Washington, asked the Justices whether they would advise on abstract legal questions raised by the European war.</t>
+        </is>
+      </c>
+      <c r="H31" s="101" t="inlineStr">
+        <is>
+          <t>The executive sought the Justices' advice on treaties, the law of nations and U.S. law outside any case.</t>
+        </is>
+      </c>
+      <c r="I31" s="101" t="inlineStr">
+        <is>
+          <t>The request (and the refusal) is the origin of the bar on advisory opinions.</t>
+        </is>
+      </c>
+      <c r="J31" s="101" t="inlineStr">
+        <is>
+          <t>• First asked whether the public could "with propriety" be availed of their advice
+• Questions arose in circumstances not giving the courts cognizance of them</t>
+        </is>
+      </c>
+      <c r="K31" s="101" t="inlineStr">
+        <is>
+          <t>Use with the Justices' reply as the historical root of the case-or-controversy requirement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="105" t="inlineStr">
+        <is>
+          <t>Advisory opinions</t>
+        </is>
+      </c>
+      <c r="B32" s="101" t="n"/>
+      <c r="C32" s="101" t="n">
+        <v>2</v>
+      </c>
+      <c r="D32" s="101" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="E32" s="102" t="inlineStr">
+        <is>
+          <t>Justices' letter to Washington (Aug. 8, 1793)</t>
+        </is>
+      </c>
+      <c r="F32" s="101" t="inlineStr">
+        <is>
+          <t>Advisory opinions: refusal</t>
+        </is>
+      </c>
+      <c r="G32" s="101" t="inlineStr">
+        <is>
+          <t>The Justices' reply to Jefferson's July 18 request for advice.</t>
+        </is>
+      </c>
+      <c r="H32" s="101" t="inlineStr">
+        <is>
+          <t>The Justices declined to decide the questions "extrajudicially."</t>
+        </is>
+      </c>
+      <c r="I32" s="101" t="inlineStr">
+        <is>
+          <t>Separation of powers bars federal judges from giving advisory opinions outside a case.</t>
+        </is>
+      </c>
+      <c r="J32" s="101" t="inlineStr">
+        <is>
+          <t>• Three reasons: lines of separation among the departments; departments as checks on each other; Justices are judges of a court in the last resort
+• Textual point: the President's power to call for opinions is limited to executive department heads</t>
+        </is>
+      </c>
+      <c r="K32" s="101" t="inlineStr">
+        <is>
+          <t>Root of the no-advisory-opinions rule; connect to standing cases that describe what courts do not do (TransUnion, Sierra Club fn. 3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="105" t="inlineStr">
+        <is>
+          <t>Standing</t>
+        </is>
+      </c>
+      <c r="B33" s="99" t="n"/>
+      <c r="C33" s="99" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E33" s="100" t="inlineStr">
+        <is>
+          <t>Massachusetts v. Mellon / Frothingham v. Mellon (1923)</t>
+        </is>
+      </c>
+      <c r="F33" s="99" t="inlineStr">
+        <is>
+          <t>Standing: taxpayer and state</t>
+        </is>
+      </c>
+      <c r="G33" s="99" t="inlineStr">
+        <is>
+          <t>Massachusetts (original suit) and a federal taxpayer challenged the Maternity Act, which gave grants to states that accepted it.</t>
+        </is>
+      </c>
+      <c r="H33" s="99" t="inlineStr">
+        <is>
+          <t>Both suits were dismissed for want of jurisdiction without reaching the merits.</t>
+        </is>
+      </c>
+      <c r="I33" s="99" t="inlineStr">
+        <is>
+          <t>A party must show a "direct injury" from the statute, "not merely that he suffers in some indefinite way in common with people generally." A state's bare claim that Congress usurped reserved powers is political, not judicial.</t>
+        </is>
+      </c>
+      <c r="J33" s="99" t="inlineStr">
+        <is>
+          <t>• State: the Act imposed no obligation, just an option it could reject "by the simple expedient of not yielding"
+• Federal taxpayer's interest is "minute and indeterminable" and the tax effect "remote, fluctuating and uncertain"; a municipal taxpayer's is direct, like a stockholder's
+• Courts have no power per se to annul acts of Congress, only to disregard them when deciding a real injury
+• Hearing it would assume authority over a co-equal department</t>
+        </is>
+      </c>
+      <c r="K33" s="99" t="inlineStr">
+        <is>
+          <t>Starting point for the taxpayer-standing line (Flast, Richardson, Hein) and the generalized-grievance bar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="105" t="inlineStr">
+        <is>
+          <t>Standing</t>
+        </is>
+      </c>
+      <c r="B34" s="99" t="n"/>
+      <c r="C34" s="99" t="n">
+        <v>2</v>
+      </c>
+      <c r="D34" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E34" s="100" t="inlineStr">
+        <is>
+          <t>Flast v. Cohen (1968)</t>
+        </is>
+      </c>
+      <c r="F34" s="99" t="inlineStr">
+        <is>
+          <t>Standing: taxpayer (Establishment)</t>
+        </is>
+      </c>
+      <c r="G34" s="99" t="inlineStr">
+        <is>
+          <t>Seven federal taxpayers challenged federal education funds used for instruction and textbooks in religious schools under the Establishment and Free Exercise Clauses.</t>
+        </is>
+      </c>
+      <c r="H34" s="99" t="inlineStr">
+        <is>
+          <t>Taxpayers have standing to challenge congressional taxing-and-spending action that violates a specific constitutional limit on that power; reversed.</t>
+        </is>
+      </c>
+      <c r="I34" s="99" t="inlineStr">
+        <is>
+          <t>Two-part nexus test: (1) the challenge targets an exercise of Congress's Art. I, Sec. 8 taxing and spending power, not incidental spending under a regulatory statute; (2) the enactment exceeds a specific constitutional limitation on that power, such as the Establishment Clause.</t>
+        </is>
+      </c>
+      <c r="J34" s="99" t="inlineStr">
+        <is>
+          <t>• Frothingham met the first nexus but failed the second (general Art. I / Tenth Amendment claim)
+• "Iceberg quality" of "cases" and "controversies": adversary context plus separation of powers = justiciability
+• Quip: Frothingham lost because her tax bill was not large enough
+• Douglas: test not durable, overrule Frothingham now; Harlan dissented</t>
+        </is>
+      </c>
+      <c r="K34" s="99" t="inlineStr">
+        <is>
+          <t>The high-water mark of taxpayer standing, later confined to its facts (Richardson, Hein); Powell and Scalia urged abandoning or overruling it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="105" t="inlineStr">
+        <is>
+          <t>Standing</t>
+        </is>
+      </c>
+      <c r="B35" s="99" t="n"/>
+      <c r="C35" s="99" t="n">
+        <v>2</v>
+      </c>
+      <c r="D35" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E35" s="100" t="inlineStr">
+        <is>
+          <t>Sierra Club v. Morton (1972)</t>
+        </is>
+      </c>
+      <c r="F35" s="99" t="inlineStr">
+        <is>
+          <t>Standing: aesthetic injury</t>
+        </is>
+      </c>
+      <c r="G35" s="99" t="inlineStr">
+        <is>
+          <t>The Sierra Club sued under the APA to stop a Disney ski resort in Mineral King valley, alleging only its special interest in conservation.</t>
+        </is>
+      </c>
+      <c r="H35" s="99" t="inlineStr">
+        <is>
+          <t>No standing: the Club did not allege that it or its members used Mineral King; affirmed.</t>
+        </is>
+      </c>
+      <c r="I35" s="99" t="inlineStr">
+        <is>
+          <t>Aesthetic and environmental harm can be injury in fact, but the plaintiff must "be himself among the injured." A mere "interest in a problem" is not enough.</t>
+        </is>
+      </c>
+      <c r="J35" s="99" t="inlineStr">
+        <is>
+          <t>• Widely shared interests are not less deserving of protection
+• Court noted the Club could amend under Rule 15 (members who use the area would likely have standing)
+• Douglas dissent: let environmental objects sue in their own name
+• Blackmun dissent: approve on condition of amendment, or an "imaginative expansion" of standing</t>
+        </is>
+      </c>
+      <c r="K35" s="99" t="inlineStr">
+        <is>
+          <t>Key for injury-in-fact and organizational standing; leads to Lujan's use-the-area requirement and Douglas v. NPS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="105" t="inlineStr">
+        <is>
+          <t>Standing</t>
+        </is>
+      </c>
+      <c r="B36" s="99" t="n"/>
+      <c r="C36" s="99" t="n">
+        <v>2</v>
+      </c>
+      <c r="D36" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E36" s="100" t="inlineStr">
+        <is>
+          <t>United States v. Richardson (1974)</t>
+        </is>
+      </c>
+      <c r="F36" s="99" t="inlineStr">
+        <is>
+          <t>Standing: generalized grievance</t>
+        </is>
+      </c>
+      <c r="G36" s="99" t="inlineStr">
+        <is>
+          <t>A taxpayer and voter challenged secret CIA expenditures under the Statement and Account Clause, claiming he could not follow government or vote intelligently.</t>
+        </is>
+      </c>
+      <c r="H36" s="99" t="inlineStr">
+        <is>
+          <t>No standing; reversed. His claim fails the Flast test and is a generalized grievance "common to all members of the public."</t>
+        </is>
+      </c>
+      <c r="I36" s="99" t="inlineStr">
+        <is>
+          <t>Undifferentiated harms shared by all citizens belong to Congress and the political process, not the courts.</t>
+        </is>
+      </c>
+      <c r="J36" s="99" t="inlineStr">
+        <is>
+          <t>• No "Athenian democracy or New England town meeting" by lawsuit
+• Powell concurring: abandon the Flast nexus test but keep Flast on its facts
+• Douglas dissent: "The sovereign in this Nation is the people, not the bureaucracy"
+• Halperin v. CIA (D.C. Cir.): FOIA plaintiff also lacked standing under the Clause</t>
+        </is>
+      </c>
+      <c r="K36" s="99" t="inlineStr">
+        <is>
+          <t>Leading generalized-grievance case; FEC v. Akins distinguishes it where a statute grants the information right.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="105" t="inlineStr">
+        <is>
+          <t>Standing</t>
+        </is>
+      </c>
+      <c r="B37" s="99" t="n"/>
+      <c r="C37" s="99" t="n">
+        <v>2</v>
+      </c>
+      <c r="D37" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E37" s="100" t="inlineStr">
+        <is>
+          <t>City of Los Angeles v. Lyons (1983)</t>
+        </is>
+      </c>
+      <c r="F37" s="99" t="inlineStr">
+        <is>
+          <t>Standing: injunctions, future harm</t>
+        </is>
+      </c>
+      <c r="G37" s="99" t="inlineStr">
+        <is>
+          <t>LA police choked Lyons unconscious during a traffic stop; he sought damages and an injunction against chokeholds.</t>
+        </is>
+      </c>
+      <c r="H37" s="99" t="inlineStr">
+        <is>
+          <t>Lyons lacked standing to seek the injunction because he showed no "real and immediate threat" of being choked again.</t>
+        </is>
+      </c>
+      <c r="I37" s="99" t="inlineStr">
+        <is>
+          <t>Past injury may support damages but not prospective relief; standing must be shown for each form of relief.</t>
+        </is>
+      </c>
+      <c r="J37" s="99" t="inlineStr">
+        <is>
+          <t>• "Incredible assertion" needed: another police encounter AND either all officers always choke or the City ordered it
+• Without likely future injury he is no more entitled to an injunction than any other citizen
+• Marshall dissent: majority fragments standing by remedy; standing turns on the stake in the dispute</t>
+        </is>
+      </c>
+      <c r="K37" s="99" t="inlineStr">
+        <is>
+          <t>Use for injunctive-relief standing and imminence; TransUnion and Clapper build on it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="105" t="inlineStr">
+        <is>
+          <t>Standing</t>
+        </is>
+      </c>
+      <c r="B38" s="99" t="n"/>
+      <c r="C38" s="99" t="n">
+        <v>2</v>
+      </c>
+      <c r="D38" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E38" s="100" t="inlineStr">
+        <is>
+          <t>Allen v. Wright (1984)</t>
+        </is>
+      </c>
+      <c r="F38" s="99" t="inlineStr">
+        <is>
+          <t>Standing: framework</t>
+        </is>
+      </c>
+      <c r="G38" s="99" t="inlineStr">
+        <is>
+          <t>The excerpt gives no facts; it is read for O'Connor's statement of standing doctrine.</t>
+        </is>
+      </c>
+      <c r="H38" s="99" t="inlineStr">
+        <is>
+          <t>The excerpt states the framework, not a disposition: Art. III standing is built on separation of powers.</t>
+        </is>
+      </c>
+      <c r="I38" s="99" t="inlineStr">
+        <is>
+          <t>Constitutional core: personal injury fairly traceable to the defendant's conduct and likely redressed by the relief. Prudential limits: no third-party rights, no generalized grievances, zone of interests.</t>
+        </is>
+      </c>
+      <c r="J38" s="99" t="inlineStr">
+        <is>
+          <t>• Three questions: injury too abstract? causation too attenuated? relief too speculative?
+• Injury must be "distinct and palpable," not abstract, conjectural or hypothetical
+• Courts act only "in the last resort, and as a necessity"
+• Quotes Bork (Vander Jagt): doctrines rest on an idea "more than an intuition but less than a rigorous and explicit theory"</t>
+        </is>
+      </c>
+      <c r="K38" s="99" t="inlineStr">
+        <is>
+          <t>Cite for the three-element test and the separation-of-powers basis of standing; Davis's complexity critique is the counterpoint.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="105" t="inlineStr">
+        <is>
+          <t>Standing</t>
+        </is>
+      </c>
+      <c r="B39" s="99" t="n"/>
+      <c r="C39" s="99" t="n">
+        <v>2</v>
+      </c>
+      <c r="D39" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E39" s="100" t="inlineStr">
+        <is>
+          <t>Lujan v. Defenders of Wildlife (1992)</t>
+        </is>
+      </c>
+      <c r="F39" s="99" t="inlineStr">
+        <is>
+          <t>Standing: elements; procedural</t>
+        </is>
+      </c>
+      <c r="G39" s="99" t="inlineStr">
+        <is>
+          <t>Wildlife groups challenged an Interior rule limiting ESA consultation to actions in the U.S. or high seas; members had visited foreign habitats and hoped to return some day.</t>
+        </is>
+      </c>
+      <c r="H39" s="99" t="inlineStr">
+        <is>
+          <t>No standing; reversed and remanded.</t>
+        </is>
+      </c>
+      <c r="I39" s="99" t="inlineStr">
+        <is>
+          <t>"Irreducible constitutional minimum": (1) injury in fact, concrete and particularized and actual or imminent; (2) causation, fairly traceable to the defendant; (3) redressability, likely not speculative. Congress cannot convert the public interest in lawful government into an individual right.</t>
+        </is>
+      </c>
+      <c r="J39" s="99" t="inlineStr">
+        <is>
+          <t>• "Some day" intentions without concrete plans are not imminent
+• Rejected ecosystem, animal and vocational nexus theories (Bronx Zoo keeper "beyond all reason")
+• Object of regulation: standing easy; regulation of a third party: "substantially more difficult"
+• Procedural right needs a concrete interest; fn. 7 relaxes redressability for a dam neighbor; Kennedy concurred, Blackmun dissented ("slash-and-burn")</t>
+        </is>
+      </c>
+      <c r="K39" s="99" t="inlineStr">
+        <is>
+          <t>Central standing test; links to Take Care Clause separation-of-powers theme. Akins and TransUnion test how far Congress can create standing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="105" t="inlineStr">
+        <is>
+          <t>Standing</t>
+        </is>
+      </c>
+      <c r="B40" s="99" t="n"/>
+      <c r="C40" s="99" t="n">
+        <v>2</v>
+      </c>
+      <c r="D40" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E40" s="100" t="inlineStr">
+        <is>
+          <t>FEC v. Akins (1998)</t>
+        </is>
+      </c>
+      <c r="F40" s="99" t="inlineStr">
+        <is>
+          <t>Standing: informational injury</t>
+        </is>
+      </c>
+      <c r="G40" s="99" t="inlineStr">
+        <is>
+          <t>Voters challenged the FEC's ruling that AIPAC was not a "political committee" required to disclose donors and spending.</t>
+        </is>
+      </c>
+      <c r="H40" s="99" t="inlineStr">
+        <is>
+          <t>The voters had standing; remanded.</t>
+        </is>
+      </c>
+      <c r="I40" s="99" t="inlineStr">
+        <is>
+          <t>Failure to obtain information a statute requires to be public is injury in fact; a widely shared but concrete injury is not a barred generalized grievance.</t>
+        </is>
+      </c>
+      <c r="J40" s="99" t="inlineStr">
+        <is>
+          <t>• Distinguished Richardson: a statute protects these plaintiffs, and Richardson was about taxpayer standing
+• Injury "directly related to voting, the most basic of political rights"
+• Agency discretion does not defeat redressability (remand "like a new jury after a mistrial")
+• Scalia dissent: Richardson reduced to a "curio"; "burnt leg, burnt arm"; transfers the Take Care duty to courts</t>
+        </is>
+      </c>
+      <c r="K40" s="99" t="inlineStr">
+        <is>
+          <t>Shows Congress can create standing through statutory information rights; contrast Lujan and TransUnion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="105" t="inlineStr">
+        <is>
+          <t>Standing</t>
+        </is>
+      </c>
+      <c r="B41" s="99" t="n"/>
+      <c r="C41" s="99" t="n">
+        <v>3</v>
+      </c>
+      <c r="D41" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E41" s="100" t="inlineStr">
+        <is>
+          <t>Hein v. Freedom from Religion Found. (2007)</t>
+        </is>
+      </c>
+      <c r="F41" s="99" t="inlineStr">
+        <is>
+          <t>Standing: taxpayer (Executive)</t>
+        </is>
+      </c>
+      <c r="G41" s="99" t="inlineStr">
+        <is>
+          <t>Taxpayers challenged White House faith-based conferences funded from general Executive Branch appropriations under the Establishment Clause.</t>
+        </is>
+      </c>
+      <c r="H41" s="99" t="inlineStr">
+        <is>
+          <t>No taxpayer standing; reversed. Flast does not reach discretionary Executive Branch expenditures.</t>
+        </is>
+      </c>
+      <c r="I41" s="99" t="inlineStr">
+        <is>
+          <t>The Flast exception is narrow, covers only congressional laws authorizing spending, and has largely been confined to its facts.</t>
+        </is>
+      </c>
+      <c r="J41" s="99" t="inlineStr">
+        <is>
+          <t>• Plurality (Alito), not a majority opinion
+• Scalia (with Thomas): overrule Flast; Alito: Scalia is "wrong," "We decide only the case at hand"
+• Souter dissent: same stake as Flast; the branch causing injury should not matter
+• Other clauses never supported taxpayer standing (Richardson, Valley Forge, Cuno)</t>
+        </is>
+      </c>
+      <c r="K41" s="99" t="inlineStr">
+        <is>
+          <t>End of the taxpayer-standing line from Frothingham through Flast and Richardson; shows narrowing without overruling.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="105" t="inlineStr">
+        <is>
+          <t>Standing</t>
+        </is>
+      </c>
+      <c r="B42" s="99" t="n"/>
+      <c r="C42" s="99" t="n">
+        <v>3</v>
+      </c>
+      <c r="D42" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E42" s="100" t="inlineStr">
+        <is>
+          <t>Clapper v. Amnesty Int'l USA (2013)</t>
+        </is>
+      </c>
+      <c r="F42" s="99" t="inlineStr">
+        <is>
+          <t>Standing: certainly impending</t>
+        </is>
+      </c>
+      <c r="G42" s="99" t="inlineStr">
+        <is>
+          <t>Lawyers and organizations who communicate with people abroad challenged FISA Sec. 702 the day it passed, fearing interception and paying to avoid it.</t>
+        </is>
+      </c>
+      <c r="H42" s="99" t="inlineStr">
+        <is>
+          <t>No standing; reversed. The feared injury was not certainly impending or fairly traceable, and plaintiffs cannot manufacture standing by spending money.</t>
+        </is>
+      </c>
+      <c r="I42" s="99" t="inlineStr">
+        <is>
+          <t>Threatened injury must be "certainly impending"; possible future injury is not enough. Standing review is especially rigorous where the merits would strike down another branch's action.</t>
+        </is>
+      </c>
+      <c r="J42" s="99" t="inlineStr">
+        <is>
+          <t>• Five-link "highly attenuated chain"; link 2 (use of 1881a vs. other authority) defeats traceability
+• FISC approval made injury depend on independent judges
+• Fn. 4: plaintiff's burden, not government's; fn. 5: fails even "substantial risk"
+• Breyer dissent: certainty is not the touchstone; "certainly" is emphasis</t>
+        </is>
+      </c>
+      <c r="K42" s="99" t="inlineStr">
+        <is>
+          <t>Leading imminence case; SBA List softens it with "substantial risk," and Douglas applies it to aesthetic injury.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="105" t="inlineStr">
+        <is>
+          <t>Standing</t>
+        </is>
+      </c>
+      <c r="B43" s="99" t="inlineStr">
+        <is>
+          <t>Ripeness</t>
+        </is>
+      </c>
+      <c r="C43" s="99" t="n">
+        <v>3</v>
+      </c>
+      <c r="D43" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E43" s="100" t="inlineStr">
+        <is>
+          <t>Susan B. Anthony List v. Driehaus (2014)</t>
+        </is>
+      </c>
+      <c r="F43" s="99" t="inlineStr">
+        <is>
+          <t>Standing: pre-enforcement</t>
+        </is>
+      </c>
+      <c r="G43" s="99" t="inlineStr">
+        <is>
+          <t>The excerpt gives no facts; it addresses standing for a pre-enforcement challenge.</t>
+        </is>
+      </c>
+      <c r="H43" s="99" t="inlineStr">
+        <is>
+          <t>Petitioners showed injury in fact; reversed and remanded for the remaining standing elements.</t>
+        </is>
+      </c>
+      <c r="I43" s="99" t="inlineStr">
+        <is>
+          <t>Pre-enforcement injury exists where the plaintiff intends conduct arguably affected with a constitutional interest, proscribed by statute, with a credible threat of prosecution (Babbitt). Future injury suffices if "certainly impending" or a "substantial risk."</t>
+        </is>
+      </c>
+      <c r="J43" s="99" t="inlineStr">
+        <is>
+          <t>• No need to be arrested or prosecuted first (Steffel)
+• Credible threat: past enforcement against others and refusal to disavow (Holder); well-founded fear plus costly compliance (American Booksellers)
+• Fn. 5: standing and ripeness boil down to the same question</t>
+        </is>
+      </c>
+      <c r="K43" s="99" t="inlineStr">
+        <is>
+          <t>Use for pre-enforcement challenges; bridges standing (Clapper) and ripeness (Texas v. United States).</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="105" t="inlineStr">
+        <is>
+          <t>Standing</t>
+        </is>
+      </c>
+      <c r="B44" s="99" t="n"/>
+      <c r="C44" s="99" t="n">
+        <v>3</v>
+      </c>
+      <c r="D44" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E44" s="100" t="inlineStr">
+        <is>
+          <t>TransUnion LLC v. Ramirez (2021)</t>
+        </is>
+      </c>
+      <c r="F44" s="99" t="inlineStr">
+        <is>
+          <t>Standing: concrete harm</t>
+        </is>
+      </c>
+      <c r="G44" s="99" t="inlineStr">
+        <is>
+          <t>A class of 8,185 sued under FCRA over false OFAC "potential terrorist" alerts; only 1,853 had reports sent to businesses, and mailing-format claims were added.</t>
+        </is>
+      </c>
+      <c r="H44" s="99" t="inlineStr">
+        <is>
+          <t>Only the 1,853 had standing on the reasonable-procedures claim; only Ramirez had standing on the two mailing claims; reversed and remanded.</t>
+        </is>
+      </c>
+      <c r="I44" s="99" t="inlineStr">
+        <is>
+          <t>"No concrete harm, no standing": a harm is concrete if it bears a close relationship to a harm traditionally recognized in American courts. An injury in law is not an injury in fact, and every class member needs standing for damages.</t>
+        </is>
+      </c>
+      <c r="J44" s="99" t="inlineStr">
+        <is>
+          <t>• Dissemination is like defamation; undisclosed file is a letter in a desk drawer
+• Risk of future harm can support an injunction but not damages alone (reckless-driver example)
+• Congress may elevate real harms but cannot enact injury into existence; Maine/Hawaii hypo; Article II rationale
+• Thomas dissent: private rights need no actual damage, "pyrrhic victory" sends suits to state court; Kagan: "judicial aggrandizement"</t>
+        </is>
+      </c>
+      <c r="K44" s="99" t="inlineStr">
+        <is>
+          <t>Limits Congress's power to create standing (contrast Akins); ties to separation of powers and to Lyons's relief-by-relief analysis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="105" t="inlineStr">
+        <is>
+          <t>Standing</t>
+        </is>
+      </c>
+      <c r="B45" s="99" t="n"/>
+      <c r="C45" s="99" t="n">
+        <v>3</v>
+      </c>
+      <c r="D45" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E45" s="100" t="inlineStr">
+        <is>
+          <t>SFFA v. Harvard (2023) (standing)</t>
+        </is>
+      </c>
+      <c r="F45" s="99" t="inlineStr">
+        <is>
+          <t>Standing: organizational</t>
+        </is>
+      </c>
+      <c r="G45" s="99" t="inlineStr">
+        <is>
+          <t>SFFA, a membership nonprofit, sued Harvard and UNC over race-based admissions; UNC said SFFA was not a genuine membership organization.</t>
+        </is>
+      </c>
+      <c r="H45" s="99" t="inlineStr">
+        <is>
+          <t>SFFA had organizational standing; UNC's standing objection was rejected.</t>
+        </is>
+      </c>
+      <c r="I45" s="99" t="inlineStr">
+        <is>
+          <t>Hunt test for representational standing: members would have standing; interests germane to the organization's purpose; no need for individual members' participation.</t>
+        </is>
+      </c>
+      <c r="J45" s="99" t="inlineStr">
+        <is>
+          <t>• Hunt's "indicia of membership" applies to memberless entities, not voluntary groups with identified members
+• Identified members represented in good faith need no further scrutiny of how the group operates
+• 47 members at filing; four rejected applicants filed declarations</t>
+        </is>
+      </c>
+      <c r="K45" s="99" t="inlineStr">
+        <is>
+          <t>Use for associational standing; contrast Sierra Club, where the group failed to allege members' injury.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="105" t="inlineStr">
+        <is>
+          <t>Standing</t>
+        </is>
+      </c>
+      <c r="B46" s="99" t="inlineStr">
+        <is>
+          <t>Political question</t>
+        </is>
+      </c>
+      <c r="C46" s="99" t="n">
+        <v>4</v>
+      </c>
+      <c r="D46" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E46" s="100" t="inlineStr">
+        <is>
+          <t>Frederick v. Biden (S.D.N.Y. 2023)</t>
+        </is>
+      </c>
+      <c r="F46" s="99" t="inlineStr">
+        <is>
+          <t>Standing; political question</t>
+        </is>
+      </c>
+      <c r="G46" s="99" t="inlineStr">
+        <is>
+          <t>A pro se plaintiff asked the court to have the House impeach and jail President Biden, 'put [Donald] Trump back in office,' and claw back spending he disagreed with.</t>
+        </is>
+      </c>
+      <c r="H46" s="99" t="inlineStr">
+        <is>
+          <t>Dismissed for lack of subject matter jurisdiction because the plaintiff lacked standing and the claims raised political questions; leave to amend was denied as futile.</t>
+        </is>
+      </c>
+      <c r="I46" s="99" t="inlineStr">
+        <is>
+          <t>Disagreement with an official's policies is a generalized grievance, not a concrete and particularized injury (TransUnion's three elements). Policy choices committed to Congress or the Executive are political questions (Japan Whaling).</t>
+        </is>
+      </c>
+      <c r="J46" s="99" t="inlineStr">
+        <is>
+          <t>• Two independent grounds: no standing AND political question
+• Standing focuses on the party; the political question doctrine focuses on the issue (DaCosta v. Laird)
+• Both doctrines come from Article III's case-or-controversy language</t>
+        </is>
+      </c>
+      <c r="K46" s="99" t="inlineStr">
+        <is>
+          <t>A clean modern example of both justiciability doctrines working together. For a client hypo about forcing an impeachment, cite it for dismissal on both grounds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="105" t="inlineStr">
+        <is>
+          <t>Standing</t>
+        </is>
+      </c>
+      <c r="B47" s="99" t="n"/>
+      <c r="C47" s="99" t="n">
+        <v>3</v>
+      </c>
+      <c r="D47" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E47" s="100" t="inlineStr">
+        <is>
+          <t>Douglas v. National Park Service (D.D.C. 2026)</t>
+        </is>
+      </c>
+      <c r="F47" s="99" t="inlineStr">
+        <is>
+          <t>Standing: aesthetic, procedural</t>
+        </is>
+      </c>
+      <c r="G47" s="99" t="inlineStr">
+        <is>
+          <t>Two plaintiffs sought a TRO against a UFC event on the White House South Lawn and Lincoln Memorial, alleging aesthetic, dignitary, physical and NEPA injuries.</t>
+        </is>
+      </c>
+      <c r="H47" s="99" t="inlineStr">
+        <is>
+          <t>TRO denied: plaintiffs showed neither a substantial likelihood of standing nor irreparable harm.</t>
+        </is>
+      </c>
+      <c r="I47" s="99" t="inlineStr">
+        <is>
+          <t>Aesthetic injury requires concrete plans to be directly affected and must be certainly impending (Clapper); a procedural right "in vacuo" is not enough.</t>
+        </is>
+      </c>
+      <c r="J47" s="99" t="inlineStr">
+        <is>
+          <t>• Romano: only a "serendipitous rideshare trip" would bring him there
+• Douglas came to protest, not for aesthetics; general emotional harm is not enough
+• Knee-pain theory waived, not definable, and easily alleviated
+• Plaintiffs must show a "substantial likelihood" of standing for a TRO</t>
+        </is>
+      </c>
+      <c r="K47" s="99" t="inlineStr">
+        <is>
+          <t>Applies Sierra Club, Lujan and Clapper to current facts; good model for an aesthetic-injury hypo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="105" t="inlineStr">
+        <is>
+          <t>Standing</t>
+        </is>
+      </c>
+      <c r="B48" s="103" t="n"/>
+      <c r="C48" s="103" t="n">
+        <v>2</v>
+      </c>
+      <c r="D48" s="103" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+      <c r="E48" s="104" t="inlineStr">
+        <is>
+          <t>Davis, Administrative Law Treatise (1983)</t>
+        </is>
+      </c>
+      <c r="F48" s="103" t="inlineStr">
+        <is>
+          <t>Critique of standing law</t>
+        </is>
+      </c>
+      <c r="G48" s="103" t="inlineStr">
+        <is>
+          <t>A treatise author's assessment of standing doctrine.</t>
+        </is>
+      </c>
+      <c r="H48" s="103" t="inlineStr">
+        <is>
+          <t>Standing law's "main failure" is "the inconsistency, unreliability, and inordinate complexity," not that courts open the doors too much or too little.</t>
+        </is>
+      </c>
+      <c r="I48" s="103" t="inlineStr">
+        <is>
+          <t>Professor adds Thole v. U.S. Bank (2020): "Courts sometimes make standing law more complicated than it needs to be." ("Any court in particular?")</t>
+        </is>
+      </c>
+      <c r="J48" s="103" t="inlineStr">
+        <is>
+          <t>• The criticism is inconsistency and complexity, not too much or too little access</t>
+        </is>
+      </c>
+      <c r="K48" s="103" t="inlineStr">
+        <is>
+          <t>Use as a critique in a standing essay (with Douglas in Flast and Powell in Richardson).</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="105" t="inlineStr">
+        <is>
+          <t>Standing</t>
+        </is>
+      </c>
+      <c r="B49" s="103" t="n"/>
+      <c r="C49" s="103" t="n">
+        <v>3</v>
+      </c>
+      <c r="D49" s="103" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+      <c r="E49" s="104" t="inlineStr">
+        <is>
+          <t>TransUnion v. Ramirez: oral argument (2021)</t>
+        </is>
+      </c>
+      <c r="F49" s="103" t="inlineStr">
+        <is>
+          <t>Standing: concreteness</t>
+        </is>
+      </c>
+      <c r="G49" s="103" t="inlineStr">
+        <is>
+          <t>Transcript of the Supreme Court argument.</t>
+        </is>
+      </c>
+      <c r="H49" s="103" t="inlineStr">
+        <is>
+          <t>Previews the concreteness debate the Court decided.</t>
+        </is>
+      </c>
+      <c r="I49" s="103" t="inlineStr">
+        <is>
+          <t>Issacharoff (for Ramirez): an OFAC label is "the scarlet letter of our time"; closest common-law analogue is defamation per se. Clement (TransUnion) pressed the "desk drawer" point that undisclosed files harm no one.</t>
+        </is>
+      </c>
+      <c r="J49" s="103" t="inlineStr">
+        <is>
+          <t>• Alito asked for the closest common-law analogue to suing over an unknown past risk
+• His 1786 hypothetical: an unpublished defamatory article can't support suit, like files never disseminated</t>
+        </is>
+      </c>
+      <c r="K49" s="103" t="inlineStr">
+        <is>
+          <t>Shows why dissemination became the dividing line in the decision (1,853 vs. 6,332).</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="105" t="inlineStr">
+        <is>
+          <t>Standing</t>
+        </is>
+      </c>
+      <c r="B50" s="103" t="n"/>
+      <c r="C50" s="103" t="n">
+        <v>2</v>
+      </c>
+      <c r="D50" s="103" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+      <c r="E50" s="104" t="inlineStr">
+        <is>
+          <t>Moore's Federal Practice: standing sections</t>
+        </is>
+      </c>
+      <c r="F50" s="103" t="inlineStr">
+        <is>
+          <t>Standing treatise</t>
+        </is>
+      </c>
+      <c r="G50" s="103" t="inlineStr">
+        <is>
+          <t>Assigned treatise sections giving an overview of standing.</t>
+        </is>
+      </c>
+      <c r="H50" s="103" t="inlineStr">
+        <is>
+          <t>Standing focuses on WHO may bring suit (§ 101.20).</t>
+        </is>
+      </c>
+      <c r="I50" s="103" t="inlineStr">
+        <is>
+          <t>Standing has constitutional and prudential components (§ 101.22); only one plaintiff needs standing (§ 101.23).</t>
+        </is>
+      </c>
+      <c r="J50" s="103" t="inlineStr">
+        <is>
+          <t>• "Only one plaintiff need have standing"
+• Assigned partly to teach how to use a treatise</t>
+        </is>
+      </c>
+      <c r="K50" s="103" t="inlineStr">
+        <is>
+          <t>Cite for the one-plaintiff rule when multiple plaintiffs sue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="105" t="inlineStr">
+        <is>
+          <t>Standing</t>
+        </is>
+      </c>
+      <c r="B51" s="103" t="n"/>
+      <c r="C51" s="103" t="n">
+        <v>3</v>
+      </c>
+      <c r="D51" s="103" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+      <c r="E51" s="104" t="inlineStr">
+        <is>
+          <t>FISC website: About the Foreign Intelligence Surveillance Court</t>
+        </is>
+      </c>
+      <c r="F51" s="103" t="inlineStr">
+        <is>
+          <t>Background for Clapper</t>
+        </is>
+      </c>
+      <c r="G51" s="103" t="inlineStr">
+        <is>
+          <t>The court's own description of itself.</t>
+        </is>
+      </c>
+      <c r="H51" s="103" t="inlineStr">
+        <is>
+          <t>"The FISC is an Article III federal court."</t>
+        </is>
+      </c>
+      <c r="I51" s="103" t="inlineStr">
+        <is>
+          <t>Created by FISA (1978) to review government applications for foreign-intelligence surveillance; 11 district judges designated by the Chief Justice for up to seven years, from at least seven circuits, three living near D.C.</t>
+        </is>
+      </c>
+      <c r="J51" s="103" t="inlineStr">
+        <is>
+          <t>• It is an Article III court
+• Its judges are designated by the Chief Justice</t>
+        </is>
+      </c>
+      <c r="K51" s="103" t="inlineStr">
+        <is>
+          <t>Background for Clapper: the FISC's secret approval process is part of why the plaintiffs could only speculate about surveillance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="105" t="inlineStr">
+        <is>
+          <t>Standing</t>
+        </is>
+      </c>
+      <c r="B52" s="103" t="inlineStr">
+        <is>
+          <t>Judicial review &amp; federal jurisdiction</t>
+        </is>
+      </c>
+      <c r="C52" s="103" t="n">
+        <v>4</v>
+      </c>
+      <c r="D52" s="103" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+      <c r="E52" s="104" t="inlineStr">
+        <is>
+          <t>Article III, Section 2 (text)</t>
+        </is>
+      </c>
+      <c r="F52" s="103" t="inlineStr">
+        <is>
+          <t>Judicial power: text</t>
+        </is>
+      </c>
+      <c r="G52" s="103" t="inlineStr">
+        <is>
+          <t>The constitutional text listing the cases and controversies federal courts may hear.</t>
+        </is>
+      </c>
+      <c r="H52" s="103" t="inlineStr">
+        <is>
+          <t>Extends the judicial power to listed controversies, including those "between a State and Citizens of another State."</t>
+        </is>
+      </c>
+      <c r="I52" s="103" t="inlineStr">
+        <is>
+          <t>Gives the Supreme Court original jurisdiction in cases involving States and ambassadors, and appellate jurisdiction "with such Exceptions, and under such Regulations as the Congress shall make."</t>
+        </is>
+      </c>
+      <c r="J52" s="103" t="inlineStr">
+        <is>
+          <t>• The state-citizen clause is what Chisholm applied and the Eleventh Amendment cut back
+• The Exceptions Clause is the basis for McCardle
+• Marbury: Congress can't add to original jurisdiction</t>
+        </is>
+      </c>
+      <c r="K52" s="103" t="inlineStr">
+        <is>
+          <t>Anchor text for Chisholm, Hans, McCardle and Marbury.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="105" t="inlineStr">
+        <is>
+          <t>Ripeness</t>
+        </is>
+      </c>
+      <c r="B53" s="99" t="n"/>
+      <c r="C53" s="99" t="n">
+        <v>3</v>
+      </c>
+      <c r="D53" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E53" s="100" t="inlineStr">
+        <is>
+          <t>Texas v. United States (1998)</t>
+        </is>
+      </c>
+      <c r="F53" s="99" t="inlineStr">
+        <is>
+          <t>Ripeness</t>
+        </is>
+      </c>
+      <c r="G53" s="99" t="inlineStr">
+        <is>
+          <t>Texas sought a declaration that Voting Rights Act preclearance did not apply to state sanctions (appointing a master or management team) for failing school districts.</t>
+        </is>
+      </c>
+      <c r="H53" s="99" t="inlineStr">
+        <is>
+          <t>Not ripe; the Court agreed with the three-judge District Court.</t>
+        </is>
+      </c>
+      <c r="I53" s="99" t="inlineStr">
+        <is>
+          <t>A claim resting on "contingent future events that may not occur as anticipated, or indeed may not occur at all" is unripe. Abbott Labs test: fitness of the issues and hardship of withholding review.</t>
+        </is>
+      </c>
+      <c r="J53" s="99" t="inlineStr">
+        <is>
+          <t>• Not fit: no district identified, better decided in a particular application, no state-court interpretation
+• No hardship: Texas need not do or refrain from anything; it can just go ahead and appoint
+• "Threat to federalism" is an abstraction; contrast Abbott Labs' direct day-to-day effect</t>
+        </is>
+      </c>
+      <c r="K53" s="99" t="inlineStr">
+        <is>
+          <t>Core ripeness case; pair with SBA List fn. 5 on the overlap of ripeness and standing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="105" t="inlineStr">
+        <is>
+          <t>Ripeness</t>
+        </is>
+      </c>
+      <c r="B54" s="99" t="inlineStr">
+        <is>
+          <t>Standing</t>
+        </is>
+      </c>
+      <c r="C54" s="99" t="n">
+        <v>3</v>
+      </c>
+      <c r="D54" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E54" s="100" t="inlineStr">
+        <is>
+          <t>Susan B. Anthony List v. Driehaus (2014)</t>
+        </is>
+      </c>
+      <c r="F54" s="99" t="inlineStr">
+        <is>
+          <t>Standing: pre-enforcement</t>
+        </is>
+      </c>
+      <c r="G54" s="99" t="inlineStr">
+        <is>
+          <t>The excerpt gives no facts; it addresses standing for a pre-enforcement challenge.</t>
+        </is>
+      </c>
+      <c r="H54" s="99" t="inlineStr">
+        <is>
+          <t>Petitioners showed injury in fact; reversed and remanded for the remaining standing elements.</t>
+        </is>
+      </c>
+      <c r="I54" s="99" t="inlineStr">
+        <is>
+          <t>Pre-enforcement injury exists where the plaintiff intends conduct arguably affected with a constitutional interest, proscribed by statute, with a credible threat of prosecution (Babbitt). Future injury suffices if "certainly impending" or a "substantial risk."</t>
+        </is>
+      </c>
+      <c r="J54" s="99" t="inlineStr">
+        <is>
+          <t>• No need to be arrested or prosecuted first (Steffel)
+• Credible threat: past enforcement against others and refusal to disavow (Holder); well-founded fear plus costly compliance (American Booksellers)
+• Fn. 5: standing and ripeness boil down to the same question</t>
+        </is>
+      </c>
+      <c r="K54" s="99" t="inlineStr">
+        <is>
+          <t>Use for pre-enforcement challenges; bridges standing (Clapper) and ripeness (Texas v. United States).</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="105" t="inlineStr">
+        <is>
+          <t>Ripeness</t>
+        </is>
+      </c>
+      <c r="B55" s="103" t="n"/>
+      <c r="C55" s="103" t="n">
+        <v>3</v>
+      </c>
+      <c r="D55" s="103" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+      <c r="E55" s="104" t="inlineStr">
+        <is>
+          <t>Moore's Federal Practice: ripeness sections</t>
+        </is>
+      </c>
+      <c r="F55" s="103" t="inlineStr">
+        <is>
+          <t>Ripeness treatise</t>
+        </is>
+      </c>
+      <c r="G55" s="103" t="inlineStr">
+        <is>
+          <t>Assigned sections on the nature of ripeness, its relation to standing, and its criteria.</t>
+        </is>
+      </c>
+      <c r="H55" s="103" t="inlineStr">
+        <is>
+          <t>"Fitness" and "hardship" are the primary criteria (§ 101.76).</t>
+        </is>
+      </c>
+      <c r="I55" s="103" t="inlineStr">
+        <is>
+          <t>Ripeness and standing overlap (§ 101.71); see Texas v. United States for the application.</t>
+        </is>
+      </c>
+      <c r="J55" s="103" t="inlineStr">
+        <is>
+          <t>• Fitness and hardship are the two criteria
+• Ripeness and standing often "boil down to the same question" (SBA List fn. 5)</t>
+        </is>
+      </c>
+      <c r="K55" s="103" t="inlineStr">
+        <is>
+          <t>Pair with Texas v. United States and Abbott Labs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="105" t="inlineStr">
+        <is>
+          <t>Mootness</t>
+        </is>
+      </c>
+      <c r="B56" s="99" t="n"/>
+      <c r="C56" s="99" t="n">
+        <v>3</v>
+      </c>
+      <c r="D56" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E56" s="100" t="inlineStr">
+        <is>
+          <t>Roe v. Wade (1973) (mootness)</t>
+        </is>
+      </c>
+      <c r="F56" s="99" t="inlineStr">
+        <is>
+          <t>Mootness: capable of repetition</t>
+        </is>
+      </c>
+      <c r="G56" s="99" t="inlineStr">
+        <is>
+          <t>Roe, pregnant when she sued in 1970, was no longer shown pregnant by the time of judgment and appeal.</t>
+        </is>
+      </c>
+      <c r="H56" s="99" t="inlineStr">
+        <is>
+          <t>Not moot: pregnancy is "capable of repetition, yet evading review."</t>
+        </is>
+      </c>
+      <c r="I56" s="99" t="inlineStr">
+        <is>
+          <t>An actual controversy must exist at every stage of review, but an exception applies to short, recurring injuries.</t>
+        </is>
+      </c>
+      <c r="J56" s="99" t="inlineStr">
+        <is>
+          <t>• 266-day gestation is shorter than appellate review; pregnancy can recur
+• "Our law should not be that rigid"
+• Merits (abortion right) are not part of Con Law I</t>
+        </is>
+      </c>
+      <c r="K56" s="99" t="inlineStr">
+        <is>
+          <t>Classic capable-of-repetition example; Klaassen shows the exception's limits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="105" t="inlineStr">
+        <is>
+          <t>Mootness</t>
+        </is>
+      </c>
+      <c r="B57" s="99" t="n"/>
+      <c r="C57" s="99" t="n">
+        <v>3</v>
+      </c>
+      <c r="D57" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E57" s="100" t="inlineStr">
+        <is>
+          <t>City of Mesquite v. Aladdin's Castle (1981)</t>
+        </is>
+      </c>
+      <c r="F57" s="99" t="inlineStr">
+        <is>
+          <t>Mootness: voluntary cessation</t>
+        </is>
+      </c>
+      <c r="G57" s="99" t="inlineStr">
+        <is>
+          <t>While the case was on appeal, Mesquite deleted the challenged "connections with criminal elements" licensing language; it had earlier reenacted an age rule after losing.</t>
+        </is>
+      </c>
+      <c r="H57" s="99" t="inlineStr">
+        <is>
+          <t>Not moot; the Court reached the vagueness merits.</t>
+        </is>
+      </c>
+      <c r="I57" s="99" t="inlineStr">
+        <is>
+          <t>Voluntary cessation does not deprive a court of power to decide; a case is moot only if it is "absolutely clear" the conduct could not reasonably be expected to recur.</t>
+        </is>
+      </c>
+      <c r="J57" s="99" t="inlineStr">
+        <is>
+          <t>• City could reenact if the judgment were vacated and said so at oral argument
+• Test is "stringent"; otherwise defendants would be "free to return to his old ways"
+• If a case becomes moot on appeal, the judgment below is normally vacated</t>
+        </is>
+      </c>
+      <c r="K57" s="99" t="inlineStr">
+        <is>
+          <t>Leading voluntary-cessation case; use whenever a government repeals a challenged rule during litigation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="105" t="inlineStr">
+        <is>
+          <t>Mootness</t>
+        </is>
+      </c>
+      <c r="B58" s="99" t="n"/>
+      <c r="C58" s="99" t="n">
+        <v>3</v>
+      </c>
+      <c r="D58" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E58" s="100" t="inlineStr">
+        <is>
+          <t>Klaassen v. Trustees of Indiana Univ. (7th Cir. 2022)</t>
+        </is>
+      </c>
+      <c r="F58" s="99" t="inlineStr">
+        <is>
+          <t>Mootness: limits of exception</t>
+        </is>
+      </c>
+      <c r="G58" s="99" t="inlineStr">
+        <is>
+          <t>Students challenged Indiana University's COVID-19 vaccine requirement; the only plaintiff without a religious exemption withdrew with no plans to return.</t>
+        </is>
+      </c>
+      <c r="H58" s="99" t="inlineStr">
+        <is>
+          <t>Moot; judgment vacated and remanded with instructions to dismiss.</t>
+        </is>
+      </c>
+      <c r="I58" s="99" t="inlineStr">
+        <is>
+          <t>Capable-of-repetition-yet-evading-review applies only if the dispute can recur between the same parties and is too short-lived for review.</t>
+        </is>
+      </c>
+      <c r="J58" s="99" t="inlineStr">
+        <is>
+          <t>• Two reasons the exception failed: no recurrence for these plaintiffs; policy not evanescent (four-year enrollment)
+• Abandoned mask-and-test claim could not be revived post-argument
+• "The only plaintiff with standing withdrew from the University"</t>
+        </is>
+      </c>
+      <c r="K58" s="99" t="inlineStr">
+        <is>
+          <t>Contrast with Roe: the exception needs both a short duration and recurrence for the same plaintiff.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="105" t="inlineStr">
+        <is>
+          <t>Political question</t>
+        </is>
+      </c>
+      <c r="B59" s="99" t="n"/>
+      <c r="C59" s="99" t="n">
+        <v>4</v>
+      </c>
+      <c r="D59" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E59" s="100" t="inlineStr">
+        <is>
+          <t>Baker v. Carr (1962)</t>
+        </is>
+      </c>
+      <c r="F59" s="99" t="inlineStr">
+        <is>
+          <t>Political question doctrine</t>
+        </is>
+      </c>
+      <c r="G59" s="99" t="inlineStr">
+        <is>
+          <t>The reader excerpt omits the facts and gives only Justice Brennan's statement of the political question doctrine.</t>
+        </is>
+      </c>
+      <c r="H59" s="99" t="inlineStr">
+        <is>
+          <t>A case should be dismissed as a political question only if one of six formulations is 'inextricable from the case at bar.'</t>
+        </is>
+      </c>
+      <c r="I59" s="99" t="inlineStr">
+        <is>
+          <t>Six formulations: (1) a textually demonstrable commitment of the issue to a coordinate political department; (2) a lack of judicially discoverable and manageable standards; (3) the impossibility of deciding without an initial policy determination clearly for nonjudicial discretion; (4) the impossibility of independent resolution without expressing lack of respect due coordinate branches; (5) an unusual need for unquestioning adherence to a political decision already made; (6) the potential embarrassment of multifarious pronouncements by various departments on one question. Nonjusticiability is primarily a function of separation of powers.</t>
+        </is>
+      </c>
+      <c r="J59" s="99" t="inlineStr">
+        <is>
+          <t>• The doctrine concerns 'political questions,' not 'political cases': courts cannot refuse a bona fide controversy over whether 'political' action exceeds constitutional authority
+• Requires 'discriminating inquiry into the precise facts and posture' of each case, not 'semantic cataloguing'
+• A dispute between coequal branches with resources to protect themselves is NOT one of Baker's six (that is Rehnquist in Goldwater)
+• Builds on Coleman v. Miller's two 'dominant considerations': finality of political action and lack of judicial criteria</t>
+        </is>
+      </c>
+      <c r="K59" s="99" t="inlineStr">
+        <is>
+          <t>Baker is the framework for every political question answer: run the facts through the formulations, leading with the first two. Counterpoint: the Reader Comment's tests-versus-factors debate and Powell's three-question restatement in Goldwater.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="105" t="inlineStr">
+        <is>
+          <t>Political question</t>
+        </is>
+      </c>
+      <c r="B60" s="99" t="inlineStr">
+        <is>
+          <t>Treaties &amp; executive agreements</t>
+        </is>
+      </c>
+      <c r="C60" s="99" t="n">
+        <v>4</v>
+      </c>
+      <c r="D60" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E60" s="100" t="inlineStr">
+        <is>
+          <t>Goldwater v. Carter (D.C. Cir. en banc 1979; U.S. 1979)</t>
+        </is>
+      </c>
+      <c r="F60" s="99" t="inlineStr">
+        <is>
+          <t>Political question: foreign affairs</t>
+        </is>
+      </c>
+      <c r="G60" s="99" t="inlineStr">
+        <is>
+          <t>President Carter recognized the People's Republic of China and gave one-year notice terminating the Mutual Defense Treaty with Taiwan under its termination clause, without Senate or congressional consent. Senator Goldwater and other legislators sued.</t>
+        </is>
+      </c>
+      <c r="H60" s="99" t="inlineStr">
+        <is>
+          <t>The D.C. Circuit en banc upheld the President's notice on the merits; the Supreme Court, with no majority opinion, vacated and remanded with directions to dismiss the complaint.</t>
+        </is>
+      </c>
+      <c r="I60" s="99" t="inlineStr">
+        <is>
+          <t>No single rationale controls. Rehnquist (four Justices): a nonjusticiable political question because the Constitution is silent on treaty termination and foreign relations are involved. Powell: not ripe until each branch takes official action and reaches a 'constitutional impasse.'</t>
+        </is>
+      </c>
+      <c r="J60" s="99" t="inlineStr">
+        <is>
+          <t>• D.C. Cir.: the treaty's termination clause was 'an overarching factor' and the President's authority 'at its zenith'; MacKinnon would find the case justiciable but deny the President sole power
+• Rehnquist analogized Coleman v. Miller (Art. V silent on rejection), distinguished Youngstown (private litigants, domestic impact), and vacated so the ruling would not 'spawn any legal consequences' (Munsingwear)
+• Powell restated Baker as three questions (text, judicial expertise, prudence); Congress had taken no official action; his hypo: a President putting a Senate-rejected treaty into effect is plainly decidable
+• Brennan would affirm on the recognition power: which branch holds a power is a legal question for courts; reader asks 'What is the controlling opinion?' Answer: none</t>
+        </is>
+      </c>
+      <c r="K60" s="99" t="inlineStr">
+        <is>
+          <t>Use Goldwater to contrast political question (Rehnquist) with ripeness (Powell). For a legislator suit where Congress has not voted, Powell's approach says dismiss as unripe.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="105" t="inlineStr">
+        <is>
+          <t>Political question</t>
+        </is>
+      </c>
+      <c r="B61" s="99" t="n"/>
+      <c r="C61" s="99" t="n">
+        <v>4</v>
+      </c>
+      <c r="D61" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E61" s="100" t="inlineStr">
+        <is>
+          <t>Nixon v. United States (1993)</t>
+        </is>
+      </c>
+      <c r="F61" s="99" t="inlineStr">
+        <is>
+          <t>Political question: impeachment</t>
+        </is>
+      </c>
+      <c r="G61" s="99" t="inlineStr">
+        <is>
+          <t>Federal judge Walter Nixon was impeached and convicted after a Senate committee under Rule XI heard the evidence and reported a transcript to the full Senate. He sued, claiming he was not 'tried' by the full Senate.</t>
+        </is>
+      </c>
+      <c r="H61" s="99" t="inlineStr">
+        <is>
+          <t>Nixon's challenge to Rule XI under the Impeachment Trial Clause is a nonjusticiable political question.</t>
+        </is>
+      </c>
+      <c r="I61" s="99" t="inlineStr">
+        <is>
+          <t>Textual commitment and lack of manageable standards work together: 'sole Power to try' commits impeachment trials to the Senate alone, and 'try' gives no judicially manageable standard. Courts still review action that crosses 'identifiable textual limits' (oath, two-thirds vote, Chief Justice presiding when the President is tried).</t>
+        </is>
+      </c>
+      <c r="J61" s="99" t="inlineStr">
+        <is>
+          <t>• 'Sole' means the Senate acts 'independently and without assistance or interference'; the Committee of Style argument that 'sole' was cosmetic failed
+• No judicial role because impeachment and criminal trial are separate proceedings (bias risk) and impeachment is the Legislature's only check on the Judiciary; Senate abuse is checked by House/Senate division and the two-thirds rule
+• Pardon clause answer: a pardon mitigates punishment and does not overturn a conviction
+• White (with Blackmun): justiciable, 'try' is no harder than 'due process,' but the Senate did try Nixon; Souter: nonjusticiable on prudential grounds, but a 'coin toss' or 'bad guy' conviction might warrant review</t>
+        </is>
+      </c>
+      <c r="K61" s="99" t="inlineStr">
+        <is>
+          <t>Nixon is the leading example of Baker factors 1 and 2 applied together. For a hypo, contrast the majority (no review) with White and Souter (review of extreme cases).</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="105" t="inlineStr">
+        <is>
+          <t>Political question</t>
+        </is>
+      </c>
+      <c r="B62" s="99" t="n"/>
+      <c r="C62" s="99" t="n">
+        <v>4</v>
+      </c>
+      <c r="D62" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E62" s="100" t="inlineStr">
+        <is>
+          <t>Vieth v. Jubelirer (2004)</t>
+        </is>
+      </c>
+      <c r="F62" s="99" t="inlineStr">
+        <is>
+          <t>Political question doctrine</t>
+        </is>
+      </c>
+      <c r="G62" s="99" t="inlineStr">
+        <is>
+          <t>The reader excerpt omits the facts and gives only the plurality's discussion of Baker.</t>
+        </is>
+      </c>
+      <c r="H62" s="99" t="inlineStr">
+        <is>
+          <t>The reader excerpt gives no disposition; the plurality relied on Baker's second test, the lack of judicially discoverable and manageable standards.</t>
+        </is>
+      </c>
+      <c r="I62" s="99" t="inlineStr">
+        <is>
+          <t>Baker's six 'independent tests' are 'probably listed in descending order of both importance and certainty,' and the second is valid because 'the judicial Power' is the traditional power of courts, which must act by principled rule.</t>
+        </is>
+      </c>
+      <c r="J62" s="99" t="inlineStr">
+        <is>
+          <t>• Called Baker's list 'tests,' not factors (contrast Sotomayor's 'factors' in Zivotofsky)
+• Legislative law may be 'inconsistent, illogical, and ad hoc'; law from courts 'must be principled, rational, and based upon reasoned distinctions'
+• Plurality opinion only; Kennedy concurred in the judgment and the separate opinions are omitted</t>
+        </is>
+      </c>
+      <c r="K62" s="99" t="inlineStr">
+        <is>
+          <t>Use Vieth to explain why manageable standards matter: judicial legitimacy depends on rules. Pair it with the Reader Comment on tests versus factors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="105" t="inlineStr">
+        <is>
+          <t>Political question</t>
+        </is>
+      </c>
+      <c r="B63" s="99" t="inlineStr">
+        <is>
+          <t>Standing</t>
+        </is>
+      </c>
+      <c r="C63" s="99" t="n">
+        <v>4</v>
+      </c>
+      <c r="D63" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E63" s="100" t="inlineStr">
+        <is>
+          <t>Frederick v. Biden (S.D.N.Y. 2023)</t>
+        </is>
+      </c>
+      <c r="F63" s="99" t="inlineStr">
+        <is>
+          <t>Standing; political question</t>
+        </is>
+      </c>
+      <c r="G63" s="99" t="inlineStr">
+        <is>
+          <t>A pro se plaintiff asked the court to have the House impeach and jail President Biden, 'put [Donald] Trump back in office,' and claw back spending he disagreed with.</t>
+        </is>
+      </c>
+      <c r="H63" s="99" t="inlineStr">
+        <is>
+          <t>Dismissed for lack of subject matter jurisdiction because the plaintiff lacked standing and the claims raised political questions; leave to amend was denied as futile.</t>
+        </is>
+      </c>
+      <c r="I63" s="99" t="inlineStr">
+        <is>
+          <t>Disagreement with an official's policies is a generalized grievance, not a concrete and particularized injury (TransUnion's three elements). Policy choices committed to Congress or the Executive are political questions (Japan Whaling).</t>
+        </is>
+      </c>
+      <c r="J63" s="99" t="inlineStr">
+        <is>
+          <t>• Two independent grounds: no standing AND political question
+• Standing focuses on the party; the political question doctrine focuses on the issue (DaCosta v. Laird)
+• Both doctrines come from Article III's case-or-controversy language</t>
+        </is>
+      </c>
+      <c r="K63" s="99" t="inlineStr">
+        <is>
+          <t>A clean modern example of both justiciability doctrines working together. For a client hypo about forcing an impeachment, cite it for dismissal on both grounds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="105" t="inlineStr">
+        <is>
+          <t>Political question</t>
+        </is>
+      </c>
+      <c r="B64" s="101" t="n"/>
+      <c r="C64" s="101" t="n">
+        <v>4</v>
+      </c>
+      <c r="D64" s="101" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="E64" s="102" t="inlineStr">
+        <is>
+          <t>Reader Comment on Baker (tests vs. factors)</t>
+        </is>
+      </c>
+      <c r="F64" s="101" t="inlineStr">
+        <is>
+          <t>Political question doctrine</t>
+        </is>
+      </c>
+      <c r="G64" s="101" t="inlineStr">
+        <is>
+          <t>A short reader note following Vieth.</t>
+        </is>
+      </c>
+      <c r="H64" s="101" t="inlineStr">
+        <is>
+          <t>Not a decision.</t>
+        </is>
+      </c>
+      <c r="I64" s="101" t="inlineStr">
+        <is>
+          <t>The Vieth plurality calls Baker's list six 'tests'; Sotomayor in Zivotofsky v. Clinton (2012) calls them 'factors.' In practice the Court discusses only the first two (textual commitment; no manageable standards).</t>
+        </is>
+      </c>
+      <c r="J64" s="101" t="inlineStr">
+        <is>
+          <t>• Tests suggest any one is decisive; factors suggest weighing
+• Zivotofsky quotes Nixon quoting Baker for the first two only</t>
+        </is>
+      </c>
+      <c r="K64" s="101" t="inlineStr">
+        <is>
+          <t>Use it to argue the doctrine has narrowed to textual commitment and manageable standards, with the prudential factors (Souter in Nixon) on the margins.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="105" t="inlineStr">
+        <is>
+          <t>Political question</t>
+        </is>
+      </c>
+      <c r="B65" s="103" t="n"/>
+      <c r="C65" s="103" t="n">
+        <v>4</v>
+      </c>
+      <c r="D65" s="103" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+      <c r="E65" s="104" t="inlineStr">
+        <is>
+          <t>Moore's Federal Practice: political question sections</t>
+        </is>
+      </c>
+      <c r="F65" s="103" t="inlineStr">
+        <is>
+          <t>Political question treatise</t>
+        </is>
+      </c>
+      <c r="G65" s="103" t="inlineStr">
+        <is>
+          <t>Assigned sections on the doctrine and Baker's elements.</t>
+        </is>
+      </c>
+      <c r="H65" s="103" t="inlineStr">
+        <is>
+          <t>Not all of Baker's elements carry equal weight.</t>
+        </is>
+      </c>
+      <c r="I65" s="103" t="inlineStr">
+        <is>
+          <t>Covers the nature of the doctrine (§ 101.110), Baker's elements (§ 101.112) and that not all elements are equal (§ 101.114).</t>
+        </is>
+      </c>
+      <c r="J65" s="103" t="inlineStr">
+        <is>
+          <t>• Only the first two Baker factors (textual commitment; no manageable standards) do real work in later cases</t>
+        </is>
+      </c>
+      <c r="K65" s="103" t="inlineStr">
+        <is>
+          <t>Use with the reader comment on Baker (tests vs. factors) and Vieth's "descending order."</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="105" t="inlineStr">
+        <is>
+          <t>Political question</t>
+        </is>
+      </c>
+      <c r="B66" s="103" t="inlineStr">
+        <is>
+          <t>Treaties &amp; executive agreements</t>
+        </is>
+      </c>
+      <c r="C66" s="103" t="n">
+        <v>4</v>
+      </c>
+      <c r="D66" s="103" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+      <c r="E66" s="104" t="inlineStr">
+        <is>
+          <t>Goldwater v. Carter background documents</t>
+        </is>
+      </c>
+      <c r="F66" s="103" t="inlineStr">
+        <is>
+          <t>Treaty termination</t>
+        </is>
+      </c>
+      <c r="G66" s="103" t="inlineStr">
+        <is>
+          <t>President Carter's statements on recognizing the PRC and the Taiwan Relations Act.</t>
+        </is>
+      </c>
+      <c r="H66" s="103" t="inlineStr">
+        <is>
+          <t>On Dec. 15, 1978, the U.S. announced recognition of the PRC as the sole government of China and notice terminating the Mutual Defense Treaty with Taiwan.</t>
+        </is>
+      </c>
+      <c r="I66" s="103" t="inlineStr">
+        <is>
+          <t>The Taiwan Relations Act (1979) kept unofficial relations through the American Institute in Taiwan.</t>
+        </is>
+      </c>
+      <c r="J66" s="103" t="inlineStr">
+        <is>
+          <t>• The treaty was ended by presidential notice under its own termination clause (Article X), which is what the senators challenged</t>
+        </is>
+      </c>
+      <c r="K66" s="103" t="inlineStr">
+        <is>
+          <t>Factual setting for Goldwater's political-question and ripeness opinions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="105" t="inlineStr">
+        <is>
+          <t>State sovereign immunity</t>
+        </is>
+      </c>
+      <c r="B67" s="99" t="n"/>
+      <c r="C67" s="99" t="n">
+        <v>4</v>
+      </c>
+      <c r="D67" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E67" s="100" t="inlineStr">
+        <is>
+          <t>Chisholm v. Georgia (1793)</t>
+        </is>
+      </c>
+      <c r="F67" s="99" t="inlineStr">
+        <is>
+          <t>State sovereign immunity</t>
+        </is>
+      </c>
+      <c r="G67" s="99" t="inlineStr">
+        <is>
+          <t>A South Carolina citizen sued Georgia in assumpsit to collect a debt, invoking the Supreme Court's original jurisdiction. Georgia refused to appear and filed a remonstrance.</t>
+        </is>
+      </c>
+      <c r="H67" s="99" t="inlineStr">
+        <is>
+          <t>A State could be sued in federal court by a citizen of another State; Justice Iredell alone dissented.</t>
+        </is>
+      </c>
+      <c r="I67" s="99" t="inlineStr">
+        <is>
+          <t>The majority read Article III's literal grant over controversies 'between a State and Citizens of another State' to defeat state immunity. The Eleventh Amendment overruled the result, and Hans and Alden treat Iredell's dissent as the original understanding.</t>
+        </is>
+      </c>
+      <c r="J67" s="99" t="inlineStr">
+        <is>
+          <t>• The case began in the Supreme Court under its original jurisdiction, not on appeal
+• Four majority Justices wrote separately on the literal text: Wilson and Jay said immunity clashed with popular sovereignty; Blair and Cushing found a surrender in Art. III
+• Reaction was a 'profound shock'; Georgia's House passed a bill making enforcement a felony punishable by death (Guthrie found no record it became law)
+• Alden: the 'shall not be construed to extend' wording shows Congress overruled Chisholm rather than changed Article III; VOPA: the Amendment's text 'only eliminates the basis for our judgment' in Chisholm</t>
+        </is>
+      </c>
+      <c r="K67" s="99" t="inlineStr">
+        <is>
+          <t>Open any sovereign immunity answer here: text (Chisholm majority) versus structure and history (Iredell, Hans, Alden). Counterpoint: the swift amendment may mean the country 'changed its collective mind' rather than restored an original understanding (Currie, quoted in Alden).</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="105" t="inlineStr">
+        <is>
+          <t>State sovereign immunity</t>
+        </is>
+      </c>
+      <c r="B68" s="99" t="n"/>
+      <c r="C68" s="99" t="n">
+        <v>4</v>
+      </c>
+      <c r="D68" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E68" s="100" t="inlineStr">
+        <is>
+          <t>Hans v. Louisiana (1890)</t>
+        </is>
+      </c>
+      <c r="F68" s="99" t="inlineStr">
+        <is>
+          <t>State sovereign immunity</t>
+        </is>
+      </c>
+      <c r="G68" s="99" t="inlineStr">
+        <is>
+          <t>A Louisiana citizen sued Louisiana in federal court, claiming a state constitutional amendment impaired the obligation of contracts, so the case arose under federal law.</t>
+        </is>
+      </c>
+      <c r="H68" s="99" t="inlineStr">
+        <is>
+          <t>A State cannot be sued in federal court by its own citizen without its consent, even in a federal-question case and even though the Eleventh Amendment's text covers only out-of-state and foreign plaintiffs.</t>
+        </is>
+      </c>
+      <c r="I68" s="99" t="inlineStr">
+        <is>
+          <t>State immunity is not confined to the Eleventh Amendment's text; the Amendment reflects a broader principle that a sovereign is not suable by individuals without consent. A State may waive immunity and set the terms of its consent.</t>
+        </is>
+      </c>
+      <c r="J68" s="99" t="inlineStr">
+        <is>
+          <t>• Rejected the 'anomalous result' that a State could be sued by its own citizens but not by citizens of other States
+• The Amendment 'actually reversed' Chisholm and vindicated Iredell's 'able opinion' over the majority's reliance on the 'letter'
+• Relied on Hamilton (Fed. 81) and on Madison and Marshall at the Virginia convention against Mason and Henry
+• Proviso hypothetical: an amendment expressly allowing own-citizen suits would never have been ratified ('almost an absurdity')</t>
+        </is>
+      </c>
+      <c r="K68" s="99" t="inlineStr">
+        <is>
+          <t>Hans starts the structural immunity line (Hans, Alden, Allen, VOPA): immunity comes from history and the plan of the Constitution, not the Amendment's words. Counterpoint: a textualist reading like the Chisholm majority's.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="105" t="inlineStr">
+        <is>
+          <t>State sovereign immunity</t>
+        </is>
+      </c>
+      <c r="B69" s="99" t="n"/>
+      <c r="C69" s="99" t="n">
+        <v>4</v>
+      </c>
+      <c r="D69" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E69" s="100" t="inlineStr">
+        <is>
+          <t>Ex parte Young (1908)</t>
+        </is>
+      </c>
+      <c r="F69" s="99" t="inlineStr">
+        <is>
+          <t>Sovereign immunity: officer suits</t>
+        </is>
+      </c>
+      <c r="G69" s="99" t="inlineStr">
+        <is>
+          <t>Railroad shareholders won a federal injunction barring Minnesota's Attorney General, Edward Young, from enforcing allegedly confiscatory rate laws backed by huge penalties. Young sued in state court to enforce the rates anyway, was held in contempt, and sought habeas in the Supreme Court.</t>
+        </is>
+      </c>
+      <c r="H69" s="99" t="inlineStr">
+        <is>
+          <t>The federal court had jurisdiction to enjoin the Attorney General from enforcing an unconstitutional state law; the penalty provisions were unconstitutional on their face.</t>
+        </is>
+      </c>
+      <c r="I69" s="99" t="inlineStr">
+        <is>
+          <t>An officer who enforces an unconstitutional state act is 'stripped of his official or representative character,' so a suit to enjoin him is not a suit against the State. The officer must have some connection with enforcing the act; a general duty to enforce state law is enough.</t>
+        </is>
+      </c>
+      <c r="J69" s="99" t="inlineStr">
+        <is>
+          <t>• The injunction runs against the officer only: a federal court may NOT enjoin a state court or a grand jury
+• Disobey-and-defend was inadequate: few agents would risk heavy fines and prison to test the law, and rate questions are too complex for a jury
+• Harlan dissent: Young was sued only as Attorney General to tie the State's hands, so it was really a suit against Minnesota; he asked how an order requiring official action can be a suit against the State but one forbidding it is not
+• Edelman called Young a 'watershed' that let the Civil War Amendments serve 'as a sword'; CRS and VOPA call it a 'fiction'</t>
+        </is>
+      </c>
+      <c r="K69" s="99" t="inlineStr">
+        <is>
+          <t>Young is the main exception to immunity: prospective relief against officers for ongoing violations of federal law. Pair it with its limits (Edelman: no retroactive money; CRS: no state-law claims) and its extension in VOPA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="105" t="inlineStr">
+        <is>
+          <t>State sovereign immunity</t>
+        </is>
+      </c>
+      <c r="B70" s="99" t="n"/>
+      <c r="C70" s="99" t="n">
+        <v>4</v>
+      </c>
+      <c r="D70" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E70" s="100" t="inlineStr">
+        <is>
+          <t>Edelman v. Jordan (1974)</t>
+        </is>
+      </c>
+      <c r="F70" s="99" t="inlineStr">
+        <is>
+          <t>Sovereign immunity: remedies</t>
+        </is>
+      </c>
+      <c r="G70" s="99" t="inlineStr">
+        <is>
+          <t>A class sued Illinois public aid officials in federal court for processing disability benefit applications late, in violation of federal time limits. The district court ordered prospective compliance and payment of benefits wrongfully withheld in the past.</t>
+        </is>
+      </c>
+      <c r="H70" s="99" t="inlineStr">
+        <is>
+          <t>The Eleventh Amendment bars the retroactive award of benefits paid from the state treasury; prospective injunctive relief under Ex parte Young is allowed.</t>
+        </is>
+      </c>
+      <c r="I70" s="99" t="inlineStr">
+        <is>
+          <t>When a suit is in essence for money from the state treasury, the State is the real party in interest even if officials are named. An 'ancillary effect on the state treasury' that comes from complying with a prospective decree is permissible.</t>
+        </is>
+      </c>
+      <c r="J70" s="99" t="inlineStr">
+        <is>
+          <t>• Line drawn between future compliance and 'reparation for the past' (Judge McGowan in Rothstein v. Wyman); the line is not always 'between day and night'
+• No 'constructive consent': joining a federal program is not waiver; waiver needs 'the most express language' or overwhelming implication
+• The State may raise the Eleventh Amendment for the first time on appeal because it 'partakes of the nature of a jurisdictional bar'
+• Disapproved Shapiro v. Thompson and summary affirmances to the extent inconsistent; stare decisis is weaker on constitutional questions</t>
+        </is>
+      </c>
+      <c r="K70" s="99" t="inlineStr">
+        <is>
+          <t>Use Edelman to limit Ex parte Young: prospective relief yes, retroactive money no. It also supplies the strict waiver standard later used in the CRS report and Alden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="105" t="inlineStr">
+        <is>
+          <t>State sovereign immunity</t>
+        </is>
+      </c>
+      <c r="B71" s="99" t="inlineStr">
+        <is>
+          <t>Section 5 enforcement</t>
+        </is>
+      </c>
+      <c r="C71" s="99" t="n">
+        <v>9</v>
+      </c>
+      <c r="D71" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E71" s="100" t="inlineStr">
+        <is>
+          <t>City of Boerne v. Flores (1997)</t>
+        </is>
+      </c>
+      <c r="F71" s="99" t="inlineStr">
+        <is>
+          <t>Section 5 enforcement power</t>
+        </is>
+      </c>
+      <c r="G71" s="99" t="inlineStr">
+        <is>
+          <t>Boerne, Texas, relying on a historic-preservation ordinance, denied the Archbishop a permit to enlarge St. Peter Catholic Church. The Archbishop sued under RFRA, which Congress passed after Employment Division v. Smith to restore the compelling-interest test against every level of government.</t>
+        </is>
+      </c>
+      <c r="H71" s="99" t="inlineStr">
+        <is>
+          <t>RFRA exceeds Congress's power under § 5 of the Fourteenth Amendment as applied to the States because it makes a substantive change in constitutional protections rather than enforcing them.</t>
+        </is>
+      </c>
+      <c r="I71" s="99" t="inlineStr">
+        <is>
+          <t>Congruence and proportionality: "There must be a congruence and proportionality between the injury to be prevented or remedied and the means adopted to that end." Section 5 lets Congress remedy and prevent violations, even by barring some constitutional conduct, but not redefine the right: "Congress does not enforce a constitutional right by changing what the right is."</t>
+        </is>
+      </c>
+      <c r="J71" s="99" t="inlineStr">
+        <is>
+          <t>• Background: Sherbert required a compelling interest for substantial burdens; Smith held "neutral, generally applicable laws may be applied to religious practices" without one, partly because courts cannot judge a belief's centrality; RFRA restored Sherbert and Yoder by statute and added least restrictive means
+• The thin record was not RFRA's "most serious shortcoming"; its sweep was: every government, all laws past and future, no end date, and "the most demanding test known to constitutional law"
+• Contrast the Voting Rights Act measures upheld: targeted regions, discrete laws, bailout, time limits; but termination dates and geographic limits are NOT required
+• The Court interprets the Constitution in cases: "it is this Court's precedent, not RFRA, which must control"; the Civil Rights Cases treat § 5 as corrective, not "general legislation"</t>
+        </is>
+      </c>
+      <c r="K71" s="99" t="inlineStr">
+        <is>
+          <t>The central limit on Congress's § 5 power and a judicial-supremacy statement in the Marbury line; counter with Kennedy's concession that Congress has a duty to interpret the Constitution and gets wide latitude in choosing remedies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="105" t="inlineStr">
+        <is>
+          <t>State sovereign immunity</t>
+        </is>
+      </c>
+      <c r="B72" s="99" t="inlineStr">
+        <is>
+          <t>Tenth Amendment &amp; federalism</t>
+        </is>
+      </c>
+      <c r="C72" s="99" t="n">
+        <v>4</v>
+      </c>
+      <c r="D72" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E72" s="100" t="inlineStr">
+        <is>
+          <t>Alden v. Maine (1999)</t>
+        </is>
+      </c>
+      <c r="F72" s="99" t="inlineStr">
+        <is>
+          <t>State sovereign immunity</t>
+        </is>
+      </c>
+      <c r="G72" s="99" t="inlineStr">
+        <is>
+          <t>Maine probation officers sued the State for FLSA overtime. After Seminole Tribe ended their federal suit, they refiled in Maine's own courts, which dismissed on sovereign immunity.</t>
+        </is>
+      </c>
+      <c r="H72" s="99" t="inlineStr">
+        <is>
+          <t>Congress's Article I powers do not include power to subject nonconsenting States to private damages suits in their own courts, and Maine had not consented.</t>
+        </is>
+      </c>
+      <c r="I72" s="99" t="inlineStr">
+        <is>
+          <t>State immunity is a fundamental aspect of sovereignty retained at ratification, except as altered by the plan of the Convention or certain amendments; the Eleventh Amendment 'confirmed rather than established' it. It does not bar consented suits, suits by the United States or other States, valid Section 5 abrogation, suits against municipalities, Ex parte Young injunctions against officers, or individual-capacity damages against officers.</t>
+        </is>
+      </c>
+      <c r="J72" s="99" t="inlineStr">
+        <is>
+          <t>• 'Eleventh Amendment immunity' is 'something of a misnomer': immunity comes from structure, so it reaches state courts even though the text limits only 'the Judicial power of the United States'
+• Suits by the United States differ because they require 'political responsibility' for each suit; here the U.S. did not send 'even a single attorney to Maine'
+• Neither the Supremacy Clause nor the Necessary and Proper Clause overrides immunity: a law violating state sovereignty is not 'proper'
+• Souter dissent: the immunity rests on bad history and resembles Lochner-era doctrine, 'probably as fleeting'; Torres later narrowed Alden's Article I statement</t>
+        </is>
+      </c>
+      <c r="K72" s="99" t="inlineStr">
+        <is>
+          <t>Alden is the high-water mark of the dignity rationale: 'Congress has vast power but not all power.' Use its list of remaining avenues (U.S. suits, Young, officer damages) for hypos; counterpoint is Torres, which lets Article I war powers override immunity in state court.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="105" t="inlineStr">
+        <is>
+          <t>State sovereign immunity</t>
+        </is>
+      </c>
+      <c r="B73" s="99" t="n"/>
+      <c r="C73" s="99" t="n">
+        <v>5</v>
+      </c>
+      <c r="D73" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E73" s="100" t="inlineStr">
+        <is>
+          <t>Virginia Office for Protection &amp; Advocacy v. Stewart (2011)</t>
+        </is>
+      </c>
+      <c r="F73" s="99" t="inlineStr">
+        <is>
+          <t>Sovereign immunity: Ex parte Young</t>
+        </is>
+      </c>
+      <c r="G73" s="99" t="inlineStr">
+        <is>
+          <t>A Virginia agency created by state law and authorized to sue state officials brought a federal suit for prospective relief against officials of state-run mental hospitals.</t>
+        </is>
+      </c>
+      <c r="H73" s="99" t="inlineStr">
+        <is>
+          <t>Ex parte Young allows the suit; the Eleventh Amendment does not bar an agency of the same State from invoking federal jurisdiction against state officials.</t>
+        </is>
+      </c>
+      <c r="I73" s="99" t="inlineStr">
+        <is>
+          <t>Young rests on the 'fiction' that an official ordered only to stop violating federal law is not the State. It does not apply when the State is the real party in interest, as when the judgment would expend itself on the public treasury or domain.</t>
+        </is>
+      </c>
+      <c r="J73" s="99" t="inlineStr">
+        <is>
+          <t>• The Amendment's text 'only eliminates the basis for our judgment' in Chisholm; since Hans it confirms a structural immunity
+• Virginia's own law created the agency and let it sue, so it proceeds 'on the same terms as any other litigant'
+• Roberts dissent: this had 'never happened before'; Young gave private parties relief, not a forum for disputes between two state actors
+• Restates the defaults: States may waive; Congress may abrogate under Section 5 but not Article I commerce power</t>
+        </is>
+      </c>
+      <c r="K73" s="99" t="inlineStr">
+        <is>
+          <t>VOPA extends Young to an unusual plaintiff while restating its limits. Use it with Edelman to separate permitted prospective relief from barred treasury relief.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="105" t="inlineStr">
+        <is>
+          <t>State sovereign immunity</t>
+        </is>
+      </c>
+      <c r="B74" s="99" t="inlineStr">
+        <is>
+          <t>Section 5 enforcement</t>
+        </is>
+      </c>
+      <c r="C74" s="99" t="n">
+        <v>5</v>
+      </c>
+      <c r="D74" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E74" s="100" t="inlineStr">
+        <is>
+          <t>Allen v. Cooper (2020)</t>
+        </is>
+      </c>
+      <c r="F74" s="99" t="inlineStr">
+        <is>
+          <t>Sovereign immunity: abrogation</t>
+        </is>
+      </c>
+      <c r="G74" s="99" t="inlineStr">
+        <is>
+          <t>A videographer who documented the Blackbeard shipwreck owned by North Carolina sued the State after it posted five of his videos online and used one of his photos in a newsletter, relying on the Copyright Remedy Clarification Act's abrogation of immunity.</t>
+        </is>
+      </c>
+      <c r="H74" s="99" t="inlineStr">
+        <is>
+          <t>The CRCA did not validly abrogate state immunity: the Intellectual Property Clause cannot support abrogation, and Section 5 could not on this legislative record.</t>
+        </is>
+      </c>
+      <c r="I74" s="99" t="inlineStr">
+        <is>
+          <t>Abrogation requires (1) unequivocal statutory language and (2) a valid constitutional authority. Article I generally cannot be used to circumvent state immunity (Seminole Tribe; Florida Prepaid).</t>
+        </is>
+      </c>
+      <c r="J74" s="99" t="inlineStr">
+        <is>
+          <t>• 'Florida Prepaid all but prewrote our decision today'; overruling it needed a 'special justification' that Allen did not offer
+• Katz is 'bankruptcy exceptionalism,' a 'good-for-one-clause-only holding': the Bankruptcy Clause itself abrogated in the plan of the Convention
+• Thomas: no 'special justification' requirement; a 'demonstrably erroneous' precedent must be corrected, but Florida Prepaid was not; Katz is 'not good for even that clause'
+• Clear statement was undisputed; the case turned on the source of power</t>
+        </is>
+      </c>
+      <c r="K74" s="99" t="inlineStr">
+        <is>
+          <t>Allen sets the two-step abrogation test and treats Katz as unique. Counterpoint: Torres and Kagan's concurrence ('PennEast proved me wrong') widened the plan-of-the-Convention route.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="105" t="inlineStr">
+        <is>
+          <t>State sovereign immunity</t>
+        </is>
+      </c>
+      <c r="B75" s="99" t="inlineStr">
+        <is>
+          <t>Section 5 enforcement</t>
+        </is>
+      </c>
+      <c r="C75" s="99" t="n">
+        <v>9</v>
+      </c>
+      <c r="D75" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E75" s="100" t="inlineStr">
+        <is>
+          <t>Allen v. Cooper (2020) (Section 5)</t>
+        </is>
+      </c>
+      <c r="F75" s="99" t="inlineStr">
+        <is>
+          <t>Section 5: abrogation for copyright</t>
+        </is>
+      </c>
+      <c r="G75" s="99" t="inlineStr">
+        <is>
+          <t>Same case as Week 5 (Blackbeard's ship Queen Anne's Revenge; North Carolina posted the videographer's copyrighted footage). Here the reader reprints the Section 5 part: could the Copyright Remedy Clarification Act (CRCA) abrogate state immunity under §5?</t>
+        </is>
+      </c>
+      <c r="H75" s="99" t="inlineStr">
+        <is>
+          <t>No. Under Florida Prepaid, the CRCA fails congruence and proportionality, so it is not valid §5 legislation. Affirmed.</t>
+        </is>
+      </c>
+      <c r="I75" s="99" t="inlineStr">
+        <is>
+          <t>An abrogation is valid under §5 only if it is tailored to remedy or prevent conduct §1 actually forbids. Infringement violates due process only if it is intentional (or reckless) AND the State offers no adequate remedy. The record showed about a dozen possible state infringements, mostly innocent, and nothing on state remedies, while the CRCA covered every infringement suit: "indiscriminate scope" out of proportion to any due process problem.</t>
+        </is>
+      </c>
+      <c r="J75" s="99" t="inlineStr">
+        <is>
+          <t>• §5, unlike almost all of Article I, can abrogate (Fitzpatrick)
+• Negligent acts don't "deprive" property (Daniels)
+• Oman Report: only 12 examples, 2 intentional; Oman said States are "respectful of the copyright law"
+• Florida Prepaid (patents) "all but prewrote" the result
+• Congress may try again with a tailored law and a better record: "bring digital Blackbeards to justice"
+• Thomas concurred in part; Breyer (with Ginsburg) concurred in the judgment (opinions omitted in reader)</t>
+        </is>
+      </c>
+      <c r="K75" s="99" t="inlineStr">
+        <is>
+          <t>Applies Boerne in the immunity setting: map the right (intentional infringement + no state remedy), the record, and the statute's scope. Pairs with the Week 5 Article I holding (Intellectual Property Clause can't abrogate).</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="105" t="inlineStr">
+        <is>
+          <t>State sovereign immunity</t>
+        </is>
+      </c>
+      <c r="B76" s="99" t="n"/>
+      <c r="C76" s="99" t="n">
+        <v>5</v>
+      </c>
+      <c r="D76" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E76" s="100" t="inlineStr">
+        <is>
+          <t>Torres v. Texas Department of Public Safety (2022)</t>
+        </is>
+      </c>
+      <c r="F76" s="99" t="inlineStr">
+        <is>
+          <t>Sovereign immunity: structural waiver</t>
+        </is>
+      </c>
+      <c r="G76" s="99" t="inlineStr">
+        <is>
+          <t>An Army reservist who returned from Iraq with constrictive bronchitis from burn pits sued Texas in state court under USERRA after the State refused to reemploy him in a different role.</t>
+        </is>
+      </c>
+      <c r="H76" s="99" t="inlineStr">
+        <is>
+          <t>States cannot invoke sovereign immunity to block USERRA suits because they agreed in the plan of the Convention that their sovereignty would yield to the federal power to raise and support armies.</t>
+        </is>
+      </c>
+      <c r="I76" s="99" t="inlineStr">
+        <is>
+          <t>Structural waiver applies when the federal power is 'complete in itself, and the States consented to the exercise of that power, in its entirety, in the plan of the Convention' (PennEast). States may be sued by consent, by Section 5 abrogation, or by such structural waiver.</t>
+        </is>
+      </c>
+      <c r="J76" s="99" t="inlineStr">
+        <is>
+          <t>• Recognized structural waivers: suits between States, suits by the U.S., bankruptcy (Katz), eminent domain (PennEast), and now the military powers
+• Distinguished Seminole Tribe and Florida Prepaid: those powers are not denied to the States or essential to the Union's survival
+• Kagan concurring: 'PennEast proved me wrong' about Katz being good for one clause; Thomas dissent: the Court 'brushes aside' Alden while elevating a passing phrase from PennEast
+• State courts may not apply a state immunity statute to block the federal claim (Supremacy Clause; Testa v. Katt)</t>
+        </is>
+      </c>
+      <c r="K76" s="99" t="inlineStr">
+        <is>
+          <t>Torres shows the plan-of-the-Convention exception swallowing part of Alden. Use it against Seminole Tribe and Allen to sort which Article I powers can support private suits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="105" t="inlineStr">
+        <is>
+          <t>State sovereign immunity</t>
+        </is>
+      </c>
+      <c r="B77" s="101" t="inlineStr">
+        <is>
+          <t>Tenth Amendment &amp; federalism</t>
+        </is>
+      </c>
+      <c r="C77" s="101" t="n">
+        <v>4</v>
+      </c>
+      <c r="D77" s="101" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="E77" s="102" t="inlineStr">
+        <is>
+          <t>The Federalist No. 63 (1788)</t>
+        </is>
+      </c>
+      <c r="F77" s="101" t="inlineStr">
+        <is>
+          <t>Senate and state sovereignty</t>
+        </is>
+      </c>
+      <c r="G77" s="101" t="inlineStr">
+        <is>
+          <t>Madison's essay on the Senate.</t>
+        </is>
+      </c>
+      <c r="H77" s="101" t="inlineStr">
+        <is>
+          <t>Not a decision.</t>
+        </is>
+      </c>
+      <c r="I77" s="101" t="inlineStr">
+        <is>
+          <t>Election of senators by state legislatures gives the States an agency in the federal government, 'a convenient link between the two systems.' Equal state votes in the Senate recognize and preserve the States' 'residuary sovereignty.'</t>
+        </is>
+      </c>
+      <c r="J77" s="101" t="inlineStr">
+        <is>
+          <t>• Equal vote is 'at once a constitutional recognition of the portion of sovereignty remaining in the individual states, and an instrument for preserving that residuary sovereignty'
+• The 'diseases' governments are most liable to: 'the facility and excess of law-making'</t>
+        </is>
+      </c>
+      <c r="K77" s="101" t="inlineStr">
+        <is>
+          <t>Use it for the political safeguards of federalism: the States were protected through their role in forming the federal government.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="105" t="inlineStr">
+        <is>
+          <t>State sovereign immunity</t>
+        </is>
+      </c>
+      <c r="B78" s="101" t="n"/>
+      <c r="C78" s="101" t="n">
+        <v>4</v>
+      </c>
+      <c r="D78" s="101" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="E78" s="102" t="inlineStr">
+        <is>
+          <t>The Federalist No. 81 (1788)</t>
+        </is>
+      </c>
+      <c r="F78" s="101" t="inlineStr">
+        <is>
+          <t>State sovereign immunity</t>
+        </is>
+      </c>
+      <c r="G78" s="101" t="inlineStr">
+        <is>
+          <t>Hamilton's essay on the judiciary, including original jurisdiction and suits against States.</t>
+        </is>
+      </c>
+      <c r="H78" s="101" t="inlineStr">
+        <is>
+          <t>Not a decision.</t>
+        </is>
+      </c>
+      <c r="I78" s="101" t="inlineStr">
+        <is>
+          <t>'It is inherent in the nature of sovereignty, not to be amenable to the suit of an individual without its consent.' Unless surrendered in the plan of the Convention, that immunity stays with the States.</t>
+        </is>
+      </c>
+      <c r="J78" s="101" t="inlineStr">
+        <is>
+          <t>• Suits against States for debts would be pointless because recoveries could not be enforced 'without waging war against the contracting state'
+• States get original Supreme Court jurisdiction because it 'would ill suit its dignity to be turned over to an inferior tribunal'
+• Quoted by Hans, Alden and Allen; source of the 'plan of the Convention' idea later used in Katz, PennEast and Torres</t>
+        </is>
+      </c>
+      <c r="K78" s="101" t="inlineStr">
+        <is>
+          <t>The founding text for immunity and its exceptions: cite it for the default rule and for the 'surrender in the plan of the Convention' exception.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="105" t="inlineStr">
+        <is>
+          <t>State sovereign immunity</t>
+        </is>
+      </c>
+      <c r="B79" s="101" t="n"/>
+      <c r="C79" s="101" t="n">
+        <v>4</v>
+      </c>
+      <c r="D79" s="101" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="E79" s="102" t="inlineStr">
+        <is>
+          <t>Guthrie, The Eleventh Article of Amendment (1908)</t>
+        </is>
+      </c>
+      <c r="F79" s="101" t="inlineStr">
+        <is>
+          <t>Eleventh Amendment history</t>
+        </is>
+      </c>
+      <c r="G79" s="101" t="inlineStr">
+        <is>
+          <t>A 1908 Columbia Law Review article tracing state suability from ratification through Chisholm and the Eleventh Amendment.</t>
+        </is>
+      </c>
+      <c r="H79" s="101" t="inlineStr">
+        <is>
+          <t>Not a decision.</t>
+        </is>
+      </c>
+      <c r="I79" s="101" t="inlineStr">
+        <is>
+          <t>Founding views conflicted: Hamilton, Madison and Marshall said States were not suable by individuals, while Pendleton, Henry and Mason (some as an objection) and Wilson and Randolph read Article III to allow it.</t>
+        </is>
+      </c>
+      <c r="J79" s="101" t="inlineStr">
+        <is>
+          <t>• Chisholm was an assumpsit suit for a debt under the Supreme Court's original jurisdiction; Iredell alone dissented
+• The amendment resolution came two days after Chisholm; Adams declared it ratified in 1798
+• Georgia's reported death-penalty statute has no record; probably a bill that passed only the lower house</t>
+        </is>
+      </c>
+      <c r="K79" s="101" t="inlineStr">
+        <is>
+          <t>Use Guthrie as the counterpoint to Hans and Alden: the founding record was divided, not a settled consensus for immunity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="105" t="inlineStr">
+        <is>
+          <t>State sovereign immunity</t>
+        </is>
+      </c>
+      <c r="B80" s="103" t="n"/>
+      <c r="C80" s="103" t="n">
+        <v>4</v>
+      </c>
+      <c r="D80" s="103" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+      <c r="E80" s="104" t="inlineStr">
+        <is>
+          <t>CRS Report R45323: Eleventh Amendment and State Sovereign Immunity (2023)</t>
+        </is>
+      </c>
+      <c r="F80" s="103" t="inlineStr">
+        <is>
+          <t>Sovereign immunity</t>
+        </is>
+      </c>
+      <c r="G80" s="103" t="inlineStr">
+        <is>
+          <t>A CRS summary of state sovereign immunity doctrine.</t>
+        </is>
+      </c>
+      <c r="H80" s="103" t="inlineStr">
+        <is>
+          <t>"Eleventh Amendment immunity" is "something of a misnomer": the immunity neither derives from nor is limited by the Amendment's text.</t>
+        </is>
+      </c>
+      <c r="I80" s="103" t="inlineStr">
+        <is>
+          <t>States may be sued only by (1) waiver/consent, unequivocally expressed (including as a clear condition on federal funds, e.g., IDEA); (2) structural waiver in the plan of the Convention (suits between States or by the U.S.; Bankruptcy, eminent domain, armed forces); (3) abrogation: "unmistakably clear" language plus a valid power, chiefly § 5 of the Fourteenth Amendment, not Article I; and Ex parte Young for prospective relief against officers.</t>
+        </is>
+      </c>
+      <c r="J80" s="103" t="inlineStr">
+        <is>
+          <t>• Two imperatives: the States' dignity and financial solvency
+• Immunity reaches suits by a State's own citizens, suits in state courts, and federal agency adjudication
+• Ex parte Young is "narrow": no damages from the treasury, prospective only</t>
+        </is>
+      </c>
+      <c r="K80" s="103" t="inlineStr">
+        <is>
+          <t>The cleanest summary for a sovereign-immunity essay; pair with Hans, Alden, Allen v. Cooper, Torres, Edelman.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="105" t="inlineStr">
+        <is>
+          <t>State sovereign immunity</t>
+        </is>
+      </c>
+      <c r="B81" s="103" t="n"/>
+      <c r="C81" s="103" t="n">
+        <v>5</v>
+      </c>
+      <c r="D81" s="103" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+      <c r="E81" s="104" t="inlineStr">
+        <is>
+          <t>CALI Assessment: Eleventh Amendment</t>
+        </is>
+      </c>
+      <c r="F81" s="103" t="inlineStr">
+        <is>
+          <t>Sovereign immunity</t>
+        </is>
+      </c>
+      <c r="G81" s="103" t="inlineStr">
+        <is>
+          <t>A self-test on sovereign immunity.</t>
+        </is>
+      </c>
+      <c r="H81" s="103" t="inlineStr">
+        <is>
+          <t>The reader's note asks whether the "correct" answer to Question 4 fits Katz (2006), PennEast (2021) and Torres (2022).</t>
+        </is>
+      </c>
+      <c r="I81" s="103" t="inlineStr">
+        <is>
+          <t>Signals that structural-waiver cases have moved the doctrine since the assessment was written.</t>
+        </is>
+      </c>
+      <c r="J81" s="103" t="inlineStr">
+        <is>
+          <t>• The professor flags that the CALI answer may be outdated after the structural-waiver cases</t>
+        </is>
+      </c>
+      <c r="K81" s="103" t="inlineStr">
+        <is>
+          <t>Use to show awareness that Torres expanded structural waiver.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="105" t="inlineStr">
+        <is>
+          <t>State sovereign immunity</t>
+        </is>
+      </c>
+      <c r="B82" s="103" t="inlineStr">
+        <is>
+          <t>Section 5 enforcement</t>
+        </is>
+      </c>
+      <c r="C82" s="103" t="n">
+        <v>9</v>
+      </c>
+      <c r="D82" s="103" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+      <c r="E82" s="104" t="inlineStr">
+        <is>
+          <t>CRS, Federalism-Based Limitations (R45323): Civil War Amendments / Section 5</t>
+        </is>
+      </c>
+      <c r="F82" s="103" t="inlineStr">
+        <is>
+          <t>Section 5 enforcement: overview</t>
+        </is>
+      </c>
+      <c r="G82" s="103" t="inlineStr">
+        <is>
+          <t>CRS overview of Congress's power to enforce the 13th, 14th and 15th Amendments.</t>
+        </is>
+      </c>
+      <c r="H82" s="103" t="inlineStr">
+        <is>
+          <t>N/A (overview).</t>
+        </is>
+      </c>
+      <c r="I82" s="103" t="inlineStr">
+        <is>
+          <t>Each Civil War Amendment gives Congress power to enforce it 'by appropriate legislation,' including prophylactic laws that bar some constitutional conduct (e.g., 13th: 'badges and incidents of slavery'; 15th: literacy-test bans). Two limits on §5: (1) STATE ACTION only, no purely private conduct (Civil Rights Cases 1883; Morrison); (2) REMEDIAL only: congruence and proportionality (Boerne). Courts apply a 3-step test: identify the right precisely; ask whether Congress found a history and pattern of state violations; compare the law's scope to that record.</t>
+        </is>
+      </c>
+      <c r="J82" s="103" t="inlineStr">
+        <is>
+          <t>• Most Boerne cases involve abrogating state sovereign immunity (Congress usually can't use Article I to abrogate)
+• ADA Title I (employment): no valid abrogation (Garrett: no pattern; disability = rational basis)
+• ADA Title II (courthouse access): valid (Lane: pattern + fundamental right + limited remedy)
+• FMLA family-care leave: valid (sex discrimination gets heightened scrutiny); self-care leave: not
+• More deference for suspect classes/fundamental rights
+• Congruence and proportionality is needed only for PROPHYLACTIC laws; a remedy for actual 14th Amendment violations can abrogate without it
+• Practical advice: build a record; draft narrowly</t>
+        </is>
+      </c>
+      <c r="K82" s="103" t="inlineStr">
+        <is>
+          <t>Use to organize any §5 answer: state action, then congruence and proportionality in three steps, then the type of right (heightened scrutiny vs. rational basis). Links Boerne to Allen v. Cooper and to the Eleventh Amendment unit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="105" t="inlineStr">
+        <is>
+          <t>Commerce Clause</t>
+        </is>
+      </c>
+      <c r="B83" s="99" t="inlineStr">
+        <is>
+          <t>Dormant Commerce Clause</t>
+        </is>
+      </c>
+      <c r="C83" s="99" t="n">
+        <v>5</v>
+      </c>
+      <c r="D83" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E83" s="100" t="inlineStr">
+        <is>
+          <t>Gibbons v. Ogden (1824)</t>
+        </is>
+      </c>
+      <c r="F83" s="99" t="inlineStr">
+        <is>
+          <t>Commerce Clause</t>
+        </is>
+      </c>
+      <c r="G83" s="99" t="inlineStr">
+        <is>
+          <t>New York laws granted an exclusive steamboat privilege, enforced by a New York decree against the appellant, who claimed the laws conflicted with the commerce power and with an act of Congress licensing vessels.</t>
+        </is>
+      </c>
+      <c r="H83" s="99" t="inlineStr">
+        <is>
+          <t>The New York laws, as applied to vessels licensed under the federal act, collide with federal law and must yield under the Supremacy Clause.</t>
+        </is>
+      </c>
+      <c r="I83" s="99" t="inlineStr">
+        <is>
+          <t>Commerce is 'traffic, but it is something more: it is intercourse,' including navigation. 'Among the several States' means 'intermingled with' and reaches commerce that concerns more States than one, but not the 'completely internal commerce of a State.' The power to regulate is 'complete in itself' and limited mainly by political checks.</t>
+        </is>
+      </c>
+      <c r="J83" s="99" t="inlineStr">
+        <is>
+          <t>• Rejected strict construction; 'the enumeration presupposes something not enumerated'
+• Restraints on Congress are political: the people's influence at elections, not courts
+• Marshall saw 'great force' in the exclusive-power argument but did not rest on it; Justice Johnson concurred on the ground that the commerce power is exclusive
+• Licensed steamboats can no more be restrained 'than if they were wafted on their voyage by the winds'</t>
+        </is>
+      </c>
+      <c r="K83" s="99" t="inlineStr">
+        <is>
+          <t>Gibbons is the broad starting point that Wickard says was 'restored' and Lopez cites for limits ('the enumeration presupposes something not enumerated'). Use it both ways.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="105" t="inlineStr">
+        <is>
+          <t>Commerce Clause</t>
+        </is>
+      </c>
+      <c r="B84" s="99" t="inlineStr">
+        <is>
+          <t>Major questions &amp; nondelegation</t>
+        </is>
+      </c>
+      <c r="C84" s="99" t="n">
+        <v>5</v>
+      </c>
+      <c r="D84" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E84" s="100" t="inlineStr">
+        <is>
+          <t>A. L. A. Schechter Poultry Corp. v. United States (1935)</t>
+        </is>
+      </c>
+      <c r="F84" s="99" t="inlineStr">
+        <is>
+          <t>Commerce Clause: direct/indirect</t>
+        </is>
+      </c>
+      <c r="G84" s="99" t="inlineStr">
+        <is>
+          <t>Brooklyn slaughterhouses that bought poultry shipped from other States and sold only to local retailers were convicted of violating the NIRA Live Poultry Code's wage, hour and trade rules.</t>
+        </is>
+      </c>
+      <c r="H84" s="99" t="inlineStr">
+        <is>
+          <t>The code provisions were invalid as an unconstitutional delegation and as regulation of intrastate transactions that affect interstate commerce only indirectly; convictions reversed.</t>
+        </is>
+      </c>
+      <c r="I84" s="99" t="inlineStr">
+        <is>
+          <t>Congress may reach intrastate activity with direct effects on interstate commerce but not indirect ones; the distinction is 'essential to the maintenance of our constitutional system.' Once goods come to 'permanent rest' in a State, the stream of commerce ends.</t>
+        </is>
+      </c>
+      <c r="J84" s="99" t="inlineStr">
+        <is>
+          <t>• 'Extraordinary conditions do not create or enlarge constitutional power'
+• The government's wage argument 'proves too much': it would reach rents, advertising and every cost
+• Cardozo concurrence: society 'is an elastic medium which transmits all tremors throughout its territory; the only question is of their size'; 'To find immediacy or directness here is to find it almost everywhere'
+• Goods only resting temporarily before moving on stay in the stream; Wickard abandoned the direct/indirect label but did not expressly overrule Schechter</t>
+        </is>
+      </c>
+      <c r="K84" s="99" t="inlineStr">
+        <is>
+          <t>Schechter marks the pre-1937 limit. Contrast Wickard's substantial-effects test; Lopez and Morrison later borrow its worry that federal power could reach everything.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="105" t="inlineStr">
+        <is>
+          <t>Commerce Clause</t>
+        </is>
+      </c>
+      <c r="B85" s="99" t="n"/>
+      <c r="C85" s="99" t="n">
+        <v>5</v>
+      </c>
+      <c r="D85" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E85" s="100" t="inlineStr">
+        <is>
+          <t>Wickard v. Filburn (1942)</t>
+        </is>
+      </c>
+      <c r="F85" s="99" t="inlineStr">
+        <is>
+          <t>Commerce Clause: aggregation</t>
+        </is>
+      </c>
+      <c r="G85" s="99" t="inlineStr">
+        <is>
+          <t>Ohio farmer Filburn grew wheat beyond his AAA quota, using the excess on his farm for feed, flour and seed, and was assessed a marketing penalty.</t>
+        </is>
+      </c>
+      <c r="H85" s="99" t="inlineStr">
+        <is>
+          <t>Congress could apply wheat marketing quotas to wheat grown for consumption on the farm.</t>
+        </is>
+      </c>
+      <c r="I85" s="99" t="inlineStr">
+        <is>
+          <t>Even local, noncommercial activity may be reached if it 'exerts a substantial economic effect on interstate commerce,' whatever it is called. A trivial individual effect counts when, 'taken together with that of many others similarly situated,' it is 'far from trivial.'</t>
+        </is>
+      </c>
+      <c r="J85" s="99" t="inlineStr">
+        <is>
+          <t>• Home-grown wheat 'competes with wheat in commerce': it supplies needs otherwise met by purchases and can flow into the market
+• Direct/indirect and labels like production or consumption are no longer controlling
+• 'With the wisdom, workability, or fairness, of the plan of regulation we have nothing to do'
+• Lopez calls it 'perhaps the most far reaching example' but still economic activity; Raich reaffirmed it</t>
+        </is>
+      </c>
+      <c r="K85" s="99" t="inlineStr">
+        <is>
+          <t>Wickard is the aggregation case: use it for any home-production hypo. Counterpoint: Morrison refuses to aggregate noneconomic violence, and O'Connor in Raich says Wickard did not reach 'the home cook's herb garden.'</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="105" t="inlineStr">
+        <is>
+          <t>Commerce Clause</t>
+        </is>
+      </c>
+      <c r="B86" s="99" t="n"/>
+      <c r="C86" s="99" t="n">
+        <v>6</v>
+      </c>
+      <c r="D86" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E86" s="100" t="inlineStr">
+        <is>
+          <t>Perez v. United States (1971)</t>
+        </is>
+      </c>
+      <c r="F86" s="99" t="inlineStr">
+        <is>
+          <t>Commerce Clause: class of activities</t>
+        </is>
+      </c>
+      <c r="G86" s="99" t="inlineStr">
+        <is>
+          <t>Perez was convicted under the federal loan-sharking statute for extortionate collection from a local butcher shop owner, with no proof of interstate movement.</t>
+        </is>
+      </c>
+      <c r="H86" s="99" t="inlineStr">
+        <is>
+          <t>Congress could criminalize extortionate credit transactions, even purely local ones, under the Commerce Clause; conviction affirmed.</t>
+        </is>
+      </c>
+      <c r="I86" s="99" t="inlineStr">
+        <is>
+          <t>The Commerce Clause reaches three categories: (1) use of the channels of commerce; (2) protection of instrumentalities and persons or things in commerce; (3) activities affecting commerce. When a class of activities is within federal power, courts may not 'excise, as trivial, individual instances' of the class.</t>
+        </is>
+      </c>
+      <c r="J86" s="99" t="inlineStr">
+        <is>
+          <t>• Category examples: shipping stolen goods (channels); destroying aircraft or thefts from interstate shipments (instrumentalities and things in commerce)
+• Congress need not make particularized findings, though here it found loan sharking funds national organized crime
+• Stewart dissent: no rational line between loan sharking and other local crime, which the Ninth and Tenth Amendments reserve to the States
+• Holmes in Westfall: Congress may 'embrace more than the precise thing to be prevented'</t>
+        </is>
+      </c>
+      <c r="K86" s="99" t="inlineStr">
+        <is>
+          <t>Perez gives the three-category framework Lopez later refines, and its class-of-activities rule underlies Russell and Raich. Stewart's dissent previews Lopez's police-power concern.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="105" t="inlineStr">
+        <is>
+          <t>Commerce Clause</t>
+        </is>
+      </c>
+      <c r="B87" s="99" t="n"/>
+      <c r="C87" s="99" t="n">
+        <v>6</v>
+      </c>
+      <c r="D87" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E87" s="100" t="inlineStr">
+        <is>
+          <t>Hodel v. Virginia Surface Mining &amp; Reclamation Ass'n (1981)</t>
+        </is>
+      </c>
+      <c r="F87" s="99" t="inlineStr">
+        <is>
+          <t>Commerce Clause: rational basis</t>
+        </is>
+      </c>
+      <c r="G87" s="99" t="inlineStr">
+        <is>
+          <t>In a pre-enforcement facial challenge to the Surface Mining Control and Reclamation Act of 1977, a federal district court in Virginia declared central provisions unconstitutional and enjoined them.</t>
+        </is>
+      </c>
+      <c r="H87" s="99" t="inlineStr">
+        <is>
+          <t>On a facial challenge, the Act is a valid exercise of the commerce power and does not violate the Fifth or Tenth Amendments.</t>
+        </is>
+      </c>
+      <c r="I87" s="99" t="inlineStr">
+        <is>
+          <t>When Congress finds an activity affects interstate commerce, courts ask only whether the finding is rational and whether the means are reasonable and appropriate. Preventing destructive interstate competition and multistate environmental harm are valid aims.</t>
+        </is>
+      </c>
+      <c r="J87" s="99" t="inlineStr">
+        <is>
+          <t>• Calling an activity 'local' or a 'land use' does not resolve the question
+• Rehnquist concurred only in the judgment: the test is substantial effect, not mere effect
+• Rehnquist: 'Simply because Congress may conclude that a particular activity substantially affects interstate commerce does not necessarily make it so'; Morrison later held findings alone insufficient
+• Rehnquist called enumerated powers 'one of the greatest fictions' of the federal system</t>
+        </is>
+      </c>
+      <c r="K87" s="99" t="inlineStr">
+        <is>
+          <t>Hodel is the deferential rational-basis case Souter cites in Lopez; Rehnquist's concurrence is the seed of Lopez and Morrison.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="105" t="inlineStr">
+        <is>
+          <t>Commerce Clause</t>
+        </is>
+      </c>
+      <c r="B88" s="99" t="n"/>
+      <c r="C88" s="99" t="n">
+        <v>6</v>
+      </c>
+      <c r="D88" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E88" s="100" t="inlineStr">
+        <is>
+          <t>Russell v. United States (1985)</t>
+        </is>
+      </c>
+      <c r="F88" s="99" t="inlineStr">
+        <is>
+          <t>Commerce Clause: statutory reach</t>
+        </is>
+      </c>
+      <c r="G88" s="99" t="inlineStr">
+        <is>
+          <t>Russell tried to have his two-unit Chicago rental building burned and was convicted under the federal arson statute covering property used in an activity affecting interstate commerce.</t>
+        </is>
+      </c>
+      <c r="H88" s="99" t="inlineStr">
+        <is>
+          <t>A rental building is property used in an activity affecting commerce, so the statute applied; conviction affirmed.</t>
+        </is>
+      </c>
+      <c r="I88" s="99" t="inlineStr">
+        <is>
+          <t>The rental of real estate is 'unquestionably' an activity affecting commerce; a local rental is an element of a broader commercial rental market, and power over the class reaches individual activity within it (Perez). The phrase 'any activity affecting interstate or foreign commerce' signals use of Congress's full commerce power.</t>
+        </is>
+      </c>
+      <c r="J88" s="99" t="inlineStr">
+        <is>
+          <t>• Congress dropped 'for business purposes'; Rep. Celler said bombing a private home would not be covered because of doubts about congressional power
+• Comment: Saneii v. Robards (W.D. Ky. 2003) held a residential real estate sale outside the commerce power for Federal Arbitration Act purposes because land is 'inherently intrastate'
+• Professor's question: can Saneii be reconciled with Russell? Tension: Russell views one rental as part of a broad market; Saneii viewed one sale alone</t>
+        </is>
+      </c>
+      <c r="K88" s="99" t="inlineStr">
+        <is>
+          <t>Russell shows the class-of-activities rule applied to real estate. Use Saneii as the counterpoint for owner-occupied or one-off property transactions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="105" t="inlineStr">
+        <is>
+          <t>Commerce Clause</t>
+        </is>
+      </c>
+      <c r="B89" s="99" t="inlineStr">
+        <is>
+          <t>Tenth Amendment &amp; federalism</t>
+        </is>
+      </c>
+      <c r="C89" s="99" t="n">
+        <v>6</v>
+      </c>
+      <c r="D89" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E89" s="100" t="inlineStr">
+        <is>
+          <t>United States v. Lopez (1995)</t>
+        </is>
+      </c>
+      <c r="F89" s="99" t="inlineStr">
+        <is>
+          <t>Commerce Clause limits</t>
+        </is>
+      </c>
+      <c r="G89" s="99" t="inlineStr">
+        <is>
+          <t>A 12th-grader brought a concealed handgun to his San Antonio high school and was charged under the Gun-Free School Zones Act of 1990.</t>
+        </is>
+      </c>
+      <c r="H89" s="99" t="inlineStr">
+        <is>
+          <t>The Act exceeds the commerce power because it neither regulates commercial activity nor requires a connection between the gun possession and interstate commerce.</t>
+        </is>
+      </c>
+      <c r="I89" s="99" t="inlineStr">
+        <is>
+          <t>Congress may regulate (1) the use of the channels of interstate commerce; (2) the instrumentalities of interstate commerce, or persons or things in interstate commerce; and (3) activities that substantially affect interstate commerce. Under the third, the Court looks at whether the activity is economic, whether there is a jurisdictional element, whether there are findings, and how attenuated the link is.</t>
+        </is>
+      </c>
+      <c r="J89" s="99" t="inlineStr">
+        <is>
+          <t>• The test is 'substantially affects,' not merely 'affects'; only category 3 could apply
+• Rejected the government's cost-of-crime and national-productivity theories as 'pil[ing] inference upon inference' toward a general police power
+• Lopez overruled nothing; Congress normally need not make findings
+• Kennedy: stare decisis bars a return to an 18th-century view; federalism is the Framers' 'unique contribution.' Thomas: original 'commerce' means buying, selling, bartering and transport. Breyer: cumulative effect plus rational basis. Souter: 'Not every epochal case has come in epochal trappings'</t>
+        </is>
+      </c>
+      <c r="K89" s="99" t="inlineStr">
+        <is>
+          <t>Lopez is the first modern limit on the commerce power. Fixes: add a jurisdictional element (Clinton's 1996 amendment) or use spending (Dole); counterpoint is Raich's broad reading for economic schemes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="105" t="inlineStr">
+        <is>
+          <t>Commerce Clause</t>
+        </is>
+      </c>
+      <c r="B90" s="99" t="inlineStr">
+        <is>
+          <t>Section 5 enforcement</t>
+        </is>
+      </c>
+      <c r="C90" s="99" t="n">
+        <v>6</v>
+      </c>
+      <c r="D90" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E90" s="100" t="inlineStr">
+        <is>
+          <t>United States v. Morrison (2000)</t>
+        </is>
+      </c>
+      <c r="F90" s="99" t="inlineStr">
+        <is>
+          <t>Commerce Clause limits</t>
+        </is>
+      </c>
+      <c r="G90" s="99" t="inlineStr">
+        <is>
+          <t>A Virginia Tech student alleged two football players raped her and sued them under the Violence Against Women Act's federal civil remedy for gender-motivated violence.</t>
+        </is>
+      </c>
+      <c r="H90" s="99" t="inlineStr">
+        <is>
+          <t>The civil remedy exceeds Congress's power under both the Commerce Clause and Section 5 of the Fourteenth Amendment.</t>
+        </is>
+      </c>
+      <c r="I90" s="99" t="inlineStr">
+        <is>
+          <t>Congress may not regulate noneconomic, violent criminal conduct based solely on its aggregate effect on interstate commerce. Congressional findings are not sufficient by themselves; whether an activity substantially affects commerce is ultimately a judicial question.</t>
+        </is>
+      </c>
+      <c r="J90" s="99" t="inlineStr">
+        <is>
+          <t>• Findings relied on the 'but-for causal chain' Lopez rejected, which would let Congress regulate all violent crime and family law
+• The Court did NOT adopt a categorical rule against aggregating noneconomic activity, but has upheld only economic activity 'thus far'
+• 'The Constitution requires a distinction between what is truly national and what is truly local'; her remedy must come from Virginia
+• Souter dissent: a 'mountain of data' and rational-basis review make the result irreconcilable with precedent; Thomas would scrap the substantial effects test</t>
+        </is>
+      </c>
+      <c r="K90" s="99" t="inlineStr">
+        <is>
+          <t>Morrison confirms Lopez even with extensive findings. For hypos, a jurisdictional hook (e.g., violence against persons traveling in interstate commerce) makes a statute stronger.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="105" t="inlineStr">
+        <is>
+          <t>Commerce Clause</t>
+        </is>
+      </c>
+      <c r="B91" s="99" t="n"/>
+      <c r="C91" s="99" t="n">
+        <v>6</v>
+      </c>
+      <c r="D91" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E91" s="100" t="inlineStr">
+        <is>
+          <t>Gonzales v. Raich (2005)</t>
+        </is>
+      </c>
+      <c r="F91" s="99" t="inlineStr">
+        <is>
+          <t>Commerce Clause: economic class</t>
+        </is>
+      </c>
+      <c r="G91" s="99" t="inlineStr">
+        <is>
+          <t>California medical marijuana patients, acting lawfully under state law, had their homegrown plants seized by federal agents and sought to bar enforcement of the Controlled Substances Act.</t>
+        </is>
+      </c>
+      <c r="H91" s="99" t="inlineStr">
+        <is>
+          <t>The Controlled Substances Act validly applies to local cultivation and use of marijuana that complies with California law.</t>
+        </is>
+      </c>
+      <c r="I91" s="99" t="inlineStr">
+        <is>
+          <t>Congress may regulate purely local activities that are part of an economic 'class of activities' that substantially affects interstate commerce, and the Court asks only whether a rational basis exists. Failure to regulate would leave 'a gaping hole' in a comprehensive scheme.</t>
+        </is>
+      </c>
+      <c r="J91" s="99" t="inlineStr">
+        <is>
+          <t>• Follows Wickard: a fungible commodity with an established interstate market; illegality of the market does not matter
+• Distinguished Lopez and Morrison: those were challenges to whole statutes; Lopez was a 'brief, single-subject statute,' while the CSA regulates 'quintessentially economic' activity
+• Scalia: power over substantially affecting activities comes from the Necessary and Proper Clause and reaches noneconomic possession if needed to make a broader regulation effective
+• O'Connor: 'perverse incentive' to bury local regulation in big schemes, making Lopez 'nothing more than a drafting guide'; daycare/charades substitutes example. Thomas: the marijuana was 'neither interstate nor commerce'</t>
+        </is>
+      </c>
+      <c r="K91" s="99" t="inlineStr">
+        <is>
+          <t>Raich shows Lopez's limit is narrow when the activity sits inside a comprehensive economic scheme. State-law compliance does not matter under the Supremacy Clause; relief lies in rescheduling or the democratic process.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="105" t="inlineStr">
+        <is>
+          <t>Commerce Clause</t>
+        </is>
+      </c>
+      <c r="B92" s="99" t="n"/>
+      <c r="C92" s="99" t="n">
+        <v>7</v>
+      </c>
+      <c r="D92" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E92" s="100" t="inlineStr">
+        <is>
+          <t>United States v. Dorsey (9th Cir. 2005)</t>
+        </is>
+      </c>
+      <c r="F92" s="99" t="inlineStr">
+        <is>
+          <t>Commerce Clause: jurisdictional element</t>
+        </is>
+      </c>
+      <c r="G92" s="99" t="inlineStr">
+        <is>
+          <t>Dorsey was convicted of possessing a firearm in a school zone in Anchorage under 18 U.S.C. § 922(q), which Congress amended after Lopez to cover only a firearm that "has moved in or that otherwise affects interstate or foreign commerce."</t>
+        </is>
+      </c>
+      <c r="H92" s="99" t="inlineStr">
+        <is>
+          <t>The amended § 922(q) is valid because its jurisdictional element ensures, case by case, that the possession affects interstate commerce, which "saves § 922(q) from the infirmity that defeated it in Lopez."</t>
+        </is>
+      </c>
+      <c r="I92" s="99" t="inlineStr">
+        <is>
+          <t>An express jurisdictional element tying each offense to interstate commerce brings a criminal statute within the commerce power (Bass, Scarborough). Lopez did not alter that rule, and Morrison noted that such an element was missing from the law it struck down.</t>
+        </is>
+      </c>
+      <c r="J92" s="99" t="inlineStr">
+        <is>
+          <t>• The cure for Lopez was the jurisdictional element, not congressional findings or a requirement that the defendant crossed state lines
+• Scarborough: "the minimal nexus that the firearm have been, at some time, in interstate commerce" suffices
+• Followed the Ninth Circuit's § 922(g) precedent and agreed with the Eighth Circuit (Danks)
+• Later abrogated by Arizona v. Gant on grounds unrelated to the Commerce Clause</t>
+        </is>
+      </c>
+      <c r="K92" s="99" t="inlineStr">
+        <is>
+          <t>Shows Congress's response to Lopez: add a jurisdictional hook. Pair with Phomma, and contrast Willett's Bonner concurrence, which doubts that a minimal nexus meaningfully limits federal power over local possession.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="105" t="inlineStr">
+        <is>
+          <t>Commerce Clause</t>
+        </is>
+      </c>
+      <c r="B93" s="99" t="inlineStr">
+        <is>
+          <t>Taxing &amp; Spending; Necessary &amp; Proper / implied powers</t>
+        </is>
+      </c>
+      <c r="C93" s="99" t="n">
+        <v>7</v>
+      </c>
+      <c r="D93" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E93" s="100" t="inlineStr">
+        <is>
+          <t>NFIB v. Sebelius (2012)</t>
+        </is>
+      </c>
+      <c r="F93" s="99" t="inlineStr">
+        <is>
+          <t>Commerce, Taxing and Spending Powers</t>
+        </is>
+      </c>
+      <c r="G93" s="99" t="inlineStr">
+        <is>
+          <t>The Affordable Care Act required individuals to buy health insurance or make a "shared responsibility payment" to the IRS, and threatened States with loss of all existing Medicaid funds unless they covered all nonelderly people below 133% of the poverty line. Florida and other States, individuals and the NFIB challenged both provisions.</t>
+        </is>
+      </c>
+      <c r="H93" s="99" t="inlineStr">
+        <is>
+          <t>The mandate cannot be upheld under the Commerce or Necessary and Proper Clauses but is valid as a tax, and the Medicaid expansion is coercive only insofar as existing Medicaid funds may be withdrawn, so that sanction is barred and the rest of the Act stands.</t>
+        </is>
+      </c>
+      <c r="I93" s="99" t="inlineStr">
+        <is>
+          <t>Commerce (Roberts): Congress may regulate existing activity but not compel individuals to enter commerce; "The Framers gave Congress the power to regulate commerce, not to compel it." Tax: substance controls over the "penalty" label; under the Drexel Furniture factors (not a heavy burden, no scienter, collected by the IRS) the payment is a tax, and the saving canon adopts any "fairly possible" constitutional reading. Spending: conditions on the use of new funds are valid, but threatening other significant independent grants turns "pressure into compulsion" ("a gun to the head," not Dole's "relatively mild encouragement").</t>
+        </is>
+      </c>
+      <c r="J93" s="99" t="inlineStr">
+        <is>
+          <t>• Necessary and Proper failed because the mandate is not "proper": it lets Congress create the predicate for exercising its own power; Raich distinguished
+• Roberts reached the commerce question only because the tax reading was a saving construction needed if the command failed; fn. 3: Ginsburg's other mandates (jury duty, draft) rest on powers other than commerce
+• Ginsburg: joins the tax holding, but would also uphold the mandate under the Commerce Clause (unique health market, free riders, the "broccoli horrible" piles inference upon inference) and the Medicaid expansion as enacted
+• Joint dissent: self-insurance is "wordplay"; "If all inactivity affecting commerce is commerce, commerce is everything"; would hold the whole Act inoperative
+• Medicaid "shift in kind, not merely degree": original program covered four categories of the needy; expansion covers the entire nonelderly population below 133% of poverty; separate funding provision (90% for newly eligible vs. 50-83%); less comprehensive coverage. Congress had styled it a mere alteration of existing Medicaid; Roberts looked past the label</t>
+        </is>
+      </c>
+      <c r="K93" s="99" t="inlineStr">
+        <is>
+          <t>Modern limit on the commerce power (activity versus inactivity) alongside Lopez and Morrison, and the first spending condition held coercive; counter with Ginsburg's view that the activity line is a "newly minted" formalism like the abandoned pre-New Deal categories.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="105" t="inlineStr">
+        <is>
+          <t>Commerce Clause</t>
+        </is>
+      </c>
+      <c r="B94" s="99" t="n"/>
+      <c r="C94" s="99" t="n">
+        <v>7</v>
+      </c>
+      <c r="D94" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E94" s="100" t="inlineStr">
+        <is>
+          <t>United States v. Phomma (D. Or. 2021)</t>
+        </is>
+      </c>
+      <c r="F94" s="99" t="inlineStr">
+        <is>
+          <t>Commerce Clause: jurisdictional element</t>
+        </is>
+      </c>
+      <c r="G94" s="99" t="inlineStr">
+        <is>
+          <t>Phomma was charged under the civil disorder statute, 18 U.S.C. § 231(a)(3), for spraying Portland police officers with bear spray during an August 2020 protest at the ICE building, where protesters blocked street traffic.</t>
+        </is>
+      </c>
+      <c r="H94" s="99" t="inlineStr">
+        <is>
+          <t>The motion to dismiss was denied because § 231(a)(3) has an express jurisdictional element requiring a civil disorder that "obstructs, delays, or adversely affects commerce."</t>
+        </is>
+      </c>
+      <c r="I94" s="99" t="inlineStr">
+        <is>
+          <t>Applying Lopez's three categories and Morrison's four factors (congressional findings, an express jurisdictional element, economic nature, attenuated link), a substantive express jurisdictional element keeps a criminal statute within the commerce power. The defendant cited no case striking down a statute that had one.</t>
+        </is>
+      </c>
+      <c r="J94" s="99" t="inlineStr">
+        <is>
+          <t>• Morrison's factors do NOT include whether the area is one the States traditionally regulate
+• The element must be substantive, not added just to ward off challenges; obstructing officers who are quelling a commerce-affecting disorder itself affects commerce (Howard)
+• Alternative basis: a superseding indictment under the "federally protected function" prong, since the protest blocked access to the ICE facility
+• A "civil disorder" requires an assemblage of three or more persons</t>
+        </is>
+      </c>
+      <c r="K94" s="99" t="inlineStr">
+        <is>
+          <t>Applies Dorsey's jurisdictional-element reasoning to protest violence; also shows overlapping federal and state prosecution of the same conduct (Phomma faced parallel state charges).</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="105" t="inlineStr">
+        <is>
+          <t>Commerce Clause</t>
+        </is>
+      </c>
+      <c r="B95" s="99" t="n"/>
+      <c r="C95" s="99" t="n">
+        <v>7</v>
+      </c>
+      <c r="D95" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E95" s="100" t="inlineStr">
+        <is>
+          <t>United States v. Protho (7th Cir. 2022)</t>
+        </is>
+      </c>
+      <c r="F95" s="99" t="inlineStr">
+        <is>
+          <t>Commerce Clause: instrumentalities</t>
+        </is>
+      </c>
+      <c r="G95" s="99" t="inlineStr">
+        <is>
+          <t>Protho used his Ford Explorer to abduct a ten-year-old girl in Calumet City, Illinois, and was convicted under the Federal Kidnapping Act, which since 2006 covers use of "any means, facility, or instrumentality of interstate or foreign commerce." The jury was told that using an automobile satisfies that element.</t>
+        </is>
+      </c>
+      <c r="H95" s="99" t="inlineStr">
+        <is>
+          <t>Conviction affirmed: automobiles are instrumentalities of interstate commerce, so the acquittal motion was properly denied and the jury was properly instructed.</t>
+        </is>
+      </c>
+      <c r="I95" s="99" t="inlineStr">
+        <is>
+          <t>For the instrumentalities category, what matters is "the nature of the regulated object's class (here, automobiles) rather than the particular use of one member of that class"; no separate proof of interstate movement is required (Mandel).</t>
+        </is>
+      </c>
+      <c r="J95" s="99" t="inlineStr">
+        <is>
+          <t>• Rejected the argument that each car must be judged individually; a car that never left the State still qualifies
+• The evidence showed he drove interstate anyway, but the holding does not depend on that
+• Nearly all circuits treat cars as instrumentalities; Cleveland: Congress's power over instrumentalities is "plenary"
+• Chavarria later distinguished it as a case about "automobiles," not all "motor vehicles"</t>
+        </is>
+      </c>
+      <c r="K95" s="99" t="inlineStr">
+        <is>
+          <t>Represents the broad, class-based reading of Lopez's instrumentalities category; set it against Chavarria to show the circuit tension over how far that category reaches into local crime.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="105" t="inlineStr">
+        <is>
+          <t>Commerce Clause</t>
+        </is>
+      </c>
+      <c r="B96" s="99" t="n"/>
+      <c r="C96" s="99" t="n">
+        <v>7</v>
+      </c>
+      <c r="D96" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E96" s="100" t="inlineStr">
+        <is>
+          <t>United States v. Chavarria (10th Cir. 2025)</t>
+        </is>
+      </c>
+      <c r="F96" s="99" t="inlineStr">
+        <is>
+          <t>Commerce Clause: instrumentalities</t>
+        </is>
+      </c>
+      <c r="G96" s="99" t="inlineStr">
+        <is>
+          <t>Chavarria and Romero allegedly kidnapped and murdered a woman in Eddy County, New Mexico. The federal kidnapping indictment alleged only that they "used a motor vehicle, a means, facility, and instrumentality of interstate commerce."</t>
+        </is>
+      </c>
+      <c r="H96" s="99" t="inlineStr">
+        <is>
+          <t>Dismissal affirmed: "motor vehicles" are not per se instrumentalities of interstate commerce, so the "threadbare, conclusory" indictment was fatally deficient.</t>
+        </is>
+      </c>
+      <c r="I96" s="99" t="inlineStr">
+        <is>
+          <t>An instrumentality of interstate commerce "must be a means to the end of commerce." Trains and aircraft qualify per se because they are used almost exclusively for commercial transport, but a generic class like motor vehicles (which includes e-bikes, lawnmowers and scooters) does not; holding otherwise would creep toward a general federal police power.</t>
+        </is>
+      </c>
+      <c r="J96" s="99" t="inlineStr">
+        <is>
+          <t>• Opens with then-Senator Biden: Congress federalizes "everything that walks, talks, and moves"; the government sought to add "everything that drives"
+• Distinguished Protho and Windham by level of generality (cars and automobiles versus motor vehicles) and called their rationales "perfunctory"
+• Did NOT decide the statute's facial constitutionality (constitutional avoidance), and New Mexico remains free to prosecute
+• An indictment alleging the defendants crossed state lines, the evil the 1932 Act targeted, would likely stand</t>
+        </is>
+      </c>
+      <c r="K96" s="99" t="inlineStr">
+        <is>
+          <t>The leading counterweight to Protho, grounded in the absence of a federal police power (Cohens v. Virginia, Federalist No. 17); use it to frame federalism as a question of who prosecutes, not whether the crime is punished.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="105" t="inlineStr">
+        <is>
+          <t>Commerce Clause</t>
+        </is>
+      </c>
+      <c r="B97" s="99" t="n"/>
+      <c r="C97" s="99" t="n">
+        <v>7</v>
+      </c>
+      <c r="D97" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E97" s="100" t="inlineStr">
+        <is>
+          <t>United States v. Bonner (5th Cir. 2025)</t>
+        </is>
+      </c>
+      <c r="F97" s="99" t="inlineStr">
+        <is>
+          <t>Commerce Clause: felon in possession</t>
+        </is>
+      </c>
+      <c r="G97" s="99" t="inlineStr">
+        <is>
+          <t>Bonner, with prior drug-trafficking and felon-in-possession convictions, pleaded guilty to possessing a firearm as a felon under 18 U.S.C. § 922(g)(1) and challenged the statute under the Second Amendment, vagueness, the Commerce Clause and Equal Protection.</t>
+        </is>
+      </c>
+      <c r="H97" s="99" t="inlineStr">
+        <is>
+          <t>Affirmed per curiam: every challenge is foreclosed by Fifth Circuit precedent (Diaz on the Commerce Clause).</t>
+        </is>
+      </c>
+      <c r="I97" s="99" t="inlineStr">
+        <is>
+          <t>In the Fifth Circuit, § 922(g)(1) needs only a firearm made in one State and found in another, resting on Scarborough's minimal nexus. Willett, concurring, says a federal criminal statute must rest on an enumerated power and respect individual rights, and doubts § 922(g)(1) does either.</t>
+        </is>
+      </c>
+      <c r="J97" s="99" t="inlineStr">
+        <is>
+          <t>• Willett: mere possession fits uneasily in the Lopez categories because aggregation ordinarily requires economic activity
+• Willett: Scarborough was statutory construction that never mentioned the Commerce Clause, so it is "scant authority"
+• "Our decisions now expand federal power not by remote implication from the constitutional text, but by remote implication from our own precedents" (echoing Brutus)
+• Willett still joined the majority because precedent controls, and asked the full court or the Supreme Court to reexamine</t>
+        </is>
+      </c>
+      <c r="K97" s="99" t="inlineStr">
+        <is>
+          <t>Use as the critique of the jurisdictional-element cases: a minimal nexus may make the commerce power limitless. Contrast Dorsey and Phomma, which treat the element as enough.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="105" t="inlineStr">
+        <is>
+          <t>Commerce Clause</t>
+        </is>
+      </c>
+      <c r="B98" s="101" t="inlineStr">
+        <is>
+          <t>Taxing &amp; Spending</t>
+        </is>
+      </c>
+      <c r="C98" s="101" t="n">
+        <v>5</v>
+      </c>
+      <c r="D98" s="101" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="E98" s="102" t="inlineStr">
+        <is>
+          <t>The Federalist Nos. 14, 36 and 45 (1787-1788)</t>
+        </is>
+      </c>
+      <c r="F98" s="101" t="inlineStr">
+        <is>
+          <t>Commerce power: founding</t>
+        </is>
+      </c>
+      <c r="G98" s="101" t="inlineStr">
+        <is>
+          <t>Assigned excerpts from Madison (14, 45) and Hamilton (36) bearing on the commerce power.</t>
+        </is>
+      </c>
+      <c r="H98" s="101" t="inlineStr">
+        <is>
+          <t>Not a decision.</t>
+        </is>
+      </c>
+      <c r="I98" s="101" t="inlineStr">
+        <is>
+          <t>Fed. 45: federal powers are 'few and defined,' and the commerce power is 'a new power' that 'few oppose.' Fed. 36 is included to show Hamilton treated agriculture, commerce and manufacturing as different activities.</t>
+        </is>
+      </c>
+      <c r="J98" s="101" t="inlineStr">
+        <is>
+          <t>• Reader Comment: Fed. 36 is there only to show farming, commerce and manufacturing as distinct (used by Thomas in Lopez)
+• Fed. 45 opens Lopez and is quoted in O'Connor's Raich dissent
+• Fed. 14 answers the objection from the country's great extent: roads, canals and navigation will ease intercourse</t>
+        </is>
+      </c>
+      <c r="K98" s="101" t="inlineStr">
+        <is>
+          <t>Use these for originalist limits on 'commerce' (Thomas in Lopez) and the 'few and defined' theme in Lopez and Raich.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="105" t="inlineStr">
+        <is>
+          <t>Commerce Clause</t>
+        </is>
+      </c>
+      <c r="B99" s="101" t="n"/>
+      <c r="C99" s="101" t="n">
+        <v>8</v>
+      </c>
+      <c r="D99" s="101" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="E99" s="102" t="inlineStr">
+        <is>
+          <t>The Federalist No. 11 (1787)</t>
+        </is>
+      </c>
+      <c r="F99" s="101" t="inlineStr">
+        <is>
+          <t>National commerce rationale</t>
+        </is>
+      </c>
+      <c r="G99" s="101" t="inlineStr">
+        <is>
+          <t>Hamilton's essay to the people of New York on the Union's commercial benefits.</t>
+        </is>
+      </c>
+      <c r="H99" s="101" t="inlineStr">
+        <is>
+          <t>No holding; argues that commercial unity requires a unified government.</t>
+        </is>
+      </c>
+      <c r="I99" s="101" t="inlineStr">
+        <is>
+          <t>"An unrestrained intercourse between the States" advances each State's trade, and "an unity of commercial, as well as political interests, can only result from an unity of government."</t>
+        </is>
+      </c>
+      <c r="J99" s="101" t="inlineStr">
+        <is>
+          <t>• Trade among disunited States would be "fettered, interrupted and narrowed by a multiplicity of causes"
+• Interchange lets a State whose staple fails from a bad harvest call on another's
+• Supports the national-market goal that the CRS sidebar says the dormant Commerce Clause preserves</t>
+        </is>
+      </c>
+      <c r="K99" s="101" t="inlineStr">
+        <is>
+          <t>Founding-era support for the national-market purpose behind both the commerce power and the dormant Commerce Clause; pair with Ginsburg's NFIB account of the Commerce Clause as the answer to the Articles' failures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="105" t="inlineStr">
+        <is>
+          <t>Commerce Clause</t>
+        </is>
+      </c>
+      <c r="B100" s="101" t="inlineStr">
+        <is>
+          <t>Tenth Amendment &amp; federalism</t>
+        </is>
+      </c>
+      <c r="C100" s="101" t="n">
+        <v>6</v>
+      </c>
+      <c r="D100" s="101" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="E100" s="102" t="inlineStr">
+        <is>
+          <t>Clinton's response to Lopez (1995) and the 1996 amendment</t>
+        </is>
+      </c>
+      <c r="F100" s="101" t="inlineStr">
+        <is>
+          <t>Commerce Clause: legislative response</t>
+        </is>
+      </c>
+      <c r="G100" s="101" t="inlineStr">
+        <is>
+          <t>After Lopez, President Clinton responded in a radio address and a message to Congress, and Congress later amended the Gun-Free School Zones Act.</t>
+        </is>
+      </c>
+      <c r="H100" s="101" t="inlineStr">
+        <is>
+          <t>Not a decision.</t>
+        </is>
+      </c>
+      <c r="I100" s="101" t="inlineStr">
+        <is>
+          <t>Clinton directed the Attorney General to report within a week, suggested tying federal funds to state school-zone gun bans, and sent Congress a bill adding a jurisdictional element. The 1996 amendment made it unlawful to possess 'a firearm that has moved in or that otherwise affects interstate or foreign commerce' in a school zone.</t>
+        </is>
+      </c>
+      <c r="J100" s="101" t="inlineStr">
+        <is>
+          <t>• Both fixes track Lopez: a jurisdictional element (category 3 nexus) and a spending-power route (Dole)
+• Reno: little prosecutorial impact because most guns have moved in commerce; no need to prove the defendant knew of the commerce link
+• CRS: the Supreme Court has not revisited the amended law; lower courts generally uphold it</t>
+        </is>
+      </c>
+      <c r="K100" s="101" t="inlineStr">
+        <is>
+          <t>Use it to show how Congress can respond to Lopez: add a jurisdictional hook or condition federal funds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="105" t="inlineStr">
+        <is>
+          <t>Commerce Clause</t>
+        </is>
+      </c>
+      <c r="B101" s="101" t="n"/>
+      <c r="C101" s="101" t="n">
+        <v>6</v>
+      </c>
+      <c r="D101" s="101" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="E101" s="102" t="inlineStr">
+        <is>
+          <t>Professor's note on Commerce Clause periods</t>
+        </is>
+      </c>
+      <c r="F101" s="101" t="inlineStr">
+        <is>
+          <t>Commerce Clause history</t>
+        </is>
+      </c>
+      <c r="G101" s="101" t="inlineStr">
+        <is>
+          <t>A note on the CALI lesson 'The Early Commerce Clause' (Gibbons up to Lopez).</t>
+        </is>
+      </c>
+      <c r="H101" s="101" t="inlineStr">
+        <is>
+          <t>Not a decision.</t>
+        </is>
+      </c>
+      <c r="I101" s="101" t="inlineStr">
+        <is>
+          <t>The critical dividing line is 1937, not 1995. Three periods: Gibbons to 1937; 1937 to 1995; and 1995 (Lopez) to the present.</t>
+        </is>
+      </c>
+      <c r="J101" s="101" t="inlineStr">
+        <is>
+          <t>• Around 1937 the Court abandoned the direct/indirect limits (Jones &amp; Laughlin, then Wickard); Lopez left that era intact and overruled nothing</t>
+        </is>
+      </c>
+      <c r="K101" s="101" t="inlineStr">
+        <is>
+          <t>Use it to frame any Commerce Clause essay: Lopez trimmed the post-1937 expansion rather than reversing it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="105" t="inlineStr">
+        <is>
+          <t>Commerce Clause</t>
+        </is>
+      </c>
+      <c r="B102" s="103" t="n"/>
+      <c r="C102" s="103" t="n">
+        <v>5</v>
+      </c>
+      <c r="D102" s="103" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+      <c r="E102" s="104" t="inlineStr">
+        <is>
+          <t>CRS, Congress's Authority to Regulate Interstate Commerce (2021)</t>
+        </is>
+      </c>
+      <c r="F102" s="103" t="inlineStr">
+        <is>
+          <t>Commerce Clause: overview</t>
+        </is>
+      </c>
+      <c r="G102" s="103" t="inlineStr">
+        <is>
+          <t>A CRS survey of Commerce Clause doctrine.</t>
+        </is>
+      </c>
+      <c r="H102" s="103" t="inlineStr">
+        <is>
+          <t>Describes three eras: constrained (before the 1930s), expansive (mid-20th century), and limits since Lopez.</t>
+        </is>
+      </c>
+      <c r="I102" s="103" t="inlineStr">
+        <is>
+          <t>Lower courts weigh four substantial-effects factors: economic nature, jurisdictional element, findings, and the attenuation of the link. NFIB: no regulation of inactivity.</t>
+        </is>
+      </c>
+      <c r="J102" s="103" t="inlineStr">
+        <is>
+          <t>• Findings are neither necessary nor sufficient (Lopez; Morrison)
+• After Lopez, Congress added a jurisdictional element to the gun law, and lower courts uphold it (see Dorsey)
+• Examples of each Lopez category</t>
+        </is>
+      </c>
+      <c r="K102" s="103" t="inlineStr">
+        <is>
+          <t>Use for the arc of Commerce Clause doctrine in an essay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="105" t="inlineStr">
+        <is>
+          <t>Commerce Clause</t>
+        </is>
+      </c>
+      <c r="B103" s="103" t="inlineStr">
+        <is>
+          <t>Taxing &amp; Spending; Necessary &amp; Proper / implied powers; Major questions &amp; nondelegation</t>
+        </is>
+      </c>
+      <c r="C103" s="103" t="n">
+        <v>5</v>
+      </c>
+      <c r="D103" s="103" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+      <c r="E103" s="104" t="inlineStr">
+        <is>
+          <t>CRS, Recurring Constitutional Issues in Federal Legislation (2022)</t>
+        </is>
+      </c>
+      <c r="F103" s="103" t="inlineStr">
+        <is>
+          <t>Congress's powers: overview</t>
+        </is>
+      </c>
+      <c r="G103" s="103" t="inlineStr">
+        <is>
+          <t>A CRS checklist for evaluating federal legislation.</t>
+        </is>
+      </c>
+      <c r="H103" s="103" t="inlineStr">
+        <is>
+          <t>Every bill raises two questions: is it within an enumerated power, and does it violate another constraint (federalism, separation of powers, individual rights)?</t>
+        </is>
+      </c>
+      <c r="I103" s="103" t="inlineStr">
+        <is>
+          <t>Summarizes Lopez's categories, Dole's spending limits, Boerne's congruence and proportionality, anti-commandeering (Murphy v. NCAA), bicameralism and presentment (Chadha), and nondelegation (intelligible principle).</t>
+        </is>
+      </c>
+      <c r="J103" s="103" t="inlineStr">
+        <is>
+          <t>• The two-question framework
+• Dole's limits restated: clear notice, relatedness, no coercion, no independent bar</t>
+        </is>
+      </c>
+      <c r="K103" s="103" t="inlineStr">
+        <is>
+          <t>A ready-made structure for any "Is this statute constitutional?" essay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="105" t="inlineStr">
+        <is>
+          <t>Commerce Clause</t>
+        </is>
+      </c>
+      <c r="B104" s="103" t="n"/>
+      <c r="C104" s="103" t="n">
+        <v>8</v>
+      </c>
+      <c r="D104" s="103" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+      <c r="E104" s="104" t="inlineStr">
+        <is>
+          <t>CALI Assessment: Contemporary Commerce Clause</t>
+        </is>
+      </c>
+      <c r="F104" s="103" t="inlineStr">
+        <is>
+          <t>Commerce Clause: practice</t>
+        </is>
+      </c>
+      <c r="G104" s="103" t="inlineStr">
+        <is>
+          <t>A self-test on post-1995 commerce cases.</t>
+        </is>
+      </c>
+      <c r="H104" s="103" t="inlineStr">
+        <is>
+          <t>The professor's note asks whether recreational bicycles are instrumentalities of interstate commerce.</t>
+        </is>
+      </c>
+      <c r="I104" s="103" t="inlineStr">
+        <is>
+          <t>Ties to the Week 7 vehicle cases: Protho (cars are instrumentalities by class) vs. Chavarria (generic "motor vehicles" are not per se instrumentalities).</t>
+        </is>
+      </c>
+      <c r="J104" s="103" t="inlineStr">
+        <is>
+          <t>• Would the bicycle answer differ in the Tenth Circuit (Chavarria)?
+• Class of object vs. particular use</t>
+        </is>
+      </c>
+      <c r="K104" s="103" t="inlineStr">
+        <is>
+          <t>Use to show the circuit split on instrumentalities.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="105" t="inlineStr">
+        <is>
+          <t>Taxing &amp; Spending</t>
+        </is>
+      </c>
+      <c r="B105" s="99" t="n"/>
+      <c r="C105" s="99" t="n">
+        <v>5</v>
+      </c>
+      <c r="D105" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E105" s="100" t="inlineStr">
+        <is>
+          <t>United States v. Butler (1936)</t>
+        </is>
+      </c>
+      <c r="F105" s="99" t="inlineStr">
+        <is>
+          <t>Spending Clause</t>
+        </is>
+      </c>
+      <c r="G105" s="99" t="inlineStr">
+        <is>
+          <t>The reader excerpt omits the facts; it gives only the Court's discussion of the power to tax and spend for the general welfare.</t>
+        </is>
+      </c>
+      <c r="H105" s="99" t="inlineStr">
+        <is>
+          <t>The Court adopted the Hamiltonian view that the power to spend for the general welfare is not limited to the enumerated powers (per O'Connor in Dole, Butler then struck down the Agricultural Adjustment Act as regulation).</t>
+        </is>
+      </c>
+      <c r="I105" s="99" t="inlineStr">
+        <is>
+          <t>Spending for public purposes 'is not limited by the direct grants of legislative power,' but must serve the general, national welfare and not local purposes.</t>
+        </is>
+      </c>
+      <c r="J105" s="99" t="inlineStr">
+        <is>
+          <t>• Madison: General Welfare Clause only refers to other enumerated powers ('mere tautology'); Hamilton: a separate power limited by the general welfare; Court adopted Story's Hamiltonian view
+• The Court's 'only one duty': lay the Constitution beside the statute and see if it 'squares'
+• Dole relies on Butler; O'Connor calls Butler the last case striking down an Act under the Spending Clause and blames its 'crabbed view' of commerce, not its spending analysis</t>
+        </is>
+      </c>
+      <c r="K105" s="99" t="inlineStr">
+        <is>
+          <t>Butler is the foundation for conditional spending: Congress may pursue ends it cannot regulate directly. Pair it with Dole's limits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="105" t="inlineStr">
+        <is>
+          <t>Taxing &amp; Spending</t>
+        </is>
+      </c>
+      <c r="B106" s="99" t="inlineStr">
+        <is>
+          <t>Tenth Amendment &amp; federalism</t>
+        </is>
+      </c>
+      <c r="C106" s="99" t="n">
+        <v>6</v>
+      </c>
+      <c r="D106" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E106" s="100" t="inlineStr">
+        <is>
+          <t>South Dakota v. Dole (1987)</t>
+        </is>
+      </c>
+      <c r="F106" s="99" t="inlineStr">
+        <is>
+          <t>Spending Clause conditions</t>
+        </is>
+      </c>
+      <c r="G106" s="99" t="inlineStr">
+        <is>
+          <t>South Dakota let 19-year-olds buy 3.2% beer. A federal law withheld 5% of certain highway funds from States allowing purchase of alcohol by anyone under 21.</t>
+        </is>
+      </c>
+      <c r="H106" s="99" t="inlineStr">
+        <is>
+          <t>The condition was a valid use of the spending power, whether or not Congress could set a drinking age directly.</t>
+        </is>
+      </c>
+      <c r="I106" s="99" t="inlineStr">
+        <is>
+          <t>Conditions on federal funds must (1) serve the general welfare; (2) be unambiguous; (3) relate to the federal interest in the particular national project; and (4) not be barred by another constitutional provision. Inducement also may not be so coercive that 'pressure turns into compulsion.'</t>
+        </is>
+      </c>
+      <c r="J106" s="99" t="inlineStr">
+        <is>
+          <t>• The independent-bar limit only stops Congress from inducing States to do something itself unconstitutional (e.g., cruel and unusual punishment); spending may pursue ends Congress cannot reach directly (Butler)
+• Losing 5% was 'relatively mild encouragement'; success in getting States to comply does not make a condition coercive
+• Court did not define the outer bounds of germaneness or adopt a 'directly related' test
+• O'Connor dissent: the condition is not reasonably related to highway spending; a condition must say how money is spent, anything more is regulation; state-capital hypothetical</t>
+        </is>
+      </c>
+      <c r="K106" s="99" t="inlineStr">
+        <is>
+          <t>Dole is the spending route around Lopez (see Clinton and Reagan). For a hypo, run all four limits plus coercion; O'Connor's relatedness test is the counterargument.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="105" t="inlineStr">
+        <is>
+          <t>Taxing &amp; Spending</t>
+        </is>
+      </c>
+      <c r="B107" s="99" t="inlineStr">
+        <is>
+          <t>Commerce Clause; Necessary &amp; Proper / implied powers</t>
+        </is>
+      </c>
+      <c r="C107" s="99" t="n">
+        <v>7</v>
+      </c>
+      <c r="D107" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E107" s="100" t="inlineStr">
+        <is>
+          <t>NFIB v. Sebelius (2012)</t>
+        </is>
+      </c>
+      <c r="F107" s="99" t="inlineStr">
+        <is>
+          <t>Commerce, Taxing and Spending Powers</t>
+        </is>
+      </c>
+      <c r="G107" s="99" t="inlineStr">
+        <is>
+          <t>The Affordable Care Act required individuals to buy health insurance or make a "shared responsibility payment" to the IRS, and threatened States with loss of all existing Medicaid funds unless they covered all nonelderly people below 133% of the poverty line. Florida and other States, individuals and the NFIB challenged both provisions.</t>
+        </is>
+      </c>
+      <c r="H107" s="99" t="inlineStr">
+        <is>
+          <t>The mandate cannot be upheld under the Commerce or Necessary and Proper Clauses but is valid as a tax, and the Medicaid expansion is coercive only insofar as existing Medicaid funds may be withdrawn, so that sanction is barred and the rest of the Act stands.</t>
+        </is>
+      </c>
+      <c r="I107" s="99" t="inlineStr">
+        <is>
+          <t>Commerce (Roberts): Congress may regulate existing activity but not compel individuals to enter commerce; "The Framers gave Congress the power to regulate commerce, not to compel it." Tax: substance controls over the "penalty" label; under the Drexel Furniture factors (not a heavy burden, no scienter, collected by the IRS) the payment is a tax, and the saving canon adopts any "fairly possible" constitutional reading. Spending: conditions on the use of new funds are valid, but threatening other significant independent grants turns "pressure into compulsion" ("a gun to the head," not Dole's "relatively mild encouragement").</t>
+        </is>
+      </c>
+      <c r="J107" s="99" t="inlineStr">
+        <is>
+          <t>• Necessary and Proper failed because the mandate is not "proper": it lets Congress create the predicate for exercising its own power; Raich distinguished
+• Roberts reached the commerce question only because the tax reading was a saving construction needed if the command failed; fn. 3: Ginsburg's other mandates (jury duty, draft) rest on powers other than commerce
+• Ginsburg: joins the tax holding, but would also uphold the mandate under the Commerce Clause (unique health market, free riders, the "broccoli horrible" piles inference upon inference) and the Medicaid expansion as enacted
+• Joint dissent: self-insurance is "wordplay"; "If all inactivity affecting commerce is commerce, commerce is everything"; would hold the whole Act inoperative
+• Medicaid "shift in kind, not merely degree": original program covered four categories of the needy; expansion covers the entire nonelderly population below 133% of poverty; separate funding provision (90% for newly eligible vs. 50-83%); less comprehensive coverage. Congress had styled it a mere alteration of existing Medicaid; Roberts looked past the label</t>
+        </is>
+      </c>
+      <c r="K107" s="99" t="inlineStr">
+        <is>
+          <t>Modern limit on the commerce power (activity versus inactivity) alongside Lopez and Morrison, and the first spending condition held coercive; counter with Ginsburg's view that the activity line is a "newly minted" formalism like the abandoned pre-New Deal categories.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="105" t="inlineStr">
+        <is>
+          <t>Taxing &amp; Spending</t>
+        </is>
+      </c>
+      <c r="B108" s="101" t="inlineStr">
+        <is>
+          <t>Commerce Clause</t>
+        </is>
+      </c>
+      <c r="C108" s="101" t="n">
+        <v>5</v>
+      </c>
+      <c r="D108" s="101" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="E108" s="102" t="inlineStr">
+        <is>
+          <t>The Federalist Nos. 14, 36 and 45 (1787-1788)</t>
+        </is>
+      </c>
+      <c r="F108" s="101" t="inlineStr">
+        <is>
+          <t>Commerce power: founding</t>
+        </is>
+      </c>
+      <c r="G108" s="101" t="inlineStr">
+        <is>
+          <t>Assigned excerpts from Madison (14, 45) and Hamilton (36) bearing on the commerce power.</t>
+        </is>
+      </c>
+      <c r="H108" s="101" t="inlineStr">
+        <is>
+          <t>Not a decision.</t>
+        </is>
+      </c>
+      <c r="I108" s="101" t="inlineStr">
+        <is>
+          <t>Fed. 45: federal powers are 'few and defined,' and the commerce power is 'a new power' that 'few oppose.' Fed. 36 is included to show Hamilton treated agriculture, commerce and manufacturing as different activities.</t>
+        </is>
+      </c>
+      <c r="J108" s="101" t="inlineStr">
+        <is>
+          <t>• Reader Comment: Fed. 36 is there only to show farming, commerce and manufacturing as distinct (used by Thomas in Lopez)
+• Fed. 45 opens Lopez and is quoted in O'Connor's Raich dissent
+• Fed. 14 answers the objection from the country's great extent: roads, canals and navigation will ease intercourse</t>
+        </is>
+      </c>
+      <c r="K108" s="101" t="inlineStr">
+        <is>
+          <t>Use these for originalist limits on 'commerce' (Thomas in Lopez) and the 'few and defined' theme in Lopez and Raich.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="105" t="inlineStr">
+        <is>
+          <t>Taxing &amp; Spending</t>
+        </is>
+      </c>
+      <c r="B109" s="101" t="n"/>
+      <c r="C109" s="101" t="n">
+        <v>6</v>
+      </c>
+      <c r="D109" s="101" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="E109" s="102" t="inlineStr">
+        <is>
+          <t>Reagan, Remarks at River Dell High School (1984)</t>
+        </is>
+      </c>
+      <c r="F109" s="101" t="inlineStr">
+        <is>
+          <t>Spending Clause conditions</t>
+        </is>
+      </c>
+      <c r="G109" s="101" t="inlineStr">
+        <is>
+          <t>President Reagan's remarks supporting the federal drinking-age legislation later upheld in South Dakota v. Dole.</t>
+        </is>
+      </c>
+      <c r="H109" s="101" t="inlineStr">
+        <is>
+          <t>Not a decision.</t>
+        </is>
+      </c>
+      <c r="I109" s="101" t="inlineStr">
+        <is>
+          <t>Reagan backed withholding 5% of highway funds from States without a 21-year-old drinking age, because the 'crazy-quilt' of state laws created 'Blood Borders' as teenagers drove to lower-age States.</t>
+        </is>
+      </c>
+      <c r="J109" s="101" t="inlineStr">
+        <is>
+          <t>• He reconciled this with 'State solutions' because drunk driving is a national problem involving travel across state borders and 'The choice remains with the States'
+• He did NOT claim Congress could set a drinking age directly
+• His Commission on Drunk Driving's findings reappear in Dole's relatedness analysis</t>
+        </is>
+      </c>
+      <c r="K109" s="101" t="inlineStr">
+        <is>
+          <t>Pair with Dole to show the political case for conditional spending: national problem, mild inducement, state choice preserved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="105" t="inlineStr">
+        <is>
+          <t>Taxing &amp; Spending</t>
+        </is>
+      </c>
+      <c r="B110" s="103" t="inlineStr">
+        <is>
+          <t>Commerce Clause; Necessary &amp; Proper / implied powers; Major questions &amp; nondelegation</t>
+        </is>
+      </c>
+      <c r="C110" s="103" t="n">
+        <v>5</v>
+      </c>
+      <c r="D110" s="103" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+      <c r="E110" s="104" t="inlineStr">
+        <is>
+          <t>CRS, Recurring Constitutional Issues in Federal Legislation (2022)</t>
+        </is>
+      </c>
+      <c r="F110" s="103" t="inlineStr">
+        <is>
+          <t>Congress's powers: overview</t>
+        </is>
+      </c>
+      <c r="G110" s="103" t="inlineStr">
+        <is>
+          <t>A CRS checklist for evaluating federal legislation.</t>
+        </is>
+      </c>
+      <c r="H110" s="103" t="inlineStr">
+        <is>
+          <t>Every bill raises two questions: is it within an enumerated power, and does it violate another constraint (federalism, separation of powers, individual rights)?</t>
+        </is>
+      </c>
+      <c r="I110" s="103" t="inlineStr">
+        <is>
+          <t>Summarizes Lopez's categories, Dole's spending limits, Boerne's congruence and proportionality, anti-commandeering (Murphy v. NCAA), bicameralism and presentment (Chadha), and nondelegation (intelligible principle).</t>
+        </is>
+      </c>
+      <c r="J110" s="103" t="inlineStr">
+        <is>
+          <t>• The two-question framework
+• Dole's limits restated: clear notice, relatedness, no coercion, no independent bar</t>
+        </is>
+      </c>
+      <c r="K110" s="103" t="inlineStr">
+        <is>
+          <t>A ready-made structure for any "Is this statute constitutional?" essay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="105" t="inlineStr">
+        <is>
+          <t>Necessary &amp; Proper / implied powers</t>
+        </is>
+      </c>
+      <c r="B111" s="99" t="inlineStr">
+        <is>
+          <t>Tenth Amendment &amp; federalism</t>
+        </is>
+      </c>
+      <c r="C111" s="99" t="n">
+        <v>8</v>
+      </c>
+      <c r="D111" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E111" s="100" t="inlineStr">
+        <is>
+          <t>McCulloch v. Maryland (1819)</t>
+        </is>
+      </c>
+      <c r="F111" s="99" t="inlineStr">
+        <is>
+          <t>Necessary and Proper; state taxation</t>
+        </is>
+      </c>
+      <c r="G111" s="99" t="inlineStr">
+        <is>
+          <t>Congress chartered the second Bank of the United States in 1816, and Maryland taxed banks operating in the State that its legislature had not chartered. John James, suing for himself and Maryland, won penalties under the act against McCulloch in Baltimore County court.</t>
+        </is>
+      </c>
+      <c r="H111" s="99" t="inlineStr">
+        <is>
+          <t>Congress had power to incorporate the Bank and its branches, and Maryland's tax on the Bank's operations was unconstitutional and void.</t>
+        </is>
+      </c>
+      <c r="I111" s="99" t="inlineStr">
+        <is>
+          <t>McCulloch test: "Let the end be legitimate, let it be within the scope of the constitution, and all means which are appropriate, which are plainly adapted to that end, which are not prohibited, but consist with the letter and spirit of the constitution, are constitutional." "Necessary" means convenient, useful or conducive to, not absolutely necessary. States may not "retard, impede, burden, or in any manner control" valid federal laws, because "the power to tax involves the power to destroy."</t>
+        </is>
+      </c>
+      <c r="J111" s="99" t="inlineStr">
+        <is>
+          <t>• Art. I, § 10's "absolutely necessary" shows the framers knew how to demand strict necessity; the clause sits among Congress's powers, not its limits, and enlarges rather than restrains
+• The Tenth Amendment omits "expressly," so delegation depends on "a fair construction of the whole instrument"; incorporating a bank is a means, not "a great substantive and independent power"
+• The Constitution came from the people in state conventions, not from sovereign States; only Congress represents all, so state "CONFIDENCE" cannot be relied on
+• Did NOT bar nondiscriminatory taxes on the Bank's real property or on Maryland citizens' interest in the Bank</t>
+        </is>
+      </c>
+      <c r="K111" s="99" t="inlineStr">
+        <is>
+          <t>Foundation for implied powers and deference on the choice of means ("it is a constitution we are expounding"); NFIB used its "great substantive and independent power" limit and its pretext caveat to show the Court still polices the ends.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="105" t="inlineStr">
+        <is>
+          <t>Necessary &amp; Proper / implied powers</t>
+        </is>
+      </c>
+      <c r="B112" s="99" t="inlineStr">
+        <is>
+          <t>Commerce Clause; Taxing &amp; Spending</t>
+        </is>
+      </c>
+      <c r="C112" s="99" t="n">
+        <v>7</v>
+      </c>
+      <c r="D112" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E112" s="100" t="inlineStr">
+        <is>
+          <t>NFIB v. Sebelius (2012)</t>
+        </is>
+      </c>
+      <c r="F112" s="99" t="inlineStr">
+        <is>
+          <t>Commerce, Taxing and Spending Powers</t>
+        </is>
+      </c>
+      <c r="G112" s="99" t="inlineStr">
+        <is>
+          <t>The Affordable Care Act required individuals to buy health insurance or make a "shared responsibility payment" to the IRS, and threatened States with loss of all existing Medicaid funds unless they covered all nonelderly people below 133% of the poverty line. Florida and other States, individuals and the NFIB challenged both provisions.</t>
+        </is>
+      </c>
+      <c r="H112" s="99" t="inlineStr">
+        <is>
+          <t>The mandate cannot be upheld under the Commerce or Necessary and Proper Clauses but is valid as a tax, and the Medicaid expansion is coercive only insofar as existing Medicaid funds may be withdrawn, so that sanction is barred and the rest of the Act stands.</t>
+        </is>
+      </c>
+      <c r="I112" s="99" t="inlineStr">
+        <is>
+          <t>Commerce (Roberts): Congress may regulate existing activity but not compel individuals to enter commerce; "The Framers gave Congress the power to regulate commerce, not to compel it." Tax: substance controls over the "penalty" label; under the Drexel Furniture factors (not a heavy burden, no scienter, collected by the IRS) the payment is a tax, and the saving canon adopts any "fairly possible" constitutional reading. Spending: conditions on the use of new funds are valid, but threatening other significant independent grants turns "pressure into compulsion" ("a gun to the head," not Dole's "relatively mild encouragement").</t>
+        </is>
+      </c>
+      <c r="J112" s="99" t="inlineStr">
+        <is>
+          <t>• Necessary and Proper failed because the mandate is not "proper": it lets Congress create the predicate for exercising its own power; Raich distinguished
+• Roberts reached the commerce question only because the tax reading was a saving construction needed if the command failed; fn. 3: Ginsburg's other mandates (jury duty, draft) rest on powers other than commerce
+• Ginsburg: joins the tax holding, but would also uphold the mandate under the Commerce Clause (unique health market, free riders, the "broccoli horrible" piles inference upon inference) and the Medicaid expansion as enacted
+• Joint dissent: self-insurance is "wordplay"; "If all inactivity affecting commerce is commerce, commerce is everything"; would hold the whole Act inoperative
+• Medicaid "shift in kind, not merely degree": original program covered four categories of the needy; expansion covers the entire nonelderly population below 133% of poverty; separate funding provision (90% for newly eligible vs. 50-83%); less comprehensive coverage. Congress had styled it a mere alteration of existing Medicaid; Roberts looked past the label</t>
+        </is>
+      </c>
+      <c r="K112" s="99" t="inlineStr">
+        <is>
+          <t>Modern limit on the commerce power (activity versus inactivity) alongside Lopez and Morrison, and the first spending condition held coercive; counter with Ginsburg's view that the activity line is a "newly minted" formalism like the abandoned pre-New Deal categories.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="105" t="inlineStr">
+        <is>
+          <t>Necessary &amp; Proper / implied powers</t>
+        </is>
+      </c>
+      <c r="B113" s="101" t="inlineStr">
+        <is>
+          <t>Foundations &amp; interpretation; Tenth Amendment &amp; federalism</t>
+        </is>
+      </c>
+      <c r="C113" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="D113" s="101" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="E113" s="102" t="inlineStr">
+        <is>
+          <t>Brutus No. 1 (1787)</t>
+        </is>
+      </c>
+      <c r="F113" s="101" t="inlineStr">
+        <is>
+          <t>Anti-Federalist: consolidation</t>
+        </is>
+      </c>
+      <c r="G113" s="101" t="inlineStr">
+        <is>
+          <t>Anti-Federalist essay asking whether the 13 states should be reduced to one great republic.</t>
+        </is>
+      </c>
+      <c r="H113" s="101" t="inlineStr">
+        <is>
+          <t>The Constitution approaches so near consolidation that it must "certainly and infallibly terminate in it."</t>
+        </is>
+      </c>
+      <c r="I113" s="101" t="inlineStr">
+        <is>
+          <t>A government of the proposed scope will absorb the states.</t>
+        </is>
+      </c>
+      <c r="J113" s="101" t="inlineStr">
+        <is>
+          <t>• Not a perfect consolidation, but it will end in one
+• Counterpoint to Federalist No. 45</t>
+        </is>
+      </c>
+      <c r="K113" s="101" t="inlineStr">
+        <is>
+          <t>Use as the counterpoint to Madison's few-and-defined federal powers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="105" t="inlineStr">
+        <is>
+          <t>Necessary &amp; Proper / implied powers</t>
+        </is>
+      </c>
+      <c r="B114" s="101" t="inlineStr">
+        <is>
+          <t>Foundations &amp; interpretation; Tenth Amendment &amp; federalism</t>
+        </is>
+      </c>
+      <c r="C114" s="101" t="n">
+        <v>8</v>
+      </c>
+      <c r="D114" s="101" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="E114" s="102" t="inlineStr">
+        <is>
+          <t>Brutus No. 1 (1787)</t>
+        </is>
+      </c>
+      <c r="F114" s="101" t="inlineStr">
+        <is>
+          <t>Anti-Federalist critique</t>
+        </is>
+      </c>
+      <c r="G114" s="101" t="inlineStr">
+        <is>
+          <t>Anti-Federalist essay in the New York Journal asking whether the States should be consolidated into one great republic.</t>
+        </is>
+      </c>
+      <c r="H114" s="101" t="inlineStr">
+        <is>
+          <t>No holding; argues the Constitution approaches so near consolidation that it "must, if executed, certainly and infallibly terminate in it."</t>
+        </is>
+      </c>
+      <c r="I114" s="101" t="inlineStr">
+        <is>
+          <t>The Necessary and Proper and Supremacy Clauses make the government "a complete one, and not a confederation"; the clause "may receive a construction to justify the passing almost any law" and could "entirely abolish the State legislatures."</t>
+        </is>
+      </c>
+      <c r="J114" s="101" t="inlineStr">
+        <is>
+          <t>• Objected to the breadth of federal power, not its weakness
+• Example: Congress could repeal a state revenue law as obstructing a federal tax it deems necessary
+• Predicted that powers reserved to the States would "very soon be annihilated"
+• Willett's Bonner concurrence invokes Brutus's fear of expansion by implication</t>
+        </is>
+      </c>
+      <c r="K114" s="101" t="inlineStr">
+        <is>
+          <t>The Anti-Federalist prediction against which to test McCulloch and the modern commerce cases; cite it for the argument that implied powers lead to consolidation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="105" t="inlineStr">
+        <is>
+          <t>Necessary &amp; Proper / implied powers</t>
+        </is>
+      </c>
+      <c r="B115" s="101" t="n"/>
+      <c r="C115" s="101" t="n">
+        <v>8</v>
+      </c>
+      <c r="D115" s="101" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="E115" s="102" t="inlineStr">
+        <is>
+          <t>The Federalist No. 44 (1788)</t>
+        </is>
+      </c>
+      <c r="F115" s="101" t="inlineStr">
+        <is>
+          <t>Necessary and Proper Clause</t>
+        </is>
+      </c>
+      <c r="G115" s="101" t="inlineStr">
+        <is>
+          <t>Madison defends the Necessary and Proper Clause against Anti-Federalist attack.</t>
+        </is>
+      </c>
+      <c r="H115" s="101" t="inlineStr">
+        <is>
+          <t>No holding; argues that "without the substance of this power, the whole constitution would be a dead letter."</t>
+        </is>
+      </c>
+      <c r="I115" s="101" t="inlineStr">
+        <is>
+          <t>Wherever the end is required, the means are authorized; even silence would have yielded the needed powers "by unavoidable implication." Misuse is checked first by the executive and judiciary and, in the last resort, by the people at elections.</t>
+        </is>
+      </c>
+      <c r="J115" s="101" t="inlineStr">
+        <is>
+          <t>• Four rejected alternatives: copy the Articles' "expressly" rule, a positive enumeration, a negative enumeration, or silence (NOT an "absolutely necessary" limit)
+• "Expressly" would be construed either so strictly as to disarm the government or so loosely as to destroy the restriction
+• A negative enumeration fails because every defect would act as a positive grant
+• The reader asks whether Madison's 1791 bank speech is consistent with this essay</t>
+        </is>
+      </c>
+      <c r="K115" s="101" t="inlineStr">
+        <is>
+          <t>Use with McCulloch for the broad view of implied means, and against Madison's own 1791 strict construction to show how his position shifted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="105" t="inlineStr">
+        <is>
+          <t>Necessary &amp; Proper / implied powers</t>
+        </is>
+      </c>
+      <c r="B116" s="101" t="inlineStr">
+        <is>
+          <t>Tenth Amendment &amp; federalism</t>
+        </is>
+      </c>
+      <c r="C116" s="101" t="n">
+        <v>8</v>
+      </c>
+      <c r="D116" s="101" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="E116" s="102" t="inlineStr">
+        <is>
+          <t>Tenth Amendment Debate, House of Representatives (1789)</t>
+        </is>
+      </c>
+      <c r="F116" s="101" t="inlineStr">
+        <is>
+          <t>Tenth Amendment; implied powers</t>
+        </is>
+      </c>
+      <c r="G116" s="101" t="inlineStr">
+        <is>
+          <t>In August 1789 the House considered the proposition that became the Tenth Amendment; Tucker, and later Gerry, moved to reserve all powers "not expressly delegated."</t>
+        </is>
+      </c>
+      <c r="H116" s="101" t="inlineStr">
+        <is>
+          <t>No holding; the House rejected "expressly" and adopted the text with "or to the people" and "to the United States" added.</t>
+        </is>
+      </c>
+      <c r="I116" s="101" t="inlineStr">
+        <is>
+          <t>The Tenth Amendment reserves powers not delegated, not powers not expressly delegated, so whether a power is delegated depends on fair construction, as McCulloch later held, unlike the Articles of Confederation's "expressly" rule.</t>
+        </is>
+      </c>
+      <c r="J116" s="101" t="inlineStr">
+        <is>
+          <t>• Madison: it is impossible to confine a government to express powers unless the Constitution recounted "every minutiae"
+• Sherman: corporate bodies possess all powers incident to their corporate capacity without express statement
+• "Expressly" had been moved in the Virginia convention by opponents of ratification and given up
+• Professor's response to King's claim that the Amendment is "a clear delineation" of power: "Is it really this easy?"</t>
+        </is>
+      </c>
+      <c r="K116" s="101" t="inlineStr">
+        <is>
+          <t>Use to rebut any argument that the Tenth Amendment limits Congress to express powers; it links directly to McCulloch's reading of the omitted word.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="105" t="inlineStr">
+        <is>
+          <t>Necessary &amp; Proper / implied powers</t>
+        </is>
+      </c>
+      <c r="B117" s="101" t="n"/>
+      <c r="C117" s="101" t="n">
+        <v>8</v>
+      </c>
+      <c r="D117" s="101" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="E117" s="102" t="inlineStr">
+        <is>
+          <t>Lighthouses Act (1789)</t>
+        </is>
+      </c>
+      <c r="F117" s="101" t="inlineStr">
+        <is>
+          <t>Early implied powers</t>
+        </is>
+      </c>
+      <c r="G117" s="101" t="inlineStr">
+        <is>
+          <t>The First Congress assumed the cost of lighthouses, beacons, buoys and public piers (after one year only if the State ceded them), funded a new lighthouse near the Chesapeake Bay entrance, and left pilots to state law until Congress acts.</t>
+        </is>
+      </c>
+      <c r="H117" s="101" t="inlineStr">
+        <is>
+          <t>No holding; the reader asks which Article I, § 8 power authorizes it.</t>
+        </is>
+      </c>
+      <c r="I117" s="101" t="inlineStr">
+        <is>
+          <t>Early congressional practice treated such measures as incidents of an enumerated power: Ames in 1791 cited erecting lighthouses as an incident of the power to regulate trade.</t>
+        </is>
+      </c>
+      <c r="J117" s="101" t="inlineStr">
+        <is>
+          <t>• No clause mentions lighthouses; the answer is an incident of the power to regulate commerce (Ames)
+• § 4 left regulation of pilots to existing and future state law until Congress provides otherwise</t>
+        </is>
+      </c>
+      <c r="K117" s="101" t="inlineStr">
+        <is>
+          <t>Evidence that the First Congress read its powers to include unlisted means, supporting the broad view later adopted in McCulloch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="105" t="inlineStr">
+        <is>
+          <t>Necessary &amp; Proper / implied powers</t>
+        </is>
+      </c>
+      <c r="B118" s="101" t="n"/>
+      <c r="C118" s="101" t="n">
+        <v>8</v>
+      </c>
+      <c r="D118" s="101" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="E118" s="102" t="inlineStr">
+        <is>
+          <t>Bank of the United States Debate (1791)</t>
+        </is>
+      </c>
+      <c r="F118" s="101" t="inlineStr">
+        <is>
+          <t>Implied powers; strict construction</t>
+        </is>
+      </c>
+      <c r="G118" s="101" t="inlineStr">
+        <is>
+          <t>In the House debate on chartering the first Bank of the United States, Madison argued the bill was unconstitutional and Fisher Ames answered him.</t>
+        </is>
+      </c>
+      <c r="H118" s="101" t="inlineStr">
+        <is>
+          <t>No judicial holding; the House passed the bank bill over Madison's objection.</t>
+        </is>
+      </c>
+      <c r="I118" s="101" t="inlineStr">
+        <is>
+          <t>Madison: the federal government holds only particular granted powers; the Necessary and Proper Clause is "merely declaratory" and limited to "means necessary to the end, and incident to the nature of the specified powers," and a bank was at most "convenient." Ames: government is "the highest kind of corporation" with tacit powers needed for its ends, unless repugnant to natural rights, expressly reserved rights, or powers assigned to the States.</t>
+        </is>
+      </c>
+      <c r="J118" s="101" t="inlineStr">
+        <is>
+          <t>• Madison's only possible sources: taxing for the general welfare, borrowing, and Necessary and Proper (NOT the commerce power); "It does not borrow a shilling"
+• Madison's "chain": borrowing to capital, capital to a bank, a bank to a charter; such a chain "will reach every object of legislation"
+• Madison: a power to grant charters of incorporation was proposed at the Convention and rejected
+• Ames: Congress already taxed ships and erected lighthouses as incidents of regulating trade; implied power's danger is uncertainty, and strict rules "only set up one construction against another"</t>
+        </is>
+      </c>
+      <c r="K118" s="101" t="inlineStr">
+        <is>
+          <t>Frames the strict versus broad construction debate that McCulloch resolved; ask whether Madison's 1791 position squares with Federalist No. 44 and his 1815 openness to a bank.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="105" t="inlineStr">
+        <is>
+          <t>Necessary &amp; Proper / implied powers</t>
+        </is>
+      </c>
+      <c r="B119" s="101" t="n"/>
+      <c r="C119" s="101" t="n">
+        <v>8</v>
+      </c>
+      <c r="D119" s="101" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="E119" s="102" t="inlineStr">
+        <is>
+          <t>Fisher Ames Letters (1791)</t>
+        </is>
+      </c>
+      <c r="F119" s="101" t="inlineStr">
+        <is>
+          <t>Bank debate politics</t>
+        </is>
+      </c>
+      <c r="G119" s="101" t="inlineStr">
+        <is>
+          <t>Private letters from Ames to Thomas Dwight and George Richards Minot reporting on the House bank debate.</t>
+        </is>
+      </c>
+      <c r="H119" s="101" t="inlineStr">
+        <is>
+          <t>No holding; Ames reported that the bill passed easily, "a strong proof of the little impression" Madison's attack made.</t>
+        </is>
+      </c>
+      <c r="I119" s="101" t="inlineStr">
+        <is>
+          <t>Shows Federalists dismissed Madison's constitutional objection and that the bill's real political difficulty was its effect on moving the capital from Philadelphia to the Potomac.</t>
+        </is>
+      </c>
+      <c r="J119" s="101" t="inlineStr">
+        <is>
+          <t>• Ames called Madison's speech "full of casuistry and sophistry"
+• Madison read at length from state ratification debates to argue for strict construction
+• "Great point of difficulty": the bank might leave Congress "fast anchored and immovable" in Philadelphia</t>
+        </is>
+      </c>
+      <c r="K119" s="101" t="inlineStr">
+        <is>
+          <t>Use with McCulloch's reliance on practice to show the bank question was settled politically before it reached the Court.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="105" t="inlineStr">
+        <is>
+          <t>Necessary &amp; Proper / implied powers</t>
+        </is>
+      </c>
+      <c r="B120" s="101" t="n"/>
+      <c r="C120" s="101" t="n">
+        <v>8</v>
+      </c>
+      <c r="D120" s="101" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="E120" s="102" t="inlineStr">
+        <is>
+          <t>Madison, Seventh Annual Message (1815)</t>
+        </is>
+      </c>
+      <c r="F120" s="101" t="inlineStr">
+        <is>
+          <t>National bank</t>
+        </is>
+      </c>
+      <c r="G120" s="101" t="inlineStr">
+        <is>
+          <t>President Madison's annual message after the War of 1812, addressing a $120 million national debt and the currency.</t>
+        </is>
+      </c>
+      <c r="H120" s="101" t="inlineStr">
+        <is>
+          <t>No holding; urges restoring a uniform national currency and says that if state banks cannot do it, "the probable operation of a national bank will merit consideration."</t>
+        </is>
+      </c>
+      <c r="I120" s="101" t="inlineStr">
+        <is>
+          <t>Shows President Madison open to a national bank he had opposed as unconstitutional as a congressman in 1791, consistent with McCulloch's point that experience led former opponents to support the second bank.</t>
+        </is>
+      </c>
+      <c r="J120" s="101" t="inlineStr">
+        <is>
+          <t>• Both points: restore "the benefits of an uniform national currency," and a national bank merits consideration if state banks fail
+• Fallback: government notes as a medium of circulation
+• He did NOT call a national bank unconstitutional; contrast Congressman Madison in 1791</t>
+        </is>
+      </c>
+      <c r="K120" s="101" t="inlineStr">
+        <is>
+          <t>Use to illustrate constitutional settlement by practice (McCulloch) and the tension in Madison's own views.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="105" t="inlineStr">
+        <is>
+          <t>Necessary &amp; Proper / implied powers</t>
+        </is>
+      </c>
+      <c r="B121" s="103" t="inlineStr">
+        <is>
+          <t>Commerce Clause; Taxing &amp; Spending; Major questions &amp; nondelegation</t>
+        </is>
+      </c>
+      <c r="C121" s="103" t="n">
+        <v>5</v>
+      </c>
+      <c r="D121" s="103" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+      <c r="E121" s="104" t="inlineStr">
+        <is>
+          <t>CRS, Recurring Constitutional Issues in Federal Legislation (2022)</t>
+        </is>
+      </c>
+      <c r="F121" s="103" t="inlineStr">
+        <is>
+          <t>Congress's powers: overview</t>
+        </is>
+      </c>
+      <c r="G121" s="103" t="inlineStr">
+        <is>
+          <t>A CRS checklist for evaluating federal legislation.</t>
+        </is>
+      </c>
+      <c r="H121" s="103" t="inlineStr">
+        <is>
+          <t>Every bill raises two questions: is it within an enumerated power, and does it violate another constraint (federalism, separation of powers, individual rights)?</t>
+        </is>
+      </c>
+      <c r="I121" s="103" t="inlineStr">
+        <is>
+          <t>Summarizes Lopez's categories, Dole's spending limits, Boerne's congruence and proportionality, anti-commandeering (Murphy v. NCAA), bicameralism and presentment (Chadha), and nondelegation (intelligible principle).</t>
+        </is>
+      </c>
+      <c r="J121" s="103" t="inlineStr">
+        <is>
+          <t>• The two-question framework
+• Dole's limits restated: clear notice, relatedness, no coercion, no independent bar</t>
+        </is>
+      </c>
+      <c r="K121" s="103" t="inlineStr">
+        <is>
+          <t>A ready-made structure for any "Is this statute constitutional?" essay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="105" t="inlineStr">
+        <is>
+          <t>Tenth Amendment &amp; federalism</t>
+        </is>
+      </c>
+      <c r="B122" s="99" t="inlineStr">
+        <is>
+          <t>Necessary &amp; Proper / implied powers</t>
+        </is>
+      </c>
+      <c r="C122" s="99" t="n">
+        <v>8</v>
+      </c>
+      <c r="D122" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E122" s="100" t="inlineStr">
+        <is>
+          <t>McCulloch v. Maryland (1819)</t>
+        </is>
+      </c>
+      <c r="F122" s="99" t="inlineStr">
+        <is>
+          <t>Necessary and Proper; state taxation</t>
+        </is>
+      </c>
+      <c r="G122" s="99" t="inlineStr">
+        <is>
+          <t>Congress chartered the second Bank of the United States in 1816, and Maryland taxed banks operating in the State that its legislature had not chartered. John James, suing for himself and Maryland, won penalties under the act against McCulloch in Baltimore County court.</t>
+        </is>
+      </c>
+      <c r="H122" s="99" t="inlineStr">
+        <is>
+          <t>Congress had power to incorporate the Bank and its branches, and Maryland's tax on the Bank's operations was unconstitutional and void.</t>
+        </is>
+      </c>
+      <c r="I122" s="99" t="inlineStr">
+        <is>
+          <t>McCulloch test: "Let the end be legitimate, let it be within the scope of the constitution, and all means which are appropriate, which are plainly adapted to that end, which are not prohibited, but consist with the letter and spirit of the constitution, are constitutional." "Necessary" means convenient, useful or conducive to, not absolutely necessary. States may not "retard, impede, burden, or in any manner control" valid federal laws, because "the power to tax involves the power to destroy."</t>
+        </is>
+      </c>
+      <c r="J122" s="99" t="inlineStr">
+        <is>
+          <t>• Art. I, § 10's "absolutely necessary" shows the framers knew how to demand strict necessity; the clause sits among Congress's powers, not its limits, and enlarges rather than restrains
+• The Tenth Amendment omits "expressly," so delegation depends on "a fair construction of the whole instrument"; incorporating a bank is a means, not "a great substantive and independent power"
+• The Constitution came from the people in state conventions, not from sovereign States; only Congress represents all, so state "CONFIDENCE" cannot be relied on
+• Did NOT bar nondiscriminatory taxes on the Bank's real property or on Maryland citizens' interest in the Bank</t>
+        </is>
+      </c>
+      <c r="K122" s="99" t="inlineStr">
+        <is>
+          <t>Foundation for implied powers and deference on the choice of means ("it is a constitution we are expounding"); NFIB used its "great substantive and independent power" limit and its pretext caveat to show the Court still polices the ends.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="105" t="inlineStr">
+        <is>
+          <t>Tenth Amendment &amp; federalism</t>
+        </is>
+      </c>
+      <c r="B123" s="99" t="inlineStr">
+        <is>
+          <t>Taxing &amp; Spending</t>
+        </is>
+      </c>
+      <c r="C123" s="99" t="n">
+        <v>6</v>
+      </c>
+      <c r="D123" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E123" s="100" t="inlineStr">
+        <is>
+          <t>South Dakota v. Dole (1987)</t>
+        </is>
+      </c>
+      <c r="F123" s="99" t="inlineStr">
+        <is>
+          <t>Spending Clause conditions</t>
+        </is>
+      </c>
+      <c r="G123" s="99" t="inlineStr">
+        <is>
+          <t>South Dakota let 19-year-olds buy 3.2% beer. A federal law withheld 5% of certain highway funds from States allowing purchase of alcohol by anyone under 21.</t>
+        </is>
+      </c>
+      <c r="H123" s="99" t="inlineStr">
+        <is>
+          <t>The condition was a valid use of the spending power, whether or not Congress could set a drinking age directly.</t>
+        </is>
+      </c>
+      <c r="I123" s="99" t="inlineStr">
+        <is>
+          <t>Conditions on federal funds must (1) serve the general welfare; (2) be unambiguous; (3) relate to the federal interest in the particular national project; and (4) not be barred by another constitutional provision. Inducement also may not be so coercive that 'pressure turns into compulsion.'</t>
+        </is>
+      </c>
+      <c r="J123" s="99" t="inlineStr">
+        <is>
+          <t>• The independent-bar limit only stops Congress from inducing States to do something itself unconstitutional (e.g., cruel and unusual punishment); spending may pursue ends Congress cannot reach directly (Butler)
+• Losing 5% was 'relatively mild encouragement'; success in getting States to comply does not make a condition coercive
+• Court did not define the outer bounds of germaneness or adopt a 'directly related' test
+• O'Connor dissent: the condition is not reasonably related to highway spending; a condition must say how money is spent, anything more is regulation; state-capital hypothetical</t>
+        </is>
+      </c>
+      <c r="K123" s="99" t="inlineStr">
+        <is>
+          <t>Dole is the spending route around Lopez (see Clinton and Reagan). For a hypo, run all four limits plus coercion; O'Connor's relatedness test is the counterargument.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="105" t="inlineStr">
+        <is>
+          <t>Tenth Amendment &amp; federalism</t>
+        </is>
+      </c>
+      <c r="B124" s="99" t="inlineStr">
+        <is>
+          <t>Commerce Clause</t>
+        </is>
+      </c>
+      <c r="C124" s="99" t="n">
+        <v>6</v>
+      </c>
+      <c r="D124" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E124" s="100" t="inlineStr">
+        <is>
+          <t>United States v. Lopez (1995)</t>
+        </is>
+      </c>
+      <c r="F124" s="99" t="inlineStr">
+        <is>
+          <t>Commerce Clause limits</t>
+        </is>
+      </c>
+      <c r="G124" s="99" t="inlineStr">
+        <is>
+          <t>A 12th-grader brought a concealed handgun to his San Antonio high school and was charged under the Gun-Free School Zones Act of 1990.</t>
+        </is>
+      </c>
+      <c r="H124" s="99" t="inlineStr">
+        <is>
+          <t>The Act exceeds the commerce power because it neither regulates commercial activity nor requires a connection between the gun possession and interstate commerce.</t>
+        </is>
+      </c>
+      <c r="I124" s="99" t="inlineStr">
+        <is>
+          <t>Congress may regulate (1) the use of the channels of interstate commerce; (2) the instrumentalities of interstate commerce, or persons or things in interstate commerce; and (3) activities that substantially affect interstate commerce. Under the third, the Court looks at whether the activity is economic, whether there is a jurisdictional element, whether there are findings, and how attenuated the link is.</t>
+        </is>
+      </c>
+      <c r="J124" s="99" t="inlineStr">
+        <is>
+          <t>• The test is 'substantially affects,' not merely 'affects'; only category 3 could apply
+• Rejected the government's cost-of-crime and national-productivity theories as 'pil[ing] inference upon inference' toward a general police power
+• Lopez overruled nothing; Congress normally need not make findings
+• Kennedy: stare decisis bars a return to an 18th-century view; federalism is the Framers' 'unique contribution.' Thomas: original 'commerce' means buying, selling, bartering and transport. Breyer: cumulative effect plus rational basis. Souter: 'Not every epochal case has come in epochal trappings'</t>
+        </is>
+      </c>
+      <c r="K124" s="99" t="inlineStr">
+        <is>
+          <t>Lopez is the first modern limit on the commerce power. Fixes: add a jurisdictional element (Clinton's 1996 amendment) or use spending (Dole); counterpoint is Raich's broad reading for economic schemes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="105" t="inlineStr">
+        <is>
+          <t>Tenth Amendment &amp; federalism</t>
+        </is>
+      </c>
+      <c r="B125" s="99" t="inlineStr">
+        <is>
+          <t>State sovereign immunity</t>
+        </is>
+      </c>
+      <c r="C125" s="99" t="n">
+        <v>4</v>
+      </c>
+      <c r="D125" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E125" s="100" t="inlineStr">
+        <is>
+          <t>Alden v. Maine (1999)</t>
+        </is>
+      </c>
+      <c r="F125" s="99" t="inlineStr">
+        <is>
+          <t>State sovereign immunity</t>
+        </is>
+      </c>
+      <c r="G125" s="99" t="inlineStr">
+        <is>
+          <t>Maine probation officers sued the State for FLSA overtime. After Seminole Tribe ended their federal suit, they refiled in Maine's own courts, which dismissed on sovereign immunity.</t>
+        </is>
+      </c>
+      <c r="H125" s="99" t="inlineStr">
+        <is>
+          <t>Congress's Article I powers do not include power to subject nonconsenting States to private damages suits in their own courts, and Maine had not consented.</t>
+        </is>
+      </c>
+      <c r="I125" s="99" t="inlineStr">
+        <is>
+          <t>State immunity is a fundamental aspect of sovereignty retained at ratification, except as altered by the plan of the Convention or certain amendments; the Eleventh Amendment 'confirmed rather than established' it. It does not bar consented suits, suits by the United States or other States, valid Section 5 abrogation, suits against municipalities, Ex parte Young injunctions against officers, or individual-capacity damages against officers.</t>
+        </is>
+      </c>
+      <c r="J125" s="99" t="inlineStr">
+        <is>
+          <t>• 'Eleventh Amendment immunity' is 'something of a misnomer': immunity comes from structure, so it reaches state courts even though the text limits only 'the Judicial power of the United States'
+• Suits by the United States differ because they require 'political responsibility' for each suit; here the U.S. did not send 'even a single attorney to Maine'
+• Neither the Supremacy Clause nor the Necessary and Proper Clause overrides immunity: a law violating state sovereignty is not 'proper'
+• Souter dissent: the immunity rests on bad history and resembles Lochner-era doctrine, 'probably as fleeting'; Torres later narrowed Alden's Article I statement</t>
+        </is>
+      </c>
+      <c r="K125" s="99" t="inlineStr">
+        <is>
+          <t>Alden is the high-water mark of the dignity rationale: 'Congress has vast power but not all power.' Use its list of remaining avenues (U.S. suits, Young, officer damages) for hypos; counterpoint is Torres, which lets Article I war powers override immunity in state court.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="105" t="inlineStr">
+        <is>
+          <t>Tenth Amendment &amp; federalism</t>
+        </is>
+      </c>
+      <c r="B126" s="101" t="inlineStr">
+        <is>
+          <t>Foundations &amp; interpretation</t>
+        </is>
+      </c>
+      <c r="C126" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="D126" s="101" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="E126" s="102" t="inlineStr">
+        <is>
+          <t>Federalist No. 15 (1787)</t>
+        </is>
+      </c>
+      <c r="F126" s="101" t="inlineStr">
+        <is>
+          <t>Federalism: Articles' defects</t>
+        </is>
+      </c>
+      <c r="G126" s="101" t="inlineStr">
+        <is>
+          <t>Hamilton's critique of the Articles of Confederation, under which Congress acted through requisitions on the states.</t>
+        </is>
+      </c>
+      <c r="H126" s="101" t="inlineStr">
+        <is>
+          <t>The "great and radical vice" of the Confederation is legislation for states in their collective capacities rather than for individuals.</t>
+        </is>
+      </c>
+      <c r="I126" s="101" t="inlineStr">
+        <is>
+          <t>A law needs a sanction; against states the only sanction is arms, so a government must act directly on individuals to be enforceable through courts.</t>
+        </is>
+      </c>
+      <c r="J126" s="101" t="inlineStr">
+        <is>
+          <t>• Vice = legislating for STATES, not individuals
+• Requisitions were "mere recommendations" states obeyed at their option
+• Two sanctions: coercion of the magistracy (courts) or coercion of arms; against states every breach means war</t>
+        </is>
+      </c>
+      <c r="K126" s="101" t="inlineStr">
+        <is>
+          <t>Supports why the Constitution gives the national government power over individuals; contrast Brutus's consolidation fears.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="105" t="inlineStr">
+        <is>
+          <t>Tenth Amendment &amp; federalism</t>
+        </is>
+      </c>
+      <c r="B127" s="101" t="inlineStr">
+        <is>
+          <t>Foundations &amp; interpretation; Necessary &amp; Proper / implied powers</t>
+        </is>
+      </c>
+      <c r="C127" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="D127" s="101" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="E127" s="102" t="inlineStr">
+        <is>
+          <t>Brutus No. 1 (1787)</t>
+        </is>
+      </c>
+      <c r="F127" s="101" t="inlineStr">
+        <is>
+          <t>Anti-Federalist: consolidation</t>
+        </is>
+      </c>
+      <c r="G127" s="101" t="inlineStr">
+        <is>
+          <t>Anti-Federalist essay asking whether the 13 states should be reduced to one great republic.</t>
+        </is>
+      </c>
+      <c r="H127" s="101" t="inlineStr">
+        <is>
+          <t>The Constitution approaches so near consolidation that it must "certainly and infallibly terminate in it."</t>
+        </is>
+      </c>
+      <c r="I127" s="101" t="inlineStr">
+        <is>
+          <t>A government of the proposed scope will absorb the states.</t>
+        </is>
+      </c>
+      <c r="J127" s="101" t="inlineStr">
+        <is>
+          <t>• Not a perfect consolidation, but it will end in one
+• Counterpoint to Federalist No. 45</t>
+        </is>
+      </c>
+      <c r="K127" s="101" t="inlineStr">
+        <is>
+          <t>Use as the counterpoint to Madison's few-and-defined federal powers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="105" t="inlineStr">
+        <is>
+          <t>Tenth Amendment &amp; federalism</t>
+        </is>
+      </c>
+      <c r="B128" s="101" t="inlineStr">
+        <is>
+          <t>Foundations &amp; interpretation; Necessary &amp; Proper / implied powers</t>
+        </is>
+      </c>
+      <c r="C128" s="101" t="n">
+        <v>8</v>
+      </c>
+      <c r="D128" s="101" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="E128" s="102" t="inlineStr">
+        <is>
+          <t>Brutus No. 1 (1787)</t>
+        </is>
+      </c>
+      <c r="F128" s="101" t="inlineStr">
+        <is>
+          <t>Anti-Federalist critique</t>
+        </is>
+      </c>
+      <c r="G128" s="101" t="inlineStr">
+        <is>
+          <t>Anti-Federalist essay in the New York Journal asking whether the States should be consolidated into one great republic.</t>
+        </is>
+      </c>
+      <c r="H128" s="101" t="inlineStr">
+        <is>
+          <t>No holding; argues the Constitution approaches so near consolidation that it "must, if executed, certainly and infallibly terminate in it."</t>
+        </is>
+      </c>
+      <c r="I128" s="101" t="inlineStr">
+        <is>
+          <t>The Necessary and Proper and Supremacy Clauses make the government "a complete one, and not a confederation"; the clause "may receive a construction to justify the passing almost any law" and could "entirely abolish the State legislatures."</t>
+        </is>
+      </c>
+      <c r="J128" s="101" t="inlineStr">
+        <is>
+          <t>• Objected to the breadth of federal power, not its weakness
+• Example: Congress could repeal a state revenue law as obstructing a federal tax it deems necessary
+• Predicted that powers reserved to the States would "very soon be annihilated"
+• Willett's Bonner concurrence invokes Brutus's fear of expansion by implication</t>
+        </is>
+      </c>
+      <c r="K128" s="101" t="inlineStr">
+        <is>
+          <t>The Anti-Federalist prediction against which to test McCulloch and the modern commerce cases; cite it for the argument that implied powers lead to consolidation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="105" t="inlineStr">
+        <is>
+          <t>Tenth Amendment &amp; federalism</t>
+        </is>
+      </c>
+      <c r="B129" s="101" t="inlineStr">
+        <is>
+          <t>Foundations &amp; interpretation</t>
+        </is>
+      </c>
+      <c r="C129" s="101" t="n">
+        <v>1</v>
+      </c>
+      <c r="D129" s="101" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="E129" s="102" t="inlineStr">
+        <is>
+          <t>Federalist No. 45 (1788)</t>
+        </is>
+      </c>
+      <c r="F129" s="101" t="inlineStr">
+        <is>
+          <t>Federalism: enumerated powers</t>
+        </is>
+      </c>
+      <c r="G129" s="101" t="inlineStr">
+        <is>
+          <t>Madison answers fears that the new government will swallow the states.</t>
+        </is>
+      </c>
+      <c r="H129" s="101" t="inlineStr">
+        <is>
+          <t>Federal powers are "few and defined"; state powers are "numerous and indefinite."</t>
+        </is>
+      </c>
+      <c r="I129" s="101" t="inlineStr">
+        <is>
+          <t>Federal power operates mainly on external objects (war, peace, foreign commerce); states govern lives, liberties and property and internal order.</t>
+        </is>
+      </c>
+      <c r="J129" s="101" t="inlineStr">
+        <is>
+          <t>• Change is less the addition of NEW powers than invigoration of ORIGINAL powers
+• Commerce regulation is the one new power, which few oppose
+• Federal government most important in war; states in peace</t>
+        </is>
+      </c>
+      <c r="K129" s="101" t="inlineStr">
+        <is>
+          <t>Cite for the limited-enumerated-powers view of federalism; Brutus No. 1 is the counterpoint predicting consolidation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="105" t="inlineStr">
+        <is>
+          <t>Tenth Amendment &amp; federalism</t>
+        </is>
+      </c>
+      <c r="B130" s="101" t="inlineStr">
+        <is>
+          <t>State sovereign immunity</t>
+        </is>
+      </c>
+      <c r="C130" s="101" t="n">
+        <v>4</v>
+      </c>
+      <c r="D130" s="101" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="E130" s="102" t="inlineStr">
+        <is>
+          <t>The Federalist No. 63 (1788)</t>
+        </is>
+      </c>
+      <c r="F130" s="101" t="inlineStr">
+        <is>
+          <t>Senate and state sovereignty</t>
+        </is>
+      </c>
+      <c r="G130" s="101" t="inlineStr">
+        <is>
+          <t>Madison's essay on the Senate.</t>
+        </is>
+      </c>
+      <c r="H130" s="101" t="inlineStr">
+        <is>
+          <t>Not a decision.</t>
+        </is>
+      </c>
+      <c r="I130" s="101" t="inlineStr">
+        <is>
+          <t>Election of senators by state legislatures gives the States an agency in the federal government, 'a convenient link between the two systems.' Equal state votes in the Senate recognize and preserve the States' 'residuary sovereignty.'</t>
+        </is>
+      </c>
+      <c r="J130" s="101" t="inlineStr">
+        <is>
+          <t>• Equal vote is 'at once a constitutional recognition of the portion of sovereignty remaining in the individual states, and an instrument for preserving that residuary sovereignty'
+• The 'diseases' governments are most liable to: 'the facility and excess of law-making'</t>
+        </is>
+      </c>
+      <c r="K130" s="101" t="inlineStr">
+        <is>
+          <t>Use it for the political safeguards of federalism: the States were protected through their role in forming the federal government.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="105" t="inlineStr">
+        <is>
+          <t>Tenth Amendment &amp; federalism</t>
+        </is>
+      </c>
+      <c r="B131" s="101" t="inlineStr">
+        <is>
+          <t>Necessary &amp; Proper / implied powers</t>
+        </is>
+      </c>
+      <c r="C131" s="101" t="n">
+        <v>8</v>
+      </c>
+      <c r="D131" s="101" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="E131" s="102" t="inlineStr">
+        <is>
+          <t>Tenth Amendment Debate, House of Representatives (1789)</t>
+        </is>
+      </c>
+      <c r="F131" s="101" t="inlineStr">
+        <is>
+          <t>Tenth Amendment; implied powers</t>
+        </is>
+      </c>
+      <c r="G131" s="101" t="inlineStr">
+        <is>
+          <t>In August 1789 the House considered the proposition that became the Tenth Amendment; Tucker, and later Gerry, moved to reserve all powers "not expressly delegated."</t>
+        </is>
+      </c>
+      <c r="H131" s="101" t="inlineStr">
+        <is>
+          <t>No holding; the House rejected "expressly" and adopted the text with "or to the people" and "to the United States" added.</t>
+        </is>
+      </c>
+      <c r="I131" s="101" t="inlineStr">
+        <is>
+          <t>The Tenth Amendment reserves powers not delegated, not powers not expressly delegated, so whether a power is delegated depends on fair construction, as McCulloch later held, unlike the Articles of Confederation's "expressly" rule.</t>
+        </is>
+      </c>
+      <c r="J131" s="101" t="inlineStr">
+        <is>
+          <t>• Madison: it is impossible to confine a government to express powers unless the Constitution recounted "every minutiae"
+• Sherman: corporate bodies possess all powers incident to their corporate capacity without express statement
+• "Expressly" had been moved in the Virginia convention by opponents of ratification and given up
+• Professor's response to King's claim that the Amendment is "a clear delineation" of power: "Is it really this easy?"</t>
+        </is>
+      </c>
+      <c r="K131" s="101" t="inlineStr">
+        <is>
+          <t>Use to rebut any argument that the Tenth Amendment limits Congress to express powers; it links directly to McCulloch's reading of the omitted word.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="105" t="inlineStr">
+        <is>
+          <t>Tenth Amendment &amp; federalism</t>
+        </is>
+      </c>
+      <c r="B132" s="101" t="inlineStr">
+        <is>
+          <t>Commerce Clause</t>
+        </is>
+      </c>
+      <c r="C132" s="101" t="n">
+        <v>6</v>
+      </c>
+      <c r="D132" s="101" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="E132" s="102" t="inlineStr">
+        <is>
+          <t>Clinton's response to Lopez (1995) and the 1996 amendment</t>
+        </is>
+      </c>
+      <c r="F132" s="101" t="inlineStr">
+        <is>
+          <t>Commerce Clause: legislative response</t>
+        </is>
+      </c>
+      <c r="G132" s="101" t="inlineStr">
+        <is>
+          <t>After Lopez, President Clinton responded in a radio address and a message to Congress, and Congress later amended the Gun-Free School Zones Act.</t>
+        </is>
+      </c>
+      <c r="H132" s="101" t="inlineStr">
+        <is>
+          <t>Not a decision.</t>
+        </is>
+      </c>
+      <c r="I132" s="101" t="inlineStr">
+        <is>
+          <t>Clinton directed the Attorney General to report within a week, suggested tying federal funds to state school-zone gun bans, and sent Congress a bill adding a jurisdictional element. The 1996 amendment made it unlawful to possess 'a firearm that has moved in or that otherwise affects interstate or foreign commerce' in a school zone.</t>
+        </is>
+      </c>
+      <c r="J132" s="101" t="inlineStr">
+        <is>
+          <t>• Both fixes track Lopez: a jurisdictional element (category 3 nexus) and a spending-power route (Dole)
+• Reno: little prosecutorial impact because most guns have moved in commerce; no need to prove the defendant knew of the commerce link
+• CRS: the Supreme Court has not revisited the amended law; lower courts generally uphold it</t>
+        </is>
+      </c>
+      <c r="K132" s="101" t="inlineStr">
+        <is>
+          <t>Use it to show how Congress can respond to Lopez: add a jurisdictional hook or condition federal funds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="105" t="inlineStr">
+        <is>
+          <t>Tenth Amendment &amp; federalism</t>
+        </is>
+      </c>
+      <c r="B133" s="103" t="inlineStr">
+        <is>
+          <t>Foundations &amp; interpretation</t>
+        </is>
+      </c>
+      <c r="C133" s="103" t="n">
+        <v>1</v>
+      </c>
+      <c r="D133" s="103" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+      <c r="E133" s="104" t="inlineStr">
+        <is>
+          <t>Articles of Confederation (1781)</t>
+        </is>
+      </c>
+      <c r="F133" s="103" t="inlineStr">
+        <is>
+          <t>Founding structure</t>
+        </is>
+      </c>
+      <c r="G133" s="103" t="inlineStr">
+        <is>
+          <t>The first national charter: a league of sovereign states with a weak Congress.</t>
+        </is>
+      </c>
+      <c r="H133" s="103" t="inlineStr">
+        <is>
+          <t>Each state keeps its sovereignty and every power not "expressly delegated" (Art. II).</t>
+        </is>
+      </c>
+      <c r="I133" s="103" t="inlineStr">
+        <is>
+          <t>A "firm league of friendship"; one vote per state; Congress could not tax (states raised money); major acts needed nine states; amendment required unanimity.</t>
+        </is>
+      </c>
+      <c r="J133" s="103" t="inlineStr">
+        <is>
+          <t>• "Expressly delegated" in Art. II is the word the Tenth Amendment OMITS (McCulloch's point)
+• No federal taxing power and legislation for states, not individuals, is Federalist 15's "radical vice"
+• Unanimity for amendments</t>
+        </is>
+      </c>
+      <c r="K133" s="103" t="inlineStr">
+        <is>
+          <t>Background for why the Constitution was needed (Federalist 15) and for McCulloch's reading of the Tenth Amendment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="105" t="inlineStr">
+        <is>
+          <t>Section 5 enforcement</t>
+        </is>
+      </c>
+      <c r="B134" s="99" t="inlineStr">
+        <is>
+          <t>State sovereign immunity</t>
+        </is>
+      </c>
+      <c r="C134" s="99" t="n">
+        <v>9</v>
+      </c>
+      <c r="D134" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E134" s="100" t="inlineStr">
+        <is>
+          <t>City of Boerne v. Flores (1997)</t>
+        </is>
+      </c>
+      <c r="F134" s="99" t="inlineStr">
+        <is>
+          <t>Section 5 enforcement power</t>
+        </is>
+      </c>
+      <c r="G134" s="99" t="inlineStr">
+        <is>
+          <t>Boerne, Texas, relying on a historic-preservation ordinance, denied the Archbishop a permit to enlarge St. Peter Catholic Church. The Archbishop sued under RFRA, which Congress passed after Employment Division v. Smith to restore the compelling-interest test against every level of government.</t>
+        </is>
+      </c>
+      <c r="H134" s="99" t="inlineStr">
+        <is>
+          <t>RFRA exceeds Congress's power under § 5 of the Fourteenth Amendment as applied to the States because it makes a substantive change in constitutional protections rather than enforcing them.</t>
+        </is>
+      </c>
+      <c r="I134" s="99" t="inlineStr">
+        <is>
+          <t>Congruence and proportionality: "There must be a congruence and proportionality between the injury to be prevented or remedied and the means adopted to that end." Section 5 lets Congress remedy and prevent violations, even by barring some constitutional conduct, but not redefine the right: "Congress does not enforce a constitutional right by changing what the right is."</t>
+        </is>
+      </c>
+      <c r="J134" s="99" t="inlineStr">
+        <is>
+          <t>• Background: Sherbert required a compelling interest for substantial burdens; Smith held "neutral, generally applicable laws may be applied to religious practices" without one, partly because courts cannot judge a belief's centrality; RFRA restored Sherbert and Yoder by statute and added least restrictive means
+• The thin record was not RFRA's "most serious shortcoming"; its sweep was: every government, all laws past and future, no end date, and "the most demanding test known to constitutional law"
+• Contrast the Voting Rights Act measures upheld: targeted regions, discrete laws, bailout, time limits; but termination dates and geographic limits are NOT required
+• The Court interprets the Constitution in cases: "it is this Court's precedent, not RFRA, which must control"; the Civil Rights Cases treat § 5 as corrective, not "general legislation"</t>
+        </is>
+      </c>
+      <c r="K134" s="99" t="inlineStr">
+        <is>
+          <t>The central limit on Congress's § 5 power and a judicial-supremacy statement in the Marbury line; counter with Kennedy's concession that Congress has a duty to interpret the Constitution and gets wide latitude in choosing remedies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="105" t="inlineStr">
+        <is>
+          <t>Section 5 enforcement</t>
+        </is>
+      </c>
+      <c r="B135" s="99" t="inlineStr">
+        <is>
+          <t>Commerce Clause</t>
+        </is>
+      </c>
+      <c r="C135" s="99" t="n">
+        <v>6</v>
+      </c>
+      <c r="D135" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E135" s="100" t="inlineStr">
+        <is>
+          <t>United States v. Morrison (2000)</t>
+        </is>
+      </c>
+      <c r="F135" s="99" t="inlineStr">
+        <is>
+          <t>Commerce Clause limits</t>
+        </is>
+      </c>
+      <c r="G135" s="99" t="inlineStr">
+        <is>
+          <t>A Virginia Tech student alleged two football players raped her and sued them under the Violence Against Women Act's federal civil remedy for gender-motivated violence.</t>
+        </is>
+      </c>
+      <c r="H135" s="99" t="inlineStr">
+        <is>
+          <t>The civil remedy exceeds Congress's power under both the Commerce Clause and Section 5 of the Fourteenth Amendment.</t>
+        </is>
+      </c>
+      <c r="I135" s="99" t="inlineStr">
+        <is>
+          <t>Congress may not regulate noneconomic, violent criminal conduct based solely on its aggregate effect on interstate commerce. Congressional findings are not sufficient by themselves; whether an activity substantially affects commerce is ultimately a judicial question.</t>
+        </is>
+      </c>
+      <c r="J135" s="99" t="inlineStr">
+        <is>
+          <t>• Findings relied on the 'but-for causal chain' Lopez rejected, which would let Congress regulate all violent crime and family law
+• The Court did NOT adopt a categorical rule against aggregating noneconomic activity, but has upheld only economic activity 'thus far'
+• 'The Constitution requires a distinction between what is truly national and what is truly local'; her remedy must come from Virginia
+• Souter dissent: a 'mountain of data' and rational-basis review make the result irreconcilable with precedent; Thomas would scrap the substantial effects test</t>
+        </is>
+      </c>
+      <c r="K135" s="99" t="inlineStr">
+        <is>
+          <t>Morrison confirms Lopez even with extensive findings. For hypos, a jurisdictional hook (e.g., violence against persons traveling in interstate commerce) makes a statute stronger.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="105" t="inlineStr">
+        <is>
+          <t>Section 5 enforcement</t>
+        </is>
+      </c>
+      <c r="B136" s="99" t="inlineStr">
+        <is>
+          <t>State sovereign immunity</t>
+        </is>
+      </c>
+      <c r="C136" s="99" t="n">
+        <v>5</v>
+      </c>
+      <c r="D136" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E136" s="100" t="inlineStr">
+        <is>
+          <t>Allen v. Cooper (2020)</t>
+        </is>
+      </c>
+      <c r="F136" s="99" t="inlineStr">
+        <is>
+          <t>Sovereign immunity: abrogation</t>
+        </is>
+      </c>
+      <c r="G136" s="99" t="inlineStr">
+        <is>
+          <t>A videographer who documented the Blackbeard shipwreck owned by North Carolina sued the State after it posted five of his videos online and used one of his photos in a newsletter, relying on the Copyright Remedy Clarification Act's abrogation of immunity.</t>
+        </is>
+      </c>
+      <c r="H136" s="99" t="inlineStr">
+        <is>
+          <t>The CRCA did not validly abrogate state immunity: the Intellectual Property Clause cannot support abrogation, and Section 5 could not on this legislative record.</t>
+        </is>
+      </c>
+      <c r="I136" s="99" t="inlineStr">
+        <is>
+          <t>Abrogation requires (1) unequivocal statutory language and (2) a valid constitutional authority. Article I generally cannot be used to circumvent state immunity (Seminole Tribe; Florida Prepaid).</t>
+        </is>
+      </c>
+      <c r="J136" s="99" t="inlineStr">
+        <is>
+          <t>• 'Florida Prepaid all but prewrote our decision today'; overruling it needed a 'special justification' that Allen did not offer
+• Katz is 'bankruptcy exceptionalism,' a 'good-for-one-clause-only holding': the Bankruptcy Clause itself abrogated in the plan of the Convention
+• Thomas: no 'special justification' requirement; a 'demonstrably erroneous' precedent must be corrected, but Florida Prepaid was not; Katz is 'not good for even that clause'
+• Clear statement was undisputed; the case turned on the source of power</t>
+        </is>
+      </c>
+      <c r="K136" s="99" t="inlineStr">
+        <is>
+          <t>Allen sets the two-step abrogation test and treats Katz as unique. Counterpoint: Torres and Kagan's concurrence ('PennEast proved me wrong') widened the plan-of-the-Convention route.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="105" t="inlineStr">
+        <is>
+          <t>Section 5 enforcement</t>
+        </is>
+      </c>
+      <c r="B137" s="99" t="inlineStr">
+        <is>
+          <t>State sovereign immunity</t>
+        </is>
+      </c>
+      <c r="C137" s="99" t="n">
+        <v>9</v>
+      </c>
+      <c r="D137" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E137" s="100" t="inlineStr">
+        <is>
+          <t>Allen v. Cooper (2020) (Section 5)</t>
+        </is>
+      </c>
+      <c r="F137" s="99" t="inlineStr">
+        <is>
+          <t>Section 5: abrogation for copyright</t>
+        </is>
+      </c>
+      <c r="G137" s="99" t="inlineStr">
+        <is>
+          <t>Same case as Week 5 (Blackbeard's ship Queen Anne's Revenge; North Carolina posted the videographer's copyrighted footage). Here the reader reprints the Section 5 part: could the Copyright Remedy Clarification Act (CRCA) abrogate state immunity under §5?</t>
+        </is>
+      </c>
+      <c r="H137" s="99" t="inlineStr">
+        <is>
+          <t>No. Under Florida Prepaid, the CRCA fails congruence and proportionality, so it is not valid §5 legislation. Affirmed.</t>
+        </is>
+      </c>
+      <c r="I137" s="99" t="inlineStr">
+        <is>
+          <t>An abrogation is valid under §5 only if it is tailored to remedy or prevent conduct §1 actually forbids. Infringement violates due process only if it is intentional (or reckless) AND the State offers no adequate remedy. The record showed about a dozen possible state infringements, mostly innocent, and nothing on state remedies, while the CRCA covered every infringement suit: "indiscriminate scope" out of proportion to any due process problem.</t>
+        </is>
+      </c>
+      <c r="J137" s="99" t="inlineStr">
+        <is>
+          <t>• §5, unlike almost all of Article I, can abrogate (Fitzpatrick)
+• Negligent acts don't "deprive" property (Daniels)
+• Oman Report: only 12 examples, 2 intentional; Oman said States are "respectful of the copyright law"
+• Florida Prepaid (patents) "all but prewrote" the result
+• Congress may try again with a tailored law and a better record: "bring digital Blackbeards to justice"
+• Thomas concurred in part; Breyer (with Ginsburg) concurred in the judgment (opinions omitted in reader)</t>
+        </is>
+      </c>
+      <c r="K137" s="99" t="inlineStr">
+        <is>
+          <t>Applies Boerne in the immunity setting: map the right (intentional infringement + no state remedy), the record, and the statute's scope. Pairs with the Week 5 Article I holding (Intellectual Property Clause can't abrogate).</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="105" t="inlineStr">
+        <is>
+          <t>Section 5 enforcement</t>
+        </is>
+      </c>
+      <c r="B138" s="103" t="inlineStr">
+        <is>
+          <t>State sovereign immunity</t>
+        </is>
+      </c>
+      <c r="C138" s="103" t="n">
+        <v>9</v>
+      </c>
+      <c r="D138" s="103" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+      <c r="E138" s="104" t="inlineStr">
+        <is>
+          <t>CRS, Federalism-Based Limitations (R45323): Civil War Amendments / Section 5</t>
+        </is>
+      </c>
+      <c r="F138" s="103" t="inlineStr">
+        <is>
+          <t>Section 5 enforcement: overview</t>
+        </is>
+      </c>
+      <c r="G138" s="103" t="inlineStr">
+        <is>
+          <t>CRS overview of Congress's power to enforce the 13th, 14th and 15th Amendments.</t>
+        </is>
+      </c>
+      <c r="H138" s="103" t="inlineStr">
+        <is>
+          <t>N/A (overview).</t>
+        </is>
+      </c>
+      <c r="I138" s="103" t="inlineStr">
+        <is>
+          <t>Each Civil War Amendment gives Congress power to enforce it 'by appropriate legislation,' including prophylactic laws that bar some constitutional conduct (e.g., 13th: 'badges and incidents of slavery'; 15th: literacy-test bans). Two limits on §5: (1) STATE ACTION only, no purely private conduct (Civil Rights Cases 1883; Morrison); (2) REMEDIAL only: congruence and proportionality (Boerne). Courts apply a 3-step test: identify the right precisely; ask whether Congress found a history and pattern of state violations; compare the law's scope to that record.</t>
+        </is>
+      </c>
+      <c r="J138" s="103" t="inlineStr">
+        <is>
+          <t>• Most Boerne cases involve abrogating state sovereign immunity (Congress usually can't use Article I to abrogate)
+• ADA Title I (employment): no valid abrogation (Garrett: no pattern; disability = rational basis)
+• ADA Title II (courthouse access): valid (Lane: pattern + fundamental right + limited remedy)
+• FMLA family-care leave: valid (sex discrimination gets heightened scrutiny); self-care leave: not
+• More deference for suspect classes/fundamental rights
+• Congruence and proportionality is needed only for PROPHYLACTIC laws; a remedy for actual 14th Amendment violations can abrogate without it
+• Practical advice: build a record; draft narrowly</t>
+        </is>
+      </c>
+      <c r="K138" s="103" t="inlineStr">
+        <is>
+          <t>Use to organize any §5 answer: state action, then congruence and proportionality in three steps, then the type of right (heightened scrutiny vs. rational basis). Links Boerne to Allen v. Cooper and to the Eleventh Amendment unit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="105" t="inlineStr">
+        <is>
+          <t>Section 5 enforcement</t>
+        </is>
+      </c>
+      <c r="B139" s="103" t="n"/>
+      <c r="C139" s="103" t="n">
+        <v>9</v>
+      </c>
+      <c r="D139" s="103" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+      <c r="E139" s="104" t="inlineStr">
+        <is>
+          <t>Fourteenth Amendment, Sections 1 and 5 (text)</t>
+        </is>
+      </c>
+      <c r="F139" s="103" t="inlineStr">
+        <is>
+          <t>Section 5 enforcement: text</t>
+        </is>
+      </c>
+      <c r="G139" s="103" t="inlineStr">
+        <is>
+          <t>Constitutional text reprinted in the reader.</t>
+        </is>
+      </c>
+      <c r="H139" s="103" t="inlineStr">
+        <is>
+          <t>N/A (text).</t>
+        </is>
+      </c>
+      <c r="I139" s="103" t="inlineStr">
+        <is>
+          <t>§1: citizenship; no State may abridge privileges or immunities, deprive any person of life, liberty or property without due process, or deny equal protection. §5: "The Congress shall have the power to enforce, by appropriate legislation, the provisions of this article."</t>
+        </is>
+      </c>
+      <c r="J139" s="103" t="inlineStr">
+        <is>
+          <t>• §1 restrains STATES (source of the state action requirement)
+• §5 is the power; "appropriate" and "enforce" are the words Boerne and Allen interpret</t>
+        </is>
+      </c>
+      <c r="K139" s="103" t="inlineStr">
+        <is>
+          <t>Quote §5's 'enforce' to frame Boerne: enforcing is not redefining.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="105" t="inlineStr">
+        <is>
+          <t>Dormant Commerce Clause</t>
+        </is>
+      </c>
+      <c r="B140" s="99" t="inlineStr">
+        <is>
+          <t>Commerce Clause</t>
+        </is>
+      </c>
+      <c r="C140" s="99" t="n">
+        <v>5</v>
+      </c>
+      <c r="D140" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E140" s="100" t="inlineStr">
+        <is>
+          <t>Gibbons v. Ogden (1824)</t>
+        </is>
+      </c>
+      <c r="F140" s="99" t="inlineStr">
+        <is>
+          <t>Commerce Clause</t>
+        </is>
+      </c>
+      <c r="G140" s="99" t="inlineStr">
+        <is>
+          <t>New York laws granted an exclusive steamboat privilege, enforced by a New York decree against the appellant, who claimed the laws conflicted with the commerce power and with an act of Congress licensing vessels.</t>
+        </is>
+      </c>
+      <c r="H140" s="99" t="inlineStr">
+        <is>
+          <t>The New York laws, as applied to vessels licensed under the federal act, collide with federal law and must yield under the Supremacy Clause.</t>
+        </is>
+      </c>
+      <c r="I140" s="99" t="inlineStr">
+        <is>
+          <t>Commerce is 'traffic, but it is something more: it is intercourse,' including navigation. 'Among the several States' means 'intermingled with' and reaches commerce that concerns more States than one, but not the 'completely internal commerce of a State.' The power to regulate is 'complete in itself' and limited mainly by political checks.</t>
+        </is>
+      </c>
+      <c r="J140" s="99" t="inlineStr">
+        <is>
+          <t>• Rejected strict construction; 'the enumeration presupposes something not enumerated'
+• Restraints on Congress are political: the people's influence at elections, not courts
+• Marshall saw 'great force' in the exclusive-power argument but did not rest on it; Justice Johnson concurred on the ground that the commerce power is exclusive
+• Licensed steamboats can no more be restrained 'than if they were wafted on their voyage by the winds'</t>
+        </is>
+      </c>
+      <c r="K140" s="99" t="inlineStr">
+        <is>
+          <t>Gibbons is the broad starting point that Wickard says was 'restored' and Lopez cites for limits ('the enumeration presupposes something not enumerated'). Use it both ways.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="105" t="inlineStr">
+        <is>
+          <t>Dormant Commerce Clause</t>
+        </is>
+      </c>
+      <c r="B141" s="99" t="n"/>
+      <c r="C141" s="99" t="n">
+        <v>8</v>
+      </c>
+      <c r="D141" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E141" s="100" t="inlineStr">
+        <is>
+          <t>Dean Milk Co. v. Madison (1951)</t>
+        </is>
+      </c>
+      <c r="F141" s="99" t="inlineStr">
+        <is>
+          <t>Dormant Commerce Clause: discrimination</t>
+        </is>
+      </c>
+      <c r="G141" s="99" t="inlineStr">
+        <is>
+          <t>Madison, Wisconsin barred selling milk as pasteurized unless it was processed at an approved plant within five miles of the city center. Dean Milk, an Illinois company selling Grade A milk from plants 65 and 85 miles away, was denied a license solely because of that distance.</t>
+        </is>
+      </c>
+      <c r="H141" s="99" t="inlineStr">
+        <is>
+          <t>The five-mile rule plainly discriminates against interstate commerce and is invalid because reasonable nondiscriminatory alternatives could protect health.</t>
+        </is>
+      </c>
+      <c r="I141" s="99" t="inlineStr">
+        <is>
+          <t>A locality may not discriminate against interstate commerce, even to protect health and safety, "if reasonable nondiscriminatory alternatives, adequate to conserve legitimate local interests, are available." One State "may not place itself in a position of economic isolation" (Baldwin v. Seelig).</t>
+        </is>
+      </c>
+      <c r="J141" s="99" t="inlineStr">
+        <is>
+          <t>• Alternatives: inspect distant sources and charge importers the actual cost, or rely on producing-area ratings under the Public Health Service Model Milk Ordinance
+• A law is not valid just because it "professes to be a health measure," or the Clause would bite only when a State "artlessly discloses" discriminatory purpose
+• Immaterial that in-state milk from outside the Madison area was also excluded
+• Madison's own Health Commissioner testified that either approach would adequately protect consumers</t>
+        </is>
+      </c>
+      <c r="K141" s="99" t="inlineStr">
+        <is>
+          <t>Classic statement of the alternatives test for discriminatory laws; contrast Maine v. Taylor, where no adequate nondiscriminatory alternative existed and the ban survived.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="105" t="inlineStr">
+        <is>
+          <t>Dormant Commerce Clause</t>
+        </is>
+      </c>
+      <c r="B142" s="99" t="n"/>
+      <c r="C142" s="99" t="n">
+        <v>8</v>
+      </c>
+      <c r="D142" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E142" s="100" t="inlineStr">
+        <is>
+          <t>Pike v. Bruce Church (1970)</t>
+        </is>
+      </c>
+      <c r="F142" s="99" t="inlineStr">
+        <is>
+          <t>Dormant Commerce Clause: Pike balancing</t>
+        </is>
+      </c>
+      <c r="G142" s="99" t="inlineStr">
+        <is>
+          <t>Arizona ordered Bruce Church to stop shipping its high-quality cantaloupes uncrated from its Parker, Arizona ranch to its packing shed in Blythe, California, and to pack them in Arizona instead. Compliance meant building a $200,000 packing shed for a crop worth $700,000.</t>
+        </is>
+      </c>
+      <c r="H142" s="99" t="inlineStr">
+        <is>
+          <t>The order is invalid because Arizona's "tenuous interest" in having the cantaloupes identified as Arizona's cannot justify requiring an unneeded in-state packing plant.</t>
+        </is>
+      </c>
+      <c r="I142" s="99" t="inlineStr">
+        <is>
+          <t>Pike balancing: "Where the statute regulates even-handedly to effectuate a legitimate local public interest, and its effects on interstate commerce are only incidental, it will be upheld unless the burden imposed on such commerce is clearly excessive in relation to the putative local benefits," considering whether the interest could be promoted as well with a lesser impact. Requiring business operations to be performed in the home State is "virtually per se illegal."</t>
+        </is>
+      </c>
+      <c r="J142" s="99" t="inlineStr">
+        <is>
+          <t>• Rejected the claim that only intrastate packing was regulated: the order requires an out-of-state operation to be performed in-state
+• Protecting growers' reputation is "surely legitimate," but here Arizona wanted a superior product to bear its name to benefit other growers
+• "The nature of that burden is, constitutionally, more significant than its extent"
+• Toomer v. Witsell: if a State cannot require in-state work to promote employment, it cannot do so to enhance reputation</t>
+        </is>
+      </c>
+      <c r="K142" s="99" t="inlineStr">
+        <is>
+          <t>Source of the balancing tier for evenhanded laws; pair with Brown-Forman's two tiers and the CRS sidebar, and note that its in-state processing rule reappears in South-Central Timber.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="105" t="inlineStr">
+        <is>
+          <t>Dormant Commerce Clause</t>
+        </is>
+      </c>
+      <c r="B143" s="99" t="n"/>
+      <c r="C143" s="99" t="n">
+        <v>8</v>
+      </c>
+      <c r="D143" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E143" s="100" t="inlineStr">
+        <is>
+          <t>Reeves, Inc. v. Stake (1980)</t>
+        </is>
+      </c>
+      <c r="F143" s="99" t="inlineStr">
+        <is>
+          <t>Market participant exception</t>
+        </is>
+      </c>
+      <c r="G143" s="99" t="inlineStr">
+        <is>
+          <t>During a cement shortage, South Dakota's state-owned cement plant supplied all South Dakota customers first. Reeves, a Wyoming ready-mix company that bought about 95% of its cement there, had to cut production 76%.</t>
+        </is>
+      </c>
+      <c r="H143" s="99" t="inlineStr">
+        <is>
+          <t>The resident preference is valid because South Dakota acted as a market participant, not a market regulator.</t>
+        </is>
+      </c>
+      <c r="I143" s="99" t="inlineStr">
+        <is>
+          <t>Market participant exception: absent congressional action, a State participating in the market may favor its own citizens (Alexandria Scrap). The Commerce Clause responds principally to state taxes and regulation, not to States acting as traders.</t>
+        </is>
+      </c>
+      <c r="J143" s="99" t="inlineStr">
+        <is>
+          <t>• Reasons: state sovereignty, a trader's right to choose its customers, evenhandedness with private sellers, and Congress is better suited to these questions
+• Cement is not a natural resource; South Dakota did not restrict access to limestone or bar private plants
+• The policy is "protectionist" only in limiting a state program's benefits to those who fund it, like schools and police; Brandeis's "laboratory" quote
+• Powell dissent: the State may meet its own public needs but may not withhold cement from interstate commerce to benefit private in-state businesses</t>
+        </is>
+      </c>
+      <c r="K143" s="99" t="inlineStr">
+        <is>
+          <t>Anchor case for the market participant exception; show its limits with South-Central Timber (downstream conditions) and Camps Newfound (an open-ended tax exemption is not analogous).</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="105" t="inlineStr">
+        <is>
+          <t>Dormant Commerce Clause</t>
+        </is>
+      </c>
+      <c r="B144" s="99" t="n"/>
+      <c r="C144" s="99" t="n">
+        <v>8</v>
+      </c>
+      <c r="D144" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E144" s="100" t="inlineStr">
+        <is>
+          <t>South-Central Timber Dev., Inc. v. Wunnicke (1984)</t>
+        </is>
+      </c>
+      <c r="F144" s="99" t="inlineStr">
+        <is>
+          <t>Market participant; congressional consent</t>
+        </is>
+      </c>
+      <c r="G144" s="99" t="inlineStr">
+        <is>
+          <t>Alaska sold state timber at a reduced price on condition that buyers process it in Alaska ("primary manufacture") before shipping it out. South-Central, which shipped unprocessed logs almost entirely to Japan, sued.</t>
+        </is>
+      </c>
+      <c r="H144" s="99" t="inlineStr">
+        <is>
+          <t>Federal policy for federal timber did not authorize Alaska's rule, and (plurality) Alaska was not shielded as a market participant, so the requirement fell as a virtually per se invalid restraint on export of unprocessed logs.</t>
+        </is>
+      </c>
+      <c r="I144" s="99" t="inlineStr">
+        <is>
+          <t>Congressional authorization of state burdens on commerce must be "unmistakably clear"; a parallel federal policy is not enough. Plurality: a State may burden commerce within the market in which it participates, but may not impose conditions with a substantial regulatory effect in a downstream market.</t>
+        </is>
+      </c>
+      <c r="J144" s="99" t="inlineStr">
+        <is>
+          <t>• Three elements absent in Reeves: foreign commerce, a natural resource, and restrictions on resale
+• Substance over labels: Alaska could not avoid the ruling by keeping title until processing ended
+• Foreign commerce gets more rigorous scrutiny because the Federal Government must "speak with one voice"
+• Rehnquist dissent: the line is "artificial"; Alaska is just paying buyers to process in-state, which it could do by selling only to in-state processors, subsidizing, or processing itself</t>
+        </is>
+      </c>
+      <c r="K144" s="99" t="inlineStr">
+        <is>
+          <t>Marks the outer limit of Reeves and states the clear-statement rule for congressional consent (applied again in Maine v. Taylor); Brennan's concurrence and Rehnquist's dissent both question the doctrine's coherence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="105" t="inlineStr">
+        <is>
+          <t>Dormant Commerce Clause</t>
+        </is>
+      </c>
+      <c r="B145" s="99" t="n"/>
+      <c r="C145" s="99" t="n">
+        <v>8</v>
+      </c>
+      <c r="D145" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E145" s="100" t="inlineStr">
+        <is>
+          <t>Maine v. Taylor (1986)</t>
+        </is>
+      </c>
+      <c r="F145" s="99" t="inlineStr">
+        <is>
+          <t>Dormant Commerce Clause: discrimination</t>
+        </is>
+      </c>
+      <c r="G145" s="99" t="inlineStr">
+        <is>
+          <t>Taylor, a Maine bait dealer, imported 158,000 live golden shiners despite Maine's ban on importing live baitfish and was indicted under the federal Lacey Act. He argued that the Maine ban violated the Commerce Clause.</t>
+        </is>
+      </c>
+      <c r="H145" s="99" t="inlineStr">
+        <is>
+          <t>Maine's ban is valid because it serves legitimate local purposes (keeping out parasites and nonnative species) that could not adequately be served by available nondiscriminatory alternatives.</t>
+        </is>
+      </c>
+      <c r="I145" s="99" t="inlineStr">
+        <is>
+          <t>A law that discriminates on its face or in practical effect survives only if the State shows a legitimate local purpose that cannot be served as well by available nondiscriminatory means (Hughes v. Oklahoma); Tennessee Wine (2019) describes this as requiring narrow tailoring. Laws that burden commerce only incidentally get Pike balancing.</t>
+        </is>
+      </c>
+      <c r="J145" s="99" t="inlineStr">
+        <is>
+          <t>• An "abstract possibility" of developing tests is not an available alternative; a State need not "develop new and unproven means of protection at an uncertain cost"
+• The Lacey Act did not authorize the ban or lower scrutiny; congressional consent must be "unmistakably clear" (South-Central Timber)
+• Whether accepted sampling techniques exist is a fact question reviewed for clear error; an agency's later protectionist remark was weak evidence of intent
+• Stevens dissent ("something fishy"): ambiguity about dangers and alternatives should defeat, not sustain, a discriminatory law (quoting Dean Milk)</t>
+        </is>
+      </c>
+      <c r="K145" s="99" t="inlineStr">
+        <is>
+          <t>The rare discriminatory law that survives; contrast Dean Milk and Philadelphia v. New Jersey, and use "does not elevate free trade above all other values" for the State's side.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="105" t="inlineStr">
+        <is>
+          <t>Dormant Commerce Clause</t>
+        </is>
+      </c>
+      <c r="B146" s="99" t="n"/>
+      <c r="C146" s="99" t="n">
+        <v>8</v>
+      </c>
+      <c r="D146" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E146" s="100" t="inlineStr">
+        <is>
+          <t>Brown-Forman Distillers v. N.Y. State Liquor Authority (1986)</t>
+        </is>
+      </c>
+      <c r="F146" s="99" t="inlineStr">
+        <is>
+          <t>Dormant Commerce Clause framework</t>
+        </is>
+      </c>
+      <c r="G146" s="99" t="inlineStr">
+        <is>
+          <t>The reading excerpts only the Court's statement of doctrine; it gives no facts.</t>
+        </is>
+      </c>
+      <c r="H146" s="99" t="inlineStr">
+        <is>
+          <t>The excerpt omits the disposition; it is assigned for its two-tiered framework.</t>
+        </is>
+      </c>
+      <c r="I146" s="99" t="inlineStr">
+        <is>
+          <t>Two-tiered approach: a law that directly regulates or discriminates against interstate commerce, or favors in-state over out-of-state interests, is generally struck down without further inquiry; a law with only indirect effects that regulates evenhandedly is upheld unless the burden clearly exceeds the local benefits (Pike).</t>
+        </is>
+      </c>
+      <c r="J146" s="99" t="inlineStr">
+        <is>
+          <t>• A statute that by its terms favors in-state producers falls in the tier struck down without further inquiry
+• No clear line separates the virtually per se invalid tier from Pike balancing
+• In either tier "the critical consideration is the overall effect of the statute on both local and interstate activity"</t>
+        </is>
+      </c>
+      <c r="K146" s="99" t="inlineStr">
+        <is>
+          <t>Use as the organizing framework for any dormant Commerce Clause answer: classify the law as discriminatory (Dean Milk, Maine v. Taylor) or evenhanded (Pike), then apply the matching test.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="105" t="inlineStr">
+        <is>
+          <t>Dormant Commerce Clause</t>
+        </is>
+      </c>
+      <c r="B147" s="99" t="n"/>
+      <c r="C147" s="99" t="n">
+        <v>9</v>
+      </c>
+      <c r="D147" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E147" s="100" t="inlineStr">
+        <is>
+          <t>West Lynn Creamery, Inc. v. Healy (1994)</t>
+        </is>
+      </c>
+      <c r="F147" s="99" t="inlineStr">
+        <is>
+          <t>Dormant Commerce Clause: tax + subsidy</t>
+        </is>
+      </c>
+      <c r="G147" s="99" t="inlineStr">
+        <is>
+          <t>Massachusetts dairy farmers were losing market share to cheaper out-of-state producers. The state imposed a 'premium payment' on every dealer's Class I milk sales in Massachusetts (about two-thirds of that milk came from out of state) and paid the whole fund out only to Massachusetts farmers. West Lynn, which bought 97% of its milk from out-of-state farmers, stopped paying and faced license revocation.</t>
+        </is>
+      </c>
+      <c r="H147" s="99" t="inlineStr">
+        <is>
+          <t>The pricing order violates the dormant Commerce Clause. Reversed.</t>
+        </is>
+      </c>
+      <c r="I147" s="99" t="inlineStr">
+        <is>
+          <t>A nondiscriminatory tax combined with a subsidy paid only to in-state producers works like a protective tariff and is unconstitutional, even if each piece would be valid alone. The Court looks at the program's practical purpose and effect, not its form: "The commerce clause forbids discrimination, whether forthright or ingenious." Saving a struggling local industry is the "hallmark" of forbidden protectionism, not a justification.</t>
+        </is>
+      </c>
+      <c r="J147" s="99" t="inlineStr">
+        <is>
+          <t>• Tariff = "paradigmatic" violation; the order "neutraliz[es] advantages belonging to the place of origin" (Baldwin)
+• Like Bacchus (tax exemption), but worse: Massachusetts rebated the tax collected on OUT-of-state milk too
+• Political-process point: pairing tax with subsidy bought off the in-state farmers who would normally lobby against the tax
+• Rejected: (A) each part is lawful; (B) dealers who pay aren't the farmers' competitors (a burden at any point in the stream of commerce counts); (C) only Massachusetts consumers pay; (D) local benefit of saving the industry
+• Pure subsidy from general revenue "ordinarily" OK, but left open (n.15)
+• Scalia (with Thomas), concurring in the judgment: enforce dormant CC only against (1) facial discrimination and (2) laws indistinguishable from ones already struck; ranks four devices: discriminatory tax and exemption = invalid, tax + segregated-fund rebate (this case) = invalid, general-revenue subsidy = valid
+• Rehnquist (with Blackmun), dissenting: subsidies are valid; interest-group analysis is no basis for dormant CC; quotes Brandeis's "laboratory" of the States; warns against a "messianic insistence on a grim sink-or-swim policy of laissez-faire"</t>
+        </is>
+      </c>
+      <c r="K147" s="99" t="inlineStr">
+        <is>
+          <t>Use for disguised discrimination: tax + subsidy = tariff. Pair with Baldwin, Bacchus and Camps; contrast Reeves (market participant) and a general-revenue subsidy. Rehnquist's dissent is a federalism voice, consistent with his Lopez/Morrison stance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="105" t="inlineStr">
+        <is>
+          <t>Dormant Commerce Clause</t>
+        </is>
+      </c>
+      <c r="B148" s="99" t="n"/>
+      <c r="C148" s="99" t="n">
+        <v>9</v>
+      </c>
+      <c r="D148" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E148" s="100" t="inlineStr">
+        <is>
+          <t>Camps Newfound/Owatonna v. Town of Harrison (1997)</t>
+        </is>
+      </c>
+      <c r="F148" s="99" t="inlineStr">
+        <is>
+          <t>Dormant Commerce Clause: tax exemptions</t>
+        </is>
+      </c>
+      <c r="G148" s="99" t="inlineStr">
+        <is>
+          <t>Maine gave charities a full property tax exemption but limited it for charities operated principally for nonresidents. A Christian Science summer camp whose campers were about 95% nonresidents, charging about $400 a week, got no exemption at all.</t>
+        </is>
+      </c>
+      <c r="H148" s="99" t="inlineStr">
+        <is>
+          <t>Maine's charitable exemption, which excluded charities operated principally for nonresidents, violates the dormant Commerce Clause.</t>
+        </is>
+      </c>
+      <c r="I148" s="99" t="inlineStr">
+        <is>
+          <t>A State may not tax an enterprise more heavily because its customers come from other States, and nonprofits get the same protection; calling a discriminatory tax a real estate tax or a charitable exemption does not escape the dormant Commerce Clause.</t>
+        </is>
+      </c>
+      <c r="J148" s="99" t="inlineStr">
+        <is>
+          <t>• A nonprofit camp is "unquestionably engaged in commerce, not only as a purchaser, but also as a provider of goods and services"
+• A real estate tax geared to imported goods would be the "functional equivalent of an import tariff" (West Lynn)
+• Subsidies left open (never "squarely confronted"); exemptions and subsidies differ, and the market participant argument failed because an open-ended exemption is unlike Alexandria Scrap and Reeves
+• Scalia dissent: the doctrine "has drifted far from its moorings"; Thomas dissent: the majority created a "dormant" Necessary and Proper Clause, since land does not move in commerce</t>
+        </is>
+      </c>
+      <c r="K148" s="99" t="inlineStr">
+        <is>
+          <t>Extends the discrimination tier to nonprofits and tax exemptions and shows the limits of the market participant exception; the dissents supply the critique of the whole doctrine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="105" t="inlineStr">
+        <is>
+          <t>Dormant Commerce Clause</t>
+        </is>
+      </c>
+      <c r="B149" s="99" t="n"/>
+      <c r="C149" s="99" t="n">
+        <v>9</v>
+      </c>
+      <c r="D149" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E149" s="100" t="inlineStr">
+        <is>
+          <t>National Pork Producers Council v. Ross (2023)</t>
+        </is>
+      </c>
+      <c r="F149" s="99" t="inlineStr">
+        <is>
+          <t>Dormant Commerce Clause: extraterritoriality; Pike</t>
+        </is>
+      </c>
+      <c r="G149" s="99" t="inlineStr">
+        <is>
+          <t>California's Proposition 12 bans in-state sale of whole pork from breeding pigs confined so tightly they can't lie down, stand up, extend their limbs or turn around. It applies equally to in-state and out-of-state producers, but California imports almost all its pork. Out-of-state producers alleged compliance would raise farm-level costs about 9.2% and conceded no discrimination. Both lower courts dismissed for failure to state a claim.</t>
+        </is>
+      </c>
+      <c r="H149" s="99" t="inlineStr">
+        <is>
+          <t>Affirmed (Ninth Circuit): the complaint fails to state a dormant Commerce Clause claim. All nine Justices reject an "almost per se" rule against state laws with extraterritorial effects (Part III: 5-Justice majority, with Roberts, Alito, Kavanaugh and Jackson agreeing). The Pike claim fails on a fractured vote: IV-C's no-substantial-burden reasoning has only 4 votes, and IV-B's incommensurability reasoning only 3.</t>
+        </is>
+      </c>
+      <c r="I149" s="99" t="inlineStr">
+        <is>
+          <t>Antidiscrimination is the "very core" of the dormant Commerce Clause. Baldwin, Brown-Forman and Healy are protectionism (price-control / price-affirmation) cases, not a ban on laws with out-of-state "practical effects"; almost all state laws have ripple effects. Pike balancing mainly smokes out purposeful discrimination (and protects instrumentalities of transportation). A plaintiff must at least plausibly allege a SUBSTANTIAL burden on interstate commerce; harm to particular firms or to a "particular structure or method of operation" isn't enough (Exxon).</t>
+        </is>
+      </c>
+      <c r="J149" s="99" t="inlineStr">
+        <is>
+          <t>• VOTE MAP (handout), Gorsuch's lead opinion: I Facts (5: NG/CT/SS/EK/ACB)
+• II No discrimination (5)
+• III No per se extraterritoriality rule (5, + JR/SA/BK/KBJ in agreement = 9)
+• IV-A No clear line between discrimination and Pike cases (5; Roberts seemed to agree that many leading dormant CC cases are really about protectionism)
+• IV-B Incommensurability: courts can't weigh economic costs against moral/health benefits ("whether a particular line is longer than a particular rock is heavy") (3: NG/CT/ACB; 6 disagree: SS/EK + JR/SA/BK/KBJ)
+• IV-C Pike pleading requirement not met: no substantial burden pled; Exxon analogy ("That goes for pigs no less than gas stations") (4: NG/CT/SS/EK; 5 disagree: ACB + JR/SA/BK/KBJ)
+• IV-D Federalism + incommensurability (3: NG/CT/ACB; 6 implicitly disagree)
+• V Judgment affirmed (5)
+• IS THE OPINION FRACTURED? Gorsuch/Thomas/Barrett say no (the dissents "seek to characterize today's decision as 'fractured'"); everyone else says yes
+• IS PIKE OVERRULED? No. Kavanaugh: IV-B and IV-D "would essentially overrule the Pike balancing test," but "six Justices of this Court affirmatively retain" it (SS, EK + JR, SA, BK, KBJ)
+• WHAT'S BINDING? Majority parts: I, II, III, IV-A, V. Gorsuch (IV-D) claims the judgment "depends equally" on IV-B and IV-C; Kavanaugh: IV-B and IV-D "are not controlling precedent," but IV-C (4-Justice plurality applying Pike) is controlling for the judgment on the Pike claim
+• FIVE Justices think a substantial burden WAS pled: Barrett ("The complaint plausibly alleges that Proposition 12's costs are pervasive, burdensome, and will be felt primarily (but not exclusively) outside California"; so she doesn't join IV-C, but votes to affirm on incommensurability) + Roberts/Alito/Kavanaugh/Jackson (would remand for Pike balancing)
+• FEDERALISM CUTS BOTH WAYS: Gorsuch/Thomas/Barrett (IV-D): the dissent's test means "one complaint from an unhappy out-of-state producer and—presto—the Constitution would protect the sale of horsemeat" (also fireworks, plastic bags); Kavanaugh: California "undermines federalism" by forcing other States' farmers to follow its laws
+• Kavanaugh also flags Import-Export, Privileges and Immunities and Full Faith and Credit issues</t>
+        </is>
+      </c>
+      <c r="K149" s="99" t="inlineStr">
+        <is>
+          <t>Modern statement that the dormant CC is about discrimination. For a facially neutral law, walk the Truesdell questions (face, effect, purpose), then Pike: substantial burden first, then 'clearly excessive' balancing. Count votes carefully: Pike balancing survives (6 Justices), the extraterritoriality argument is dead (9), and the binding Pike holding is at most IV-C's narrow pleading point. Argue federalism from both sides (horsemeat vs. California dictating farm practices). The Court leaves nationwide policy to Congress under the 'wakeful' Commerce Clause.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="105" t="inlineStr">
+        <is>
+          <t>Dormant Commerce Clause</t>
+        </is>
+      </c>
+      <c r="B150" s="101" t="n"/>
+      <c r="C150" s="101" t="n">
+        <v>8</v>
+      </c>
+      <c r="D150" s="101" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="E150" s="102" t="inlineStr">
+        <is>
+          <t>CRS Legal Sidebar on the Dormant Commerce Clause (2023)</t>
+        </is>
+      </c>
+      <c r="F150" s="101" t="inlineStr">
+        <is>
+          <t>Dormant Commerce Clause overview</t>
+        </is>
+      </c>
+      <c r="G150" s="101" t="inlineStr">
+        <is>
+          <t>Congressional Research Service sidebar on a 2023 Supreme Court decision that narrowed the dormant Commerce Clause and upheld a state animal welfare law.</t>
+        </is>
+      </c>
+      <c r="H150" s="101" t="inlineStr">
+        <is>
+          <t>No holding; summarizes the modern doctrine.</t>
+        </is>
+      </c>
+      <c r="I150" s="101" t="inlineStr">
+        <is>
+          <t>Though the Commerce Clause is a grant to Congress, it is read to bar state laws that unduly restrict interstate commerce when Congress is "dormant." Discriminatory laws driven by economic protectionism generally fall unless "narrowly tailored to advance a legitimate local purpose" with no reasonable nondiscriminatory alternative; facially neutral laws that unduly burden commerce get Pike balancing.</t>
+        </is>
+      </c>
+      <c r="J150" s="101" t="inlineStr">
+        <is>
+          <t>• Purpose: it "prevents the States from adopting protectionist measures and thus preserves a national market for goods and services"
+• A neutral, safety-based law with incidental effects is upheld unless the burden is clearly excessive relative to local benefits
+• Extraterritoriality principle: neutral laws that regulate conduct wholly outside the State; the Court gave no general rule for when it applies
+• The case law is "highly fact-specific"</t>
+        </is>
+      </c>
+      <c r="K150" s="101" t="inlineStr">
+        <is>
+          <t>A compact statement of the modern doctrine to open an answer before applying Dean Milk, Pike or Maine v. Taylor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="105" t="inlineStr">
+        <is>
+          <t>Dormant Commerce Clause</t>
+        </is>
+      </c>
+      <c r="B151" s="101" t="n"/>
+      <c r="C151" s="101" t="n">
+        <v>9</v>
+      </c>
+      <c r="D151" s="101" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="E151" s="102" t="inlineStr">
+        <is>
+          <t>Reader Comment: Truesdell v. Friedlander (6th Cir. 2023)</t>
+        </is>
+      </c>
+      <c r="F151" s="101" t="inlineStr">
+        <is>
+          <t>Dormant Commerce Clause: discrimination test</t>
+        </is>
+      </c>
+      <c r="G151" s="101" t="inlineStr">
+        <is>
+          <t>A post-Pork Sixth Circuit case quoted in the reader as a checklist for finding discrimination against interstate commerce.</t>
+        </is>
+      </c>
+      <c r="H151" s="101" t="inlineStr">
+        <is>
+          <t>N/A (method).</t>
+        </is>
+      </c>
+      <c r="I151" s="101" t="inlineStr">
+        <is>
+          <t>Three questions to ferret out 'economic protectionism': (1) Does the law discriminate on its FACE? (2) If not, does it have a discriminatory EFFECT? (3) If not, did the legislature pass it for a discriminatory PURPOSE?</t>
+        </is>
+      </c>
+      <c r="J151" s="101" t="inlineStr">
+        <is>
+          <t>• Face → effect → purpose, in that order
+• Matches Pork's view that discrimination is the core and Pike mainly detects it</t>
+        </is>
+      </c>
+      <c r="K151" s="101" t="inlineStr">
+        <is>
+          <t>Ready-made framework for a dormant CC essay before reaching Pike balancing or the market-participant exception.</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="105" t="inlineStr">
+        <is>
+          <t>Major questions &amp; nondelegation</t>
+        </is>
+      </c>
+      <c r="B152" s="99" t="inlineStr">
+        <is>
+          <t>Commerce Clause</t>
+        </is>
+      </c>
+      <c r="C152" s="99" t="n">
+        <v>5</v>
+      </c>
+      <c r="D152" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E152" s="100" t="inlineStr">
+        <is>
+          <t>A. L. A. Schechter Poultry Corp. v. United States (1935)</t>
+        </is>
+      </c>
+      <c r="F152" s="99" t="inlineStr">
+        <is>
+          <t>Commerce Clause: direct/indirect</t>
+        </is>
+      </c>
+      <c r="G152" s="99" t="inlineStr">
+        <is>
+          <t>Brooklyn slaughterhouses that bought poultry shipped from other States and sold only to local retailers were convicted of violating the NIRA Live Poultry Code's wage, hour and trade rules.</t>
+        </is>
+      </c>
+      <c r="H152" s="99" t="inlineStr">
+        <is>
+          <t>The code provisions were invalid as an unconstitutional delegation and as regulation of intrastate transactions that affect interstate commerce only indirectly; convictions reversed.</t>
+        </is>
+      </c>
+      <c r="I152" s="99" t="inlineStr">
+        <is>
+          <t>Congress may reach intrastate activity with direct effects on interstate commerce but not indirect ones; the distinction is 'essential to the maintenance of our constitutional system.' Once goods come to 'permanent rest' in a State, the stream of commerce ends.</t>
+        </is>
+      </c>
+      <c r="J152" s="99" t="inlineStr">
+        <is>
+          <t>• 'Extraordinary conditions do not create or enlarge constitutional power'
+• The government's wage argument 'proves too much': it would reach rents, advertising and every cost
+• Cardozo concurrence: society 'is an elastic medium which transmits all tremors throughout its territory; the only question is of their size'; 'To find immediacy or directness here is to find it almost everywhere'
+• Goods only resting temporarily before moving on stay in the stream; Wickard abandoned the direct/indirect label but did not expressly overrule Schechter</t>
+        </is>
+      </c>
+      <c r="K152" s="99" t="inlineStr">
+        <is>
+          <t>Schechter marks the pre-1937 limit. Contrast Wickard's substantial-effects test; Lopez and Morrison later borrow its worry that federal power could reach everything.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="105" t="inlineStr">
+        <is>
+          <t>Major questions &amp; nondelegation</t>
+        </is>
+      </c>
+      <c r="B153" s="103" t="inlineStr">
+        <is>
+          <t>Commerce Clause; Taxing &amp; Spending; Necessary &amp; Proper / implied powers</t>
+        </is>
+      </c>
+      <c r="C153" s="103" t="n">
+        <v>5</v>
+      </c>
+      <c r="D153" s="103" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+      <c r="E153" s="104" t="inlineStr">
+        <is>
+          <t>CRS, Recurring Constitutional Issues in Federal Legislation (2022)</t>
+        </is>
+      </c>
+      <c r="F153" s="103" t="inlineStr">
+        <is>
+          <t>Congress's powers: overview</t>
+        </is>
+      </c>
+      <c r="G153" s="103" t="inlineStr">
+        <is>
+          <t>A CRS checklist for evaluating federal legislation.</t>
+        </is>
+      </c>
+      <c r="H153" s="103" t="inlineStr">
+        <is>
+          <t>Every bill raises two questions: is it within an enumerated power, and does it violate another constraint (federalism, separation of powers, individual rights)?</t>
+        </is>
+      </c>
+      <c r="I153" s="103" t="inlineStr">
+        <is>
+          <t>Summarizes Lopez's categories, Dole's spending limits, Boerne's congruence and proportionality, anti-commandeering (Murphy v. NCAA), bicameralism and presentment (Chadha), and nondelegation (intelligible principle).</t>
+        </is>
+      </c>
+      <c r="J153" s="103" t="inlineStr">
+        <is>
+          <t>• The two-question framework
+• Dole's limits restated: clear notice, relatedness, no coercion, no independent bar</t>
+        </is>
+      </c>
+      <c r="K153" s="103" t="inlineStr">
+        <is>
+          <t>A ready-made structure for any "Is this statute constitutional?" essay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="105" t="inlineStr">
+        <is>
+          <t>Major questions &amp; nondelegation</t>
+        </is>
+      </c>
+      <c r="B154" s="106" t="inlineStr">
+        <is>
+          <t>Separation of powers</t>
+        </is>
+      </c>
+      <c r="C154" s="106" t="n">
+        <v>5</v>
+      </c>
+      <c r="D154" s="106" t="inlineStr">
+        <is>
+          <t>Doctrine note</t>
+        </is>
+      </c>
+      <c r="E154" s="107" t="inlineStr">
+        <is>
+          <t>"Major questions" doctrine (and nondelegation)</t>
+        </is>
+      </c>
+      <c r="F154" s="106" t="inlineStr">
+        <is>
+          <t>Statutory canon; separation of powers</t>
+        </is>
+      </c>
+      <c r="G154" s="106" t="inlineStr">
+        <is>
+          <t>NOT a single reader case. The reader raises it in Study Question 27 ("a canon of statutory interpretation... what it has to do with the non-delegation doctrine") and covers nondelegation in the Week 5 CRS report (Gundy's "intelligible principle") and Schechter's separate delegation issue. The case examples in this row (West Virginia v. EPA, Biden v. Nebraska) are from OUTSIDE the reader.</t>
+        </is>
+      </c>
+      <c r="H154" s="106" t="inlineStr">
+        <is>
+          <t>Outside-the-reader anchor: West Virginia v. EPA (2022) rejected EPA's reading of the Clean Air Act to allow a sector-wide shift away from coal power. In 'extraordinary cases' of vast economic and political significance, an agency needs 'clear congressional authorization,' not a broad or vague grant. Biden v. Nebraska (2023) applied it to the student-loan forgiveness program.</t>
+        </is>
+      </c>
+      <c r="I154" s="106" t="inlineStr">
+        <is>
+          <t>MAJOR QUESTIONS: a canon of statutory interpretation. Courts presume Congress makes major policy decisions itself, so they won't read ambiguous or general statutory language to give an agency power over a question of vast economic and political significance without clear authorization. NONDELEGATION: a constitutional rule. Congress can't hand its legislative power to another branch; it must give an 'intelligible principle' (CRS; Gundy). Schechter is one of the rare cases striking a statute on that ground. LINK: the canon is a nondelegation-flavored tool that works by narrowing the STATUTE, not by striking it. It avoids the constitutional question while protecting the same value: Congress, not agencies, makes the big policy calls.</t>
+        </is>
+      </c>
+      <c r="J154" s="106" t="inlineStr">
+        <is>
+          <t>• It's a rule of STATUTORY interpretation, not a constitutional holding
+• Nondelegation = constitutional; asks whether Congress gave an 'intelligible principle' (Gundy, via CRS)
+• Major questions works by reading the statute narrowly; nondelegation would strike the statute down
+• Trigger: vast economic and political significance + agency claiming new power from old or vague text
+• Fix: Congress can always grant the power with clear authorization
+• Schechter: delegation issue is separate from its Commerce Clause holding</t>
+        </is>
+      </c>
+      <c r="K154" s="106" t="inlineStr">
+        <is>
+          <t>Study Q27 answer frame: (1) define the canon (clear authorization needed for major questions); (2) define nondelegation (intelligible principle; Schechter); (3) connect them: the canon enforces nondelegation values through interpretation, sending big policy choices back to Congress. Tie to separation of powers (Federalist 47/51).</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="105" t="inlineStr">
+        <is>
+          <t>Treaties &amp; executive agreements</t>
+        </is>
+      </c>
+      <c r="B155" s="99" t="n"/>
+      <c r="C155" s="99" t="n">
+        <v>9</v>
+      </c>
+      <c r="D155" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E155" s="100" t="inlineStr">
+        <is>
+          <t>Foster v. Neilson (1829)</t>
+        </is>
+      </c>
+      <c r="F155" s="99" t="inlineStr">
+        <is>
+          <t>Treaties: self-executing vs. not</t>
+        </is>
+      </c>
+      <c r="G155" s="99" t="inlineStr">
+        <is>
+          <t>Reader excerpt is only Chief Justice Marshall's passage on how treaties operate in U.S. courts; the facts are omitted.</t>
+        </is>
+      </c>
+      <c r="H155" s="99" t="inlineStr">
+        <is>
+          <t>Excerpt states the principle only (the reader doesn't include the disposition).</t>
+        </is>
+      </c>
+      <c r="I155" s="99" t="inlineStr">
+        <is>
+          <t>A treaty is the law of the land and is equivalent to an act of the legislature "whenever it operates of itself without the aid of any legislative provision." But when a treaty's terms "import a contract" (a party "engages to perform a particular act"), it "addresses itself to the political, not the judicial department; and the legislature must execute the contract before it can become a rule for the Court."</t>
+        </is>
+      </c>
+      <c r="J155" s="99" t="inlineStr">
+        <is>
+          <t>• Origin of the self-executing / non-self-executing distinction
+• Internationally a treaty is a contract between nations; the U.S. Constitution makes it domestic law (Supremacy Clause)
+• Marshall, C.J.
+• CRS notes it was overruled on other grounds (Percheman, 1833)</t>
+        </is>
+      </c>
+      <c r="K155" s="99" t="inlineStr">
+        <is>
+          <t>Cite for the rule that non-self-executing treaty provisions need implementing legislation before courts enforce them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="105" t="inlineStr">
+        <is>
+          <t>Treaties &amp; executive agreements</t>
+        </is>
+      </c>
+      <c r="B156" s="99" t="inlineStr">
+        <is>
+          <t>Political question</t>
+        </is>
+      </c>
+      <c r="C156" s="99" t="n">
+        <v>4</v>
+      </c>
+      <c r="D156" s="99" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="E156" s="100" t="inlineStr">
+        <is>
+          <t>Goldwater v. Carter (D.C. Cir. en banc 1979; U.S. 1979)</t>
+        </is>
+      </c>
+      <c r="F156" s="99" t="inlineStr">
+        <is>
+          <t>Political question: foreign affairs</t>
+        </is>
+      </c>
+      <c r="G156" s="99" t="inlineStr">
+        <is>
+          <t>President Carter recognized the People's Republic of China and gave one-year notice terminating the Mutual Defense Treaty with Taiwan under its termination clause, without Senate or congressional consent. Senator Goldwater and other legislators sued.</t>
+        </is>
+      </c>
+      <c r="H156" s="99" t="inlineStr">
+        <is>
+          <t>The D.C. Circuit en banc upheld the President's notice on the merits; the Supreme Court, with no majority opinion, vacated and remanded with directions to dismiss the complaint.</t>
+        </is>
+      </c>
+      <c r="I156" s="99" t="inlineStr">
+        <is>
+          <t>No single rationale controls. Rehnquist (four Justices): a nonjusticiable political question because the Constitution is silent on treaty termination and foreign relations are involved. Powell: not ripe until each branch takes official action and reaches a 'constitutional impasse.'</t>
+        </is>
+      </c>
+      <c r="J156" s="99" t="inlineStr">
+        <is>
+          <t>• D.C. Cir.: the treaty's termination clause was 'an overarching factor' and the President's authority 'at its zenith'; MacKinnon would find the case justiciable but deny the President sole power
+• Rehnquist analogized Coleman v. Miller (Art. V silent on rejection), distinguished Youngstown (private litigants, domestic impact), and vacated so the ruling would not 'spawn any legal consequences' (Munsingwear)
+• Powell restated Baker as three questions (text, judicial expertise, prudence); Congress had taken no official action; his hypo: a President putting a Senate-rejected treaty into effect is plainly decidable
+• Brennan would affirm on the recognition power: which branch holds a power is a legal question for courts; reader asks 'What is the controlling opinion?' Answer: none</t>
+        </is>
+      </c>
+      <c r="K156" s="99" t="inlineStr">
+        <is>
+          <t>Use Goldwater to contrast political question (Rehnquist) with ripeness (Powell). For a legislator suit where Congress has not voted, Powell's approach says dismiss as unripe.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="105" t="inlineStr">
+        <is>
+          <t>Treaties &amp; executive agreements</t>
+        </is>
+      </c>
+      <c r="B157" s="101" t="n"/>
+      <c r="C157" s="101" t="n">
+        <v>9</v>
+      </c>
+      <c r="D157" s="101" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="E157" s="102" t="inlineStr">
+        <is>
+          <t>Reader Comment: treaties vs. later statutes (last in time)</t>
+        </is>
+      </c>
+      <c r="F157" s="101" t="inlineStr">
+        <is>
+          <t>Treaties: conflict with statutes</t>
+        </is>
+      </c>
+      <c r="G157" s="101" t="inlineStr">
+        <is>
+          <t>Reader note on what happens when a self-executing treaty and a later statute conflict.</t>
+        </is>
+      </c>
+      <c r="H157" s="101" t="inlineStr">
+        <is>
+          <t>N/A (rule summary).</t>
+        </is>
+      </c>
+      <c r="I157" s="101" t="inlineStr">
+        <is>
+          <t>Treaties and federal statutes have equal status, so the LATER one controls to the extent of conflict (Whitney v. Robertson; Reid v. Covert, quoted in Breard v. Greene). Courts first try to read them together. Congress can modify or repeal a treaty's domestic effect by statute (Edye v. Robertson).</t>
+        </is>
+      </c>
+      <c r="J157" s="101" t="inlineStr">
+        <is>
+          <t>• Last-in-time rule applies only if the treaty provision is self-executing (Whitney)
+• Treaty doesn't outrank a statute; both are 'supreme law'
+• With a veto override, Congress can override a treaty even over the President's objection</t>
+        </is>
+      </c>
+      <c r="K157" s="101" t="inlineStr">
+        <is>
+          <t>Answer to 'treaty Monday, contrary statute Friday': the statute wins (and vice versa if the treaty is later).</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="105" t="inlineStr">
+        <is>
+          <t>Treaties &amp; executive agreements</t>
+        </is>
+      </c>
+      <c r="B158" s="101" t="inlineStr">
+        <is>
+          <t>Separation of powers</t>
+        </is>
+      </c>
+      <c r="C158" s="101" t="n">
+        <v>9</v>
+      </c>
+      <c r="D158" s="101" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="E158" s="102" t="inlineStr">
+        <is>
+          <t>Circular 175 Procedure (11 FAM 720)</t>
+        </is>
+      </c>
+      <c r="F158" s="101" t="inlineStr">
+        <is>
+          <t>Treaties vs. executive agreements: State Dept. criteria</t>
+        </is>
+      </c>
+      <c r="G158" s="101" t="inlineStr">
+        <is>
+          <t>State Department rules (Foreign Affairs Manual) for negotiating and concluding international agreements.</t>
+        </is>
+      </c>
+      <c r="H158" s="101" t="inlineStr">
+        <is>
+          <t>N/A.</t>
+        </is>
+      </c>
+      <c r="I158" s="101" t="inlineStr">
+        <is>
+          <t>Two constitutional routes: TREATY (2/3 Senate advice and consent; any subject genuinely of concern in foreign relations, if consistent with the Constitution) or AGREEMENT OTHER THAN A TREATY, based on (1) a treaty, (2) legislation, or (3) the President's own constitutional authority (foreign affairs representative, receiving ambassadors/recognition, Commander in Chief, Take Care). Factors for choosing: commitments/risks to the nation as a whole; effect on state law; need for implementing legislation; past practice; Congress's preference; formality; duration/urgency; international practice.</t>
+        </is>
+      </c>
+      <c r="J158" s="101" t="inlineStr">
+        <is>
+          <t>• 'Sole executive agreement' = only on the President's own authority, and can't conflict with a statute
+• Case-Zablocki Act: non-treaty agreements must be sent to Congress within 60 days
+• Goal: avoid 'invasion or compromise' of the powers of the President, Senate and Congress</t>
+        </is>
+      </c>
+      <c r="K158" s="101" t="inlineStr">
+        <is>
+          <t>Use the eight factors to argue whether a given agreement should have gone to the Senate as a treaty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="105" t="inlineStr">
+        <is>
+          <t>Treaties &amp; executive agreements</t>
+        </is>
+      </c>
+      <c r="B159" s="103" t="inlineStr">
+        <is>
+          <t>Political question</t>
+        </is>
+      </c>
+      <c r="C159" s="103" t="n">
+        <v>4</v>
+      </c>
+      <c r="D159" s="103" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+      <c r="E159" s="104" t="inlineStr">
+        <is>
+          <t>Goldwater v. Carter background documents</t>
+        </is>
+      </c>
+      <c r="F159" s="103" t="inlineStr">
+        <is>
+          <t>Treaty termination</t>
+        </is>
+      </c>
+      <c r="G159" s="103" t="inlineStr">
+        <is>
+          <t>President Carter's statements on recognizing the PRC and the Taiwan Relations Act.</t>
+        </is>
+      </c>
+      <c r="H159" s="103" t="inlineStr">
+        <is>
+          <t>On Dec. 15, 1978, the U.S. announced recognition of the PRC as the sole government of China and notice terminating the Mutual Defense Treaty with Taiwan.</t>
+        </is>
+      </c>
+      <c r="I159" s="103" t="inlineStr">
+        <is>
+          <t>The Taiwan Relations Act (1979) kept unofficial relations through the American Institute in Taiwan.</t>
+        </is>
+      </c>
+      <c r="J159" s="103" t="inlineStr">
+        <is>
+          <t>• The treaty was ended by presidential notice under its own termination clause (Article X), which is what the senators challenged</t>
+        </is>
+      </c>
+      <c r="K159" s="103" t="inlineStr">
+        <is>
+          <t>Factual setting for Goldwater's political-question and ripeness opinions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="105" t="inlineStr">
+        <is>
+          <t>Treaties &amp; executive agreements</t>
+        </is>
+      </c>
+      <c r="B160" s="103" t="n"/>
+      <c r="C160" s="103" t="n">
+        <v>9</v>
+      </c>
+      <c r="D160" s="103" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+      <c r="E160" s="104" t="inlineStr">
+        <is>
+          <t>CRS, International Law and Agreements (RL32528)</t>
+        </is>
+      </c>
+      <c r="F160" s="103" t="inlineStr">
+        <is>
+          <t>Treaties and executive agreements</t>
+        </is>
+      </c>
+      <c r="G160" s="103" t="inlineStr">
+        <is>
+          <t>CRS overview of the forms of U.S. international commitments and their domestic effect.</t>
+        </is>
+      </c>
+      <c r="H160" s="103" t="inlineStr">
+        <is>
+          <t>N/A (overview).</t>
+        </is>
+      </c>
+      <c r="I160" s="103" t="inlineStr">
+        <is>
+          <t>TREATY (domestic sense): negotiated by the executive, approved by 2/3 of the Senate, ratified by the President (Art. II, §2, cl. 2). Senate may attach reservations, understandings and declarations (RUDs); the President can't ratify without accepting them. EXECUTIVE AGREEMENTS (over 90% of agreements), three types: congressional-executive (authorized by statute), pursuant to a treaty, and sole executive (President's own constitutional power). SELF-EXECUTING provisions are domestic law; NON-SELF-EXECUTING ones need implementing legislation.</t>
+        </is>
+      </c>
+      <c r="J160" s="103" t="inlineStr">
+        <is>
+          <t>• In international law 'treaty' = any binding agreement; in U.S. law it means Senate-approved
+• President's power to negotiate is exclusive; early 'advice' role faded after Washington
+• Courts haven't said executive agreements are fully interchangeable with treaties, partly because challengers lack standing
+• Traditionally treaties: mutual defense, extradition, human rights, arms control, taxation, boundaries
+• Agreements needing appropriations, criminal law or revenue are treated as non-self-executing (Congress's exclusive powers)
+• Medellín: self-executing = 'automatic domestic effect as federal law upon ratification'</t>
+        </is>
+      </c>
+      <c r="K160" s="103" t="inlineStr">
+        <is>
+          <t>Framework for any treaty question: what form is it, what authority supports it, and is it self-executing? Connects to Goldwater v. Carter (treaty termination) and political question.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="105" t="inlineStr">
+        <is>
+          <t>Treaties &amp; executive agreements</t>
+        </is>
+      </c>
+      <c r="B161" s="103" t="inlineStr">
+        <is>
+          <t>Separation of powers</t>
+        </is>
+      </c>
+      <c r="C161" s="103" t="n">
+        <v>9</v>
+      </c>
+      <c r="D161" s="103" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+      <c r="E161" s="104" t="inlineStr">
+        <is>
+          <t>About Treaties (U.S. Senate website)</t>
+        </is>
+      </c>
+      <c r="F161" s="103" t="inlineStr">
+        <is>
+          <t>Treaties: Senate process</t>
+        </is>
+      </c>
+      <c r="G161" s="103" t="inlineStr">
+        <is>
+          <t>Senate explanation of its role in treaty-making.</t>
+        </is>
+      </c>
+      <c r="H161" s="103" t="inlineStr">
+        <is>
+          <t>N/A.</t>
+        </is>
+      </c>
+      <c r="I161" s="103" t="inlineStr">
+        <is>
+          <t>The President makes treaties with the advice and consent of 2/3 of Senators present. The Senate does NOT ratify treaties: after Foreign Relations Committee review it approves or rejects a resolution of ratification, and ratification happens when instruments are exchanged.</t>
+        </is>
+      </c>
+      <c r="J161" s="103" t="inlineStr">
+        <is>
+          <t>• Common trap: 'the Senate ratifies' (wrong: it consents; the President ratifies)
+• Treaties lacking support may simply never get a vote and are withdrawn; pending treaties carry over between Congresses
+• Executive agreements bypass the Senate but are still binding internationally</t>
+        </is>
+      </c>
+      <c r="K161" s="103" t="inlineStr">
+        <is>
+          <t>Use for the mechanics of advice and consent and the rise of executive agreements.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:K161"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/Con_Law_Outline_Consolidated.xlsx
+++ b/Con_Law_Outline_Consolidated.xlsx
@@ -31,11 +31,12 @@
     <sheet name="Week 9 - Class" sheetId="23" state="visible" r:id="rId23"/>
     <sheet name="Week 10 - Reading" sheetId="24" state="visible" r:id="rId24"/>
     <sheet name="Week 10 - Class" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="Cases by Doctrine" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="Midterm questions &amp; answers" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="Week 11 - Reading" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="Cases by Doctrine" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="Midterm questions &amp; answers" sheetId="28" state="visible" r:id="rId28"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="25" hidden="1">'Cases by Doctrine'!$A$1:$K$161</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="26" hidden="1">'Cases by Doctrine'!$A$1:$K$161</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -665,7 +666,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="117">
+  <cellXfs count="118">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -1003,6 +1004,9 @@
     <xf numFmtId="0" fontId="13" fillId="46" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="51" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -10740,6 +10744,756 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="117" t="inlineStr">
+        <is>
+          <t>Case / Reading</t>
+        </is>
+      </c>
+      <c r="B1" s="117" t="inlineStr">
+        <is>
+          <t>Doctrine</t>
+        </is>
+      </c>
+      <c r="C1" s="117" t="inlineStr">
+        <is>
+          <t>Holding (what was decided)</t>
+        </is>
+      </c>
+      <c r="D1" s="117" t="inlineStr">
+        <is>
+          <t>Key principle / rule it shaped</t>
+        </is>
+      </c>
+      <c r="E1" s="117" t="inlineStr">
+        <is>
+          <t>Remember for the exam</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="112" t="inlineStr">
+        <is>
+          <t>The Federalist No. 39 (Madison, 1788)</t>
+        </is>
+      </c>
+      <c r="B2" s="111" t="inlineStr">
+        <is>
+          <t>Republican government; tenure of officers</t>
+        </is>
+      </c>
+      <c r="C2" s="111" t="inlineStr">
+        <is>
+          <t>N/A (reading)</t>
+        </is>
+      </c>
+      <c r="D2" s="111" t="inlineStr">
+        <is>
+          <t>A republic is a government that gets all its power directly or indirectly from the great body of the people, run by people who serve at pleasure, for a limited term, or during good behavior. It is ESSENTIAL that power come from the people as a whole, not a favored class; it is SUFFICIENT that officers are chosen directly or indirectly by the people. House = direct election; Senate, President and judges = indirect. Key line: 'The tenure of the ministerial offices generally, will be a subject of legal regulation.'</t>
+        </is>
+      </c>
+      <c r="E2" s="111" t="inlineStr">
+        <is>
+          <t>Slaughter dissent reads 'legal regulation' of tenure to mean Congress can limit removal. Majority: Madison meant only fixed TERMS for officers, still removable by the President in between.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="112" t="inlineStr">
+        <is>
+          <t>The Federalist No. 77 (Hamilton, 1788)</t>
+        </is>
+      </c>
+      <c r="B3" s="111" t="inlineStr">
+        <is>
+          <t>Appointments and removal</t>
+        </is>
+      </c>
+      <c r="C3" s="111" t="inlineStr">
+        <is>
+          <t>N/A (reading)</t>
+        </is>
+      </c>
+      <c r="D3" s="111" t="inlineStr">
+        <is>
+          <t>Senate consent 'would be necessary to displace as well as to appoint.' Selling point: a new President couldn't sweep out good officers, giving a 'steady administration'; the Senate is more stable than other branches.</t>
+        </is>
+      </c>
+      <c r="E3" s="111" t="inlineStr">
+        <is>
+          <t>Dissent's best founding quote against at-will removal. Majority: unclear whether 'displace' meant REMOVE or REPLACE; conflicts with Fed. 70 and 72; Hamilton said by 1793 (Pacificus No. 1) that removal is executive power.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="112" t="inlineStr">
+        <is>
+          <t>Letter, Rep. William Smith to Edward Rutledge (June 21, 1789)</t>
+        </is>
+      </c>
+      <c r="B4" s="111" t="inlineStr">
+        <is>
+          <t>Decision of 1789 — background</t>
+        </is>
+      </c>
+      <c r="C4" s="111" t="inlineStr">
+        <is>
+          <t>N/A (reading)</t>
+        </is>
+      </c>
+      <c r="D4" s="111" t="inlineStr">
+        <is>
+          <t>Describes the House's 4-day debate over giving the President the removal power ('the most important question'). Smith quoted Federalist No. 77 for his side; Rep. Benson then passed him a note saying 'Publius' (Hamilton) had changed his mind and now thought the President ALONE should remove at pleasure — while Hamilton was a candidate for Secretary of the Treasury.</t>
+        </is>
+      </c>
+      <c r="E4" s="111" t="inlineStr">
+        <is>
+          <t>Shows Hamilton's Fed. 77 view was disputed or abandoned even in 1789; cuts against relying on Fed. 77.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="112" t="inlineStr">
+        <is>
+          <t>Edmond v. United States (1997) (Scalia)</t>
+        </is>
+      </c>
+      <c r="B5" s="111" t="inlineStr">
+        <is>
+          <t>Appointments Clause — principal vs. inferior officers</t>
+        </is>
+      </c>
+      <c r="C5" s="111" t="inlineStr">
+        <is>
+          <t>Civilian judges of the Coast Guard Court of Criminal Appeals are INFERIOR officers, so the Secretary of Transportation (a head of department) could validly appoint them.</t>
+        </is>
+      </c>
+      <c r="D5" s="111" t="inlineStr">
+        <is>
+          <t>Appointments Clause: principal officers = President + Senate consent; Congress may vest appointment of inferior officers in the President alone, courts of law, or heads of departments ('Excepting Clause,' for administrative convenience). 'Significant authority' (Buckley) marks officer vs. employee, NOT principal vs. inferior. Test: an inferior officer has a SUPERIOR — work is 'directed and supervised at some level' by Senate-confirmed officers. Here: the Judge Advocate General sets rules and can remove the judges without cause; the Court of Appeals for the Armed Forces can reverse them. Key: they cannot render a FINAL decision for the U.S. unless other executive officers permit it.</t>
+        </is>
+      </c>
+      <c r="E5" s="111" t="inlineStr">
+        <is>
+          <t>Factors: who supervises, who can remove (removal = 'powerful tool for control'), whether decisions are final. Morrison's factors (limited duties, jurisdiction, tenure) aren't a definitive test. First Congress called department heads 'principal' and chief clerks 'inferior.' Purpose: accountability — blame for bad picks falls on President and Senate (Fed. 76, 77).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="112" t="inlineStr">
+        <is>
+          <t>Lucia v. SEC (2018) (Kagan, 7-2)</t>
+        </is>
+      </c>
+      <c r="B6" s="111" t="inlineStr">
+        <is>
+          <t>Appointments Clause — officer vs. employee</t>
+        </is>
+      </c>
+      <c r="C6" s="111" t="inlineStr">
+        <is>
+          <t>SEC administrative law judges are 'Officers of the United States.' Because SEC staff (not the Commission) hired them, they were unconstitutionally appointed.</t>
+        </is>
+      </c>
+      <c r="D6" s="111" t="inlineStr">
+        <is>
+          <t>Officer test: (1) a CONTINUING position established by law (Germaine — not 'occasional or temporary'); and (2) exercises SIGNIFICANT AUTHORITY under federal law (Buckley). Freytag (Tax Court special trial judges) controls: SEC ALJs take testimony, conduct trials, rule on evidence, and enforce discovery orders — same as STJs. A fortiori: if the SEC declines review, the ALJ's decision becomes final and is 'deemed the action of the Commission.' Remedy: a NEW hearing before a properly appointed official, and NOT the same ALJ (Elliot), even if later properly appointed.</t>
+        </is>
+      </c>
+      <c r="E6" s="111" t="inlineStr">
+        <is>
+          <t>Facts: Raymond Lucia, 'Buckets of Money' retirement strategy; ALJ Elliot imposed $300,000 penalty and lifetime bar. The Government switched sides; Court appointed amicus. Commission itself = 'head of department' and may appoint ALJs (inferior officers). Lack of contempt/jail power doesn't matter — ALJs can exclude parties and suspend attorneys.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="112" t="inlineStr">
+        <is>
+          <t>Lucia — Thomas concurrence (with Gorsuch); other opinions</t>
+        </is>
+      </c>
+      <c r="B7" s="111" t="inlineStr">
+        <is>
+          <t>Appointments Clause</t>
+        </is>
+      </c>
+      <c r="C7" s="111" t="inlineStr">
+        <is>
+          <t>Agreed the case is indistinguishable from Freytag.</t>
+        </is>
+      </c>
+      <c r="D7" s="111" t="inlineStr">
+        <is>
+          <t>Thomas: precedents say what is SUFFICIENT to be an officer but never what is NECESSARY; the Court can't decide every future case by comparison to Freytag. (Breyer concurred in part/dissented in part; Sotomayor with Ginsburg dissented.)</t>
+        </is>
+      </c>
+      <c r="E7" s="111" t="inlineStr">
+        <is>
+          <t>Know the vote (7-2 on officer status) and that the officer test remains open-ended.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="112" t="inlineStr">
+        <is>
+          <t>Myers (1926) and Humphrey's Executor (1935) — as recounted in Trump v. Slaughter</t>
+        </is>
+      </c>
+      <c r="B8" s="111" t="inlineStr">
+        <is>
+          <t>Removal power — background</t>
+        </is>
+      </c>
+      <c r="C8" s="111" t="inlineStr">
+        <is>
+          <t>Myers: President may fire a postmaster without the Senate's consent; the 1876 law requiring consent was unconstitutional. Humphrey's: FDR couldn't fire FTC Commissioner Humphrey without cause, because the FTC was then described as 'quasi-legislative' and 'quasi-judicial,' exercising 'no part of the executive power.'</t>
+        </is>
+      </c>
+      <c r="D8" s="111" t="inlineStr">
+        <is>
+          <t>Myers (Taft): executive power + Take Care Clause imply power to remove those 'for whom he can not continue to be responsible.' Humphrey's (Sutherland): the President is 'master in his own house' but can't impose control 'in the house of another.' Humphrey's was decided on 'Black Monday' (same day as Schechter and Radford). Morrison v. Olson (1988) later admitted the FTC exercised executive power 'to some degree' even in 1935.</t>
+        </is>
+      </c>
+      <c r="E8" s="111" t="inlineStr">
+        <is>
+          <t>Humphrey reportedly called the FTC a 'publicity bureau' spreading 'Socialistic propaganda'; FDR fired him with a one-line letter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="112" t="inlineStr">
+        <is>
+          <t>Trump v. Slaughter (2026) (Roberts, 6-3)</t>
+        </is>
+      </c>
+      <c r="B9" s="111" t="inlineStr">
+        <is>
+          <t>Presidential removal power</t>
+        </is>
+      </c>
+      <c r="C9" s="111" t="inlineStr">
+        <is>
+          <t>The FTC Act's for-cause removal protection for Commissioners ('inefficiency, neglect of duty, or malfeasance') violates the separation of powers. The President could fire Commissioner Slaughter at will. Reversed and remanded.</t>
+        </is>
+      </c>
+      <c r="D9" s="111" t="inlineStr">
+        <is>
+          <t>Rule: officers who exercise EXECUTIVE power in the President's name must be removable by him at will. Sources: Vesting Clause + Take Care Clause; unity of the executive (Fed. 70: plurality 'tends to conceal faults and destroy responsibility'); the 'Decision of 1789' (Madison: removal power keeps the 'chain of dependence'); practice of early Presidents (Washington through Jackson); Hennen, Parsons, Myers. Humphrey's: 'all that is left' is that an agency exercising NO executive power need not be removable at will — 'If anything more is left of Humphrey's, we overrule it.' Today's FTC is executive 'through and through': (1) legislative rules with force of law, (2) investigates and adjudicates in-house, (3) sues in federal court for injunctions and civil penalties (billions, e.g., $2.5B Amazon).</t>
+        </is>
+      </c>
+      <c r="E9" s="111" t="inlineStr">
+        <is>
+          <t>Facts: March 2025, Trump fired the two remaining Democratic Commissioners (Slaughter, Bedoya), citing Article II, not cause. District Court reinstated her under Humphrey's; D.C. Circuit refused a stay (Judge Rao dissented: no 'headless fourth branch'); Supreme Court stayed and granted cert before judgment. Rejects 'practice makes perfect': like Chadha's ~300 legislative vetoes, widespread practice doesn't make it constitutional. Stare decisis is weakest in constitutional cases.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="112" t="inlineStr">
+        <is>
+          <t>Trump v. Slaughter — limits on the holding (Part III-B; Thomas did not join)</t>
+        </is>
+      </c>
+      <c r="B10" s="111" t="inlineStr">
+        <is>
+          <t>Removal power — open questions</t>
+        </is>
+      </c>
+      <c r="C10" s="111" t="inlineStr">
+        <is>
+          <t>Court decides only the FTC, which is in the 'heartland' of executive power.</t>
+        </is>
+      </c>
+      <c r="D10" s="111" t="inlineStr">
+        <is>
+          <t>Left open: (1) entities with no executive or sovereign power (e.g., Boy Scouts, Georgetown — congressionally chartered); (2) the Federal Reserve, to the extent it follows the tradition of the First and Second Banks of the U.S.; (3) tenure protections for judges of non-Article III courts (Tax Court, Court of Federal Claims). Footnote: Marbury's justice of the peace could have fixed tenure because he exercised JUDICIAL power, not executive.</t>
+        </is>
+      </c>
+      <c r="E10" s="111" t="inlineStr">
+        <is>
+          <t>Dissent: these carve-outs are ad hoc; also flags unresolved questions for inferior officers (Perkins) and the civil service, and mixed adjudicatory agencies like the NLRB and MSPB.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="112" t="inlineStr">
+        <is>
+          <t>Trump v. Slaughter — Gorsuch concurrence</t>
+        </is>
+      </c>
+      <c r="B11" s="111" t="inlineStr">
+        <is>
+          <t>Removal power + nondelegation</t>
+        </is>
+      </c>
+      <c r="C11" s="111" t="inlineStr">
+        <is>
+          <t>Agrees with the majority.</t>
+        </is>
+      </c>
+      <c r="D11" s="111" t="inlineStr">
+        <is>
+          <t>Warns: independent agencies hold vast LEGISLATIVE and JUDICIAL power delegated by Congress, and now the President controls all of it. Asks whether Congress would have delegated so much had it known. The 'only sure path' is to restore legislative power to Congress and judicial power to the courts — i.e., revive nondelegation.</t>
+        </is>
+      </c>
+      <c r="E11" s="111" t="inlineStr">
+        <is>
+          <t>Links removal (Slaughter) to nondelegation (Gundy dissent) and major questions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="112" t="inlineStr">
+        <is>
+          <t>Trump v. Slaughter — Sotomayor dissent (with Kagan, Jackson)</t>
+        </is>
+      </c>
+      <c r="B12" s="111" t="inlineStr">
+        <is>
+          <t>Removal power</t>
+        </is>
+      </c>
+      <c r="C12" s="111" t="inlineStr">
+        <is>
+          <t>Would uphold the FTC's for-cause protection under Humphrey's.</t>
+        </is>
+      </c>
+      <c r="D12" s="111" t="inlineStr">
+        <is>
+          <t>(1) Stare decisis: 90 years of precedent; 'profoundly easy case.' (2) 140 years of practice (ICC 1887, Board of General Appraisers 1890, Fed 1913, FTC 1914), approved by Presidents (Lincoln signed the Comptroller of the Currency law). (3) Text: the Constitution is silent on removal; Congress creates offices; Take Care 'speaks of duty, not power.' (4) Decision of 1789 decided only that the SENATE has no role in removal, not that Congress can't set causes (Bowsher distinction). (5) Fed. 77 and 39; Story, Kent, Webster, Clay, Calhoun. (6) Values besides accountability: stability, impartiality, expertise.</t>
+        </is>
+      </c>
+      <c r="E12" s="111" t="inlineStr">
+        <is>
+          <t>Majority's reply: Chadha shows long practice can't save an unconstitutional structure; the dissent would discard Myers itself.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="112" t="inlineStr">
+        <is>
+          <t>CRS, Congress's Authority to Influence and Control Executive Branch Agencies (2023)</t>
+        </is>
+      </c>
+      <c r="B13" s="111" t="inlineStr">
+        <is>
+          <t>Nondelegation — overview</t>
+        </is>
+      </c>
+      <c r="C13" s="111" t="inlineStr">
+        <is>
+          <t>N/A (reading)</t>
+        </is>
+      </c>
+      <c r="D13" s="111" t="inlineStr">
+        <is>
+          <t>Agencies have only the power Congress delegates; Congress can expand, narrow, sunset, or override it by statute. Nondelegation doctrine (separation of powers) bars Congress from giving away its core legislative function, but the test is lenient: Congress need only supply an 'INTELLIGIBLE PRINCIPLE' (J.W. Hampton, 1928). No law struck down on this ground since 1935 (Schechter, Panama Refining). 'Public interest' (NBC) and 'fair and equitable' (Yakus) standards have passed. Congress's tools: triggering conditions/factual findings, report-and-wait provisions, joint resolutions of disapproval (expedited procedures), and proposals that take effect only if enacted.</t>
+        </is>
+      </c>
+      <c r="E13" s="111" t="inlineStr">
+        <is>
+          <t>Contrast: appointment/removal doctrines stop Congress from encroaching on the executive; nondelegation stops Congress from giving its power away.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="112" t="inlineStr">
+        <is>
+          <t>A.L.A. Schechter Poultry Corp. v. United States (1935) (Hughes, unanimous)</t>
+        </is>
+      </c>
+      <c r="B14" s="111" t="inlineStr">
+        <is>
+          <t>Nondelegation</t>
+        </is>
+      </c>
+      <c r="C14" s="111" t="inlineStr">
+        <is>
+          <t>NIRA §3 (letting the President approve or write 'codes of fair competition') was an unconstitutional delegation of legislative power; convictions under the Live Poultry Code reversed. (Also: Congress couldn't regulate these intrastate sales — 'indirect' effects on commerce.)</t>
+        </is>
+      </c>
+      <c r="D14" s="111" t="inlineStr">
+        <is>
+          <t>Congress may leave subordinate rules and fact-finding to others within prescribed limits, but may not transfer its essential legislative function. 'Fair competition' was undefined and far broader than common-law 'unfair competition' or the FTC Act's 'unfair methods of competition' (which had a quasi-judicial process, findings and judicial review). The only standards were the Act's broad policy goals, so the President's discretion was 'virtually unfettered.' Congress can't let trade groups write laws either.</t>
+        </is>
+      </c>
+      <c r="E14" s="111" t="inlineStr">
+        <is>
+          <t>Facts: Brooklyn kosher poultry slaughterhouses; 'straight killing' rule barred customers from picking individual chickens; convicted on counts including selling an 'unfit' chicken and wage/hour violations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="112" t="inlineStr">
+        <is>
+          <t>Schechter — Cardozo concurrence (with Stone)</t>
+        </is>
+      </c>
+      <c r="B15" s="111" t="inlineStr">
+        <is>
+          <t>Nondelegation</t>
+        </is>
+      </c>
+      <c r="C15" s="111" t="inlineStr">
+        <is>
+          <t>Concurs.</t>
+        </is>
+      </c>
+      <c r="D15" s="111" t="inlineStr">
+        <is>
+          <t>The power is 'not canalized within banks that keep it from overflowing'; it is a 'roving commission to inquire into evils and upon discovery correct them.' If 'fair' means anything good for business, 'This is delegation running riot.' Delegation to find and stop UNFAIR practices (like the FTC) would be fine. Also invalid under the Commerce Clause: 'Activities local in their immediacy do not become interstate and national because of distant repercussions.'</t>
+        </is>
+      </c>
+      <c r="E15" s="111" t="inlineStr">
+        <is>
+          <t>Most-quoted lines: 'delegation running riot'; 'roving commission'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="112" t="inlineStr">
+        <is>
+          <t>Gundy v. United States (2019) (Kagan plurality, 5-3)</t>
+        </is>
+      </c>
+      <c r="B16" s="111" t="inlineStr">
+        <is>
+          <t>Nondelegation — intelligible principle</t>
+        </is>
+      </c>
+      <c r="C16" s="111" t="inlineStr">
+        <is>
+          <t>SORNA §20913(d), letting the Attorney General 'specify the applicability' of registration requirements to pre-Act sex offenders, is a constitutional delegation.</t>
+        </is>
+      </c>
+      <c r="D16" s="111" t="inlineStr">
+        <is>
+          <t>Nondelegation analysis begins (and often almost ends) with statutory interpretation. Read in context (the 'comprehensive' national system in the purpose clause; definition of 'sex offender' as one who 'WAS convicted'; Reynolds), the statute requires the AG to apply SORNA to pre-Act offenders AS SOON AS FEASIBLE — discretion only over transitional feasibility issues. That is 'distinctly small-bore.' Only twice (both in 1935) has the Court struck a delegation. 'If SORNA's delegation is unconstitutional, then most of Government is unconstitutional.'</t>
+        </is>
+      </c>
+      <c r="E16" s="111" t="inlineStr">
+        <is>
+          <t>Facts: Herman Gundy, convicted in Maryland before SORNA (2006), failed to register in New York; faced up to 10 years. Kavanaugh did not participate; Alito's vote made 5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="112" t="inlineStr">
+        <is>
+          <t>Gundy — Alito concurrence in the judgment</t>
+        </is>
+      </c>
+      <c r="B17" s="111" t="inlineStr">
+        <is>
+          <t>Nondelegation</t>
+        </is>
+      </c>
+      <c r="C17" s="111" t="inlineStr">
+        <is>
+          <t>Votes to affirm.</t>
+        </is>
+      </c>
+      <c r="D17" s="111" t="inlineStr">
+        <is>
+          <t>Would support reconsidering the intelligible-principle approach if a majority were willing; but it would be 'freakish' to single out this statute while the current test stands.</t>
+        </is>
+      </c>
+      <c r="E17" s="111" t="inlineStr">
+        <is>
+          <t>Signals five Justices (Alito + the 3 dissenters + later Kavanaugh) may revisit nondelegation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="112" t="inlineStr">
+        <is>
+          <t>Gundy — Gorsuch dissent (with Roberts, Thomas)</t>
+        </is>
+      </c>
+      <c r="B18" s="111" t="inlineStr">
+        <is>
+          <t>Nondelegation</t>
+        </is>
+      </c>
+      <c r="C18" s="111" t="inlineStr">
+        <is>
+          <t>Would hold the delegation unconstitutional.</t>
+        </is>
+      </c>
+      <c r="D18" s="111" t="inlineStr">
+        <is>
+          <t>The statute lets the nation's chief prosecutor write his own criminal code for ~500,000 people. Founders' reasons for hard lawmaking: liberty, deliberation, protecting minorities, fair notice, accountability (Locke: legislature 'cannot transfer the power of making laws'). Proposed test — Congress may: (1) make the policy and let others 'fill up the details' (Wayman v. Southard); (2) make a rule's application depend on executive FACT-FINDING (Cargo of the Brig Aurora); (3) assign non-legislative powers the executive already has (e.g., foreign affairs). The 'intelligible principle' phrase was a 'mutated' misreading of J.W. Hampton. Major questions doctrine is nondelegation under another name. Different AGs applied SORNA differently — proof of policymaking.</t>
+        </is>
+      </c>
+      <c r="E18" s="111" t="inlineStr">
+        <is>
+          <t>Pair with Gorsuch's Slaughter concurrence; 'Hopes and dreams are not laws.'</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="112" t="inlineStr">
+        <is>
+          <t>FCC v. Consumers' Research — Kavanaugh concurrence (question in reader)</t>
+        </is>
+      </c>
+      <c r="B19" s="111" t="inlineStr">
+        <is>
+          <t>Nondelegation</t>
+        </is>
+      </c>
+      <c r="C19" s="111" t="inlineStr">
+        <is>
+          <t>N/A (question)</t>
+        </is>
+      </c>
+      <c r="D19" s="111" t="inlineStr">
+        <is>
+          <t>Kavanaugh: 'the intelligible principle test is not toothless,' yet it 'has historically not packed much punch'; the President 'must act within the confines set by Congress.'</t>
+        </is>
+      </c>
+      <c r="E19" s="111" t="inlineStr">
+        <is>
+          <t>Reader asks: how much 'tooth' is that? Likely answer: little on its own — the real limits come from statutory interpretation and major questions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="112" t="inlineStr">
+        <is>
+          <t>Alabama Ass'n of Realtors v. HHS (2021) (per curiam)</t>
+        </is>
+      </c>
+      <c r="B20" s="111" t="inlineStr">
+        <is>
+          <t>Major questions doctrine</t>
+        </is>
+      </c>
+      <c r="C20" s="111" t="inlineStr">
+        <is>
+          <t>Vacated the stay; the CDC's nationwide COVID-19 eviction moratorium exceeded its authority under §361(a) of the Public Health Service Act.</t>
+        </is>
+      </c>
+      <c r="D20" s="111" t="inlineStr">
+        <is>
+          <t>Read the two sentences together: the second lists measures (inspection, fumigation, disinfection, pest extermination, destroying infected animals) that directly target disease; evictions affect spread only indirectly. Even if ambiguous, Congress must speak clearly for powers of 'vast economic and political significance': 80% of the country, 6-17 million tenants, ~$50B in rental aid, intrudes on state landlord-tenant law and the right to exclude. 'A wafer-thin reed.' 'Our system does not permit agencies to act unlawfully even in pursuit of desirable ends' (citing Youngstown). If the moratorium is to continue, Congress must authorize it.</t>
+        </is>
+      </c>
+      <c r="E20" s="111" t="inlineStr">
+        <is>
+          <t>Congress's own moratorium lapsed in July 2020; CDC kept extending it; criminal penalties up to $250,000 and 1 year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="112" t="inlineStr">
+        <is>
+          <t>Alabama Realtors — Breyer dissent (with Sotomayor, Kagan)</t>
+        </is>
+      </c>
+      <c r="B21" s="111" t="inlineStr">
+        <is>
+          <t>Major questions doctrine</t>
+        </is>
+      </c>
+      <c r="C21" s="111" t="inlineStr">
+        <is>
+          <t>Would leave the stay in place.</t>
+        </is>
+      </c>
+      <c r="D21" s="111" t="inlineStr">
+        <is>
+          <t>The first sentence broadly authorizes measures 'necessary' to stop disease; the second ('and other measures') expands, not limits. The order was tailored to high-transmission counties with tenant attestations. Equities and the Delta variant favor the CDC; emergency docket is the wrong place to decide.</t>
+        </is>
+      </c>
+      <c r="E21" s="111" t="inlineStr">
+        <is>
+          <t>Know the stay factors (Nken): likelihood of success, irreparable harm, harm to others, public interest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="112" t="inlineStr">
+        <is>
+          <t>West Virginia v. EPA (2022) + CRS, The Major Questions Doctrine (2022)</t>
+        </is>
+      </c>
+      <c r="B22" s="111" t="inlineStr">
+        <is>
+          <t>Major questions doctrine</t>
+        </is>
+      </c>
+      <c r="C22" s="111" t="inlineStr">
+        <is>
+          <t>West Virginia: EPA lacked clear authority (a 'previously little-used backwater' provision) to restructure the nation's energy mix.</t>
+        </is>
+      </c>
+      <c r="D22" s="111" t="inlineStr">
+        <is>
+          <t>First express use of 'major questions doctrine' in a majority opinion. Two steps: (1) the claimed authority involves vast economic and political significance; (2) Congress hasn't CLEARLY authorized it. A 'merely plausible textual basis' isn't enough; Congress doesn't hide elephants in mouseholes ('modest, vague, subtle, or ambiguous' language). Contrast Massachusetts v. EPA (2007), which rejected EPA's major-questions argument and held it could regulate vehicle greenhouse gases.</t>
+        </is>
+      </c>
+      <c r="E22" s="111" t="inlineStr">
+        <is>
+          <t>Reader question: the doctrine lets the Court AVOID the constitutional nondelegation question by reading the statute narrowly (Gorsuch: nondelegation 'by different names').</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="112" t="inlineStr">
+        <is>
+          <t>CRS, Executive Privilege and Presidential Communications: Judicial Principles (2022)</t>
+        </is>
+      </c>
+      <c r="B23" s="111" t="inlineStr">
+        <is>
+          <t>Executive privilege — overview</t>
+        </is>
+      </c>
+      <c r="C23" s="111" t="inlineStr">
+        <is>
+          <t>N/A (reading)</t>
+        </is>
+      </c>
+      <c r="D23" s="111" t="inlineStr">
+        <is>
+          <t>Not one privilege but several: state secrets; presidential communications (President and close advisers, for presidential decisionmaking); deliberative process (within agencies); law enforcement. The privilege is QUALIFIED, not absolute, and implied from Article II and separation of powers. Disputes with Congress are mostly resolved by negotiation and accommodation; the Supreme Court has never decided executive privilege against a congressional subpoena; courts prefer to avoid such disputes.</t>
+        </is>
+      </c>
+      <c r="E23" s="111" t="inlineStr">
+        <is>
+          <t>Executive branch reads the privilege broadly; Congress narrowly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="112" t="inlineStr">
+        <is>
+          <t>Watergate background and the 'smoking gun' tape (June 23, 1972)</t>
+        </is>
+      </c>
+      <c r="B24" s="111" t="inlineStr">
+        <is>
+          <t>Executive privilege — facts</t>
+        </is>
+      </c>
+      <c r="C24" s="111" t="inlineStr">
+        <is>
+          <t>N/A (reading)</t>
+        </is>
+      </c>
+      <c r="D24" s="111" t="inlineStr">
+        <is>
+          <t>Watergate break-in (June 17, 1972). Senate Watergate Committee and Special Prosecutor Archibald Cox both subpoenaed White House tapes after Alexander Butterfield revealed the Oval Office taping system; Nixon refused both (July 25, 1973). On the 'smoking gun' tape, Haldeman proposes having the CIA (Walters) tell FBI Director Pat Gray to 'stay the hell out of this,' and Nixon agrees — obstruction of the FBI investigation.</t>
+        </is>
+      </c>
+      <c r="E24" s="111" t="inlineStr">
+        <is>
+          <t>Release of this tape after U.S. v. Nixon led directly to resignation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="112" t="inlineStr">
+        <is>
+          <t>United States v. Nixon (1974) (Burger, 8-0; Rehnquist recused)</t>
+        </is>
+      </c>
+      <c r="B25" s="111" t="inlineStr">
+        <is>
+          <t>Executive privilege</t>
+        </is>
+      </c>
+      <c r="C25" s="111" t="inlineStr">
+        <is>
+          <t>The President must comply with a subpoena for tapes needed in a criminal trial; his generalized claim of privilege yields. Affirmed the order for in camera review by the District Court.</t>
+        </is>
+      </c>
+      <c r="D25" s="111" t="inlineStr">
+        <is>
+          <t>(1) Justiciable: Marbury — 'it is emphatically the province and duty of the judicial department to say what the law is,' including the scope of executive privilege. (2) A PRESUMPTIVE privilege for presidential communications exists, rooted in Article II and separation of powers (candor in advice), though not in the text (McCulloch: implied powers). (3) Not ABSOLUTE: a generalized interest in confidentiality must yield to the 'demonstrated, specific need for evidence in a pending criminal trial' (due process, Sixth Amendment compulsory process; 'the public has a right to every man's evidence'). (4) Greater deference for military, diplomatic or national-security secrets. (5) Court must review in camera and protect irrelevant material (Burr: don't treat the President as 'an ordinary individual').</t>
+        </is>
+      </c>
+      <c r="E25" s="111" t="inlineStr">
+        <is>
+          <t>Facts: Nixon named an unindicted coconspirator; Special Prosecutor (Jaworski) subpoenaed tapes for the Mitchell trial. Footnote 19: Court did NOT decide civil cases, congressional demands, or state secrets. Nixon resigned Aug. 8-9, 1974.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="112" t="inlineStr">
+        <is>
+          <t>Nixon's resignation address (Aug. 8, 1974)</t>
+        </is>
+      </c>
+      <c r="B26" s="111" t="inlineStr">
+        <is>
+          <t>Executive privilege — aftermath</t>
+        </is>
+      </c>
+      <c r="C26" s="111" t="inlineStr">
+        <is>
+          <t>N/A (reading)</t>
+        </is>
+      </c>
+      <c r="D26" s="111" t="inlineStr">
+        <is>
+          <t>Nixon resigned effective noon Aug. 9, 1974, saying he lacked the congressional support needed to govern; Vice President Ford was sworn in.</t>
+        </is>
+      </c>
+      <c r="E26" s="111" t="inlineStr">
+        <is>
+          <t>Context only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="112" t="inlineStr">
+        <is>
+          <t>Dellums v. Powell (D.C. Cir. 1977)</t>
+        </is>
+      </c>
+      <c r="B27" s="111" t="inlineStr">
+        <is>
+          <t>Executive privilege — civil cases</t>
+        </is>
+      </c>
+      <c r="C27" s="111" t="inlineStr">
+        <is>
+          <t>A former President's privilege claim in a civil damages suit is subject to a BALANCING test; here it was overcome, with a protective order against public disclosure.</t>
+        </is>
+      </c>
+      <c r="D27" s="111" t="inlineStr">
+        <is>
+          <t>A civil litigant must show a 'substantial' and 'specific' need beyond the routine desire for relevant discovery; usually that won't be met. A FORMER President's claim gets less weight than an incumbent's.</t>
+        </is>
+      </c>
+      <c r="E27" s="111" t="inlineStr">
+        <is>
+          <t>Facts: 1971 'May Day' antiwar arrests; plaintiffs sought Oval Office tapes. Extends U.S. v. Nixon's balancing from criminal to civil cases.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:K161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -19645,7 +20399,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/Con_Law_Outline_Consolidated.xlsx
+++ b/Con_Law_Outline_Consolidated.xlsx
@@ -12183,10 +12183,8 @@
           <t>Appointments &amp; removal</t>
         </is>
       </c>
-      <c r="C13" s="99" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="C13" s="99" t="n">
+        <v>10</v>
       </c>
       <c r="D13" s="99" t="inlineStr">
         <is>
@@ -12241,10 +12239,8 @@
           <t>Appointments &amp; removal</t>
         </is>
       </c>
-      <c r="C14" s="99" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="C14" s="99" t="n">
+        <v>11</v>
       </c>
       <c r="D14" s="99" t="inlineStr">
         <is>
@@ -12686,10 +12682,8 @@
           <t>Executive power</t>
         </is>
       </c>
-      <c r="C22" s="99" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="C22" s="99" t="n">
+        <v>10</v>
       </c>
       <c r="D22" s="99" t="inlineStr">
         <is>
@@ -12745,10 +12739,8 @@
           <t>Executive power</t>
         </is>
       </c>
-      <c r="C23" s="99" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="C23" s="99" t="n">
+        <v>10</v>
       </c>
       <c r="D23" s="99" t="inlineStr">
         <is>
@@ -12804,10 +12796,8 @@
           <t>Executive power</t>
         </is>
       </c>
-      <c r="C24" s="99" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="C24" s="99" t="n">
+        <v>10</v>
       </c>
       <c r="D24" s="99" t="inlineStr">
         <is>
@@ -12859,10 +12849,8 @@
         </is>
       </c>
       <c r="B25" s="99" t="n"/>
-      <c r="C25" s="99" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="C25" s="99" t="n">
+        <v>10</v>
       </c>
       <c r="D25" s="99" t="inlineStr">
         <is>
@@ -12913,10 +12901,8 @@
         </is>
       </c>
       <c r="B26" s="99" t="n"/>
-      <c r="C26" s="99" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="C26" s="99" t="n">
+        <v>10</v>
       </c>
       <c r="D26" s="99" t="inlineStr">
         <is>
@@ -12968,10 +12954,8 @@
         </is>
       </c>
       <c r="B27" s="99" t="n"/>
-      <c r="C27" s="99" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="C27" s="99" t="n">
+        <v>10</v>
       </c>
       <c r="D27" s="99" t="inlineStr">
         <is>
@@ -13022,10 +13006,8 @@
         </is>
       </c>
       <c r="B28" s="99" t="n"/>
-      <c r="C28" s="99" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="C28" s="99" t="n">
+        <v>10</v>
       </c>
       <c r="D28" s="99" t="inlineStr">
         <is>
@@ -13081,10 +13063,8 @@
           <t>Appointments &amp; removal</t>
         </is>
       </c>
-      <c r="C29" s="99" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="C29" s="99" t="n">
+        <v>11</v>
       </c>
       <c r="D29" s="99" t="inlineStr">
         <is>
@@ -13141,10 +13121,8 @@
           <t>Major questions &amp; nondelegation</t>
         </is>
       </c>
-      <c r="C30" s="99" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="C30" s="99" t="n">
+        <v>11</v>
       </c>
       <c r="D30" s="99" t="inlineStr">
         <is>
@@ -13796,10 +13774,8 @@
           <t>Executive privilege</t>
         </is>
       </c>
-      <c r="C42" s="99" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="C42" s="99" t="n">
+        <v>11</v>
       </c>
       <c r="D42" s="99" t="inlineStr">
         <is>
@@ -17887,10 +17863,8 @@
           <t>Major questions &amp; nondelegation</t>
         </is>
       </c>
-      <c r="C117" s="99" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="C117" s="99" t="n">
+        <v>11</v>
       </c>
       <c r="D117" s="99" t="inlineStr">
         <is>
@@ -20764,10 +20738,8 @@
           <t>Executive power; Treaties &amp; executive agreements</t>
         </is>
       </c>
-      <c r="C168" s="99" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="C168" s="99" t="n">
+        <v>10</v>
       </c>
       <c r="D168" s="99" t="inlineStr">
         <is>
@@ -20823,10 +20795,8 @@
           <t>Appointments &amp; removal</t>
         </is>
       </c>
-      <c r="C169" s="99" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="C169" s="99" t="n">
+        <v>11</v>
       </c>
       <c r="D169" s="99" t="inlineStr">
         <is>
@@ -20881,10 +20851,8 @@
           <t>Separation of powers</t>
         </is>
       </c>
-      <c r="C170" s="99" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="C170" s="99" t="n">
+        <v>11</v>
       </c>
       <c r="D170" s="99" t="inlineStr">
         <is>
@@ -20940,10 +20908,8 @@
           <t>Commerce Clause</t>
         </is>
       </c>
-      <c r="C171" s="99" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="C171" s="99" t="n">
+        <v>11</v>
       </c>
       <c r="D171" s="99" t="inlineStr">
         <is>
@@ -20995,10 +20961,8 @@
         </is>
       </c>
       <c r="B172" s="99" t="n"/>
-      <c r="C172" s="99" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="C172" s="99" t="n">
+        <v>11</v>
       </c>
       <c r="D172" s="99" t="inlineStr">
         <is>
@@ -21049,10 +21013,8 @@
         </is>
       </c>
       <c r="B173" s="99" t="n"/>
-      <c r="C173" s="99" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="C173" s="99" t="n">
+        <v>11</v>
       </c>
       <c r="D173" s="99" t="inlineStr">
         <is>
@@ -21104,10 +21066,8 @@
         </is>
       </c>
       <c r="B174" s="99" t="n"/>
-      <c r="C174" s="99" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="C174" s="99" t="n">
+        <v>11</v>
       </c>
       <c r="D174" s="99" t="inlineStr">
         <is>
@@ -21157,10 +21117,8 @@
         </is>
       </c>
       <c r="B175" s="99" t="n"/>
-      <c r="C175" s="99" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="C175" s="99" t="n">
+        <v>11</v>
       </c>
       <c r="D175" s="99" t="inlineStr">
         <is>
@@ -21212,10 +21170,8 @@
         </is>
       </c>
       <c r="B176" s="99" t="n"/>
-      <c r="C176" s="99" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="C176" s="99" t="n">
+        <v>11</v>
       </c>
       <c r="D176" s="99" t="inlineStr">
         <is>
@@ -21265,10 +21221,8 @@
         </is>
       </c>
       <c r="B177" s="99" t="n"/>
-      <c r="C177" s="99" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="C177" s="99" t="n">
+        <v>11</v>
       </c>
       <c r="D177" s="99" t="inlineStr">
         <is>
@@ -21320,10 +21274,8 @@
         </is>
       </c>
       <c r="B178" s="99" t="n"/>
-      <c r="C178" s="99" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="C178" s="99" t="n">
+        <v>11</v>
       </c>
       <c r="D178" s="99" t="inlineStr">
         <is>
@@ -21768,10 +21720,8 @@
           <t>Executive power; Major questions &amp; nondelegation</t>
         </is>
       </c>
-      <c r="C186" s="99" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="C186" s="99" t="n">
+        <v>10</v>
       </c>
       <c r="D186" s="99" t="inlineStr">
         <is>
@@ -21827,10 +21777,8 @@
           <t>Executive power</t>
         </is>
       </c>
-      <c r="C187" s="99" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="C187" s="99" t="n">
+        <v>10</v>
       </c>
       <c r="D187" s="99" t="inlineStr">
         <is>
@@ -21885,10 +21833,8 @@
           <t>Executive power</t>
         </is>
       </c>
-      <c r="C188" s="99" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="C188" s="99" t="n">
+        <v>10</v>
       </c>
       <c r="D188" s="99" t="inlineStr">
         <is>
@@ -21944,10 +21890,8 @@
           <t>Executive power</t>
         </is>
       </c>
-      <c r="C189" s="99" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="C189" s="99" t="n">
+        <v>10</v>
       </c>
       <c r="D189" s="99" t="inlineStr">
         <is>
@@ -22003,10 +21947,8 @@
           <t>Executive power</t>
         </is>
       </c>
-      <c r="C190" s="99" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="C190" s="99" t="n">
+        <v>10</v>
       </c>
       <c r="D190" s="99" t="inlineStr">
         <is>
@@ -22062,10 +22004,8 @@
           <t>Separation of powers</t>
         </is>
       </c>
-      <c r="C191" s="99" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="C191" s="99" t="n">
+        <v>10</v>
       </c>
       <c r="D191" s="99" t="inlineStr">
         <is>
@@ -22121,10 +22061,8 @@
           <t>Treaties &amp; executive agreements; Major questions &amp; nondelegation</t>
         </is>
       </c>
-      <c r="C192" s="99" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="C192" s="99" t="n">
+        <v>10</v>
       </c>
       <c r="D192" s="99" t="inlineStr">
         <is>
@@ -22176,10 +22114,8 @@
         </is>
       </c>
       <c r="B193" s="99" t="n"/>
-      <c r="C193" s="99" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="C193" s="99" t="n">
+        <v>10</v>
       </c>
       <c r="D193" s="99" t="inlineStr">
         <is>
@@ -22234,10 +22170,8 @@
           <t>Separation of powers</t>
         </is>
       </c>
-      <c r="C194" s="99" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="C194" s="99" t="n">
+        <v>10</v>
       </c>
       <c r="D194" s="99" t="inlineStr">
         <is>
@@ -22293,10 +22227,8 @@
           <t>Separation of powers</t>
         </is>
       </c>
-      <c r="C195" s="99" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="C195" s="99" t="n">
+        <v>10</v>
       </c>
       <c r="D195" s="99" t="inlineStr">
         <is>
@@ -22348,10 +22280,8 @@
         </is>
       </c>
       <c r="B196" s="99" t="n"/>
-      <c r="C196" s="99" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="C196" s="99" t="n">
+        <v>10</v>
       </c>
       <c r="D196" s="99" t="inlineStr">
         <is>
@@ -22406,10 +22336,8 @@
           <t>Treaties &amp; executive agreements</t>
         </is>
       </c>
-      <c r="C197" s="99" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="C197" s="99" t="n">
+        <v>10</v>
       </c>
       <c r="D197" s="99" t="inlineStr">
         <is>
@@ -22464,10 +22392,8 @@
           <t>Treaties &amp; executive agreements</t>
         </is>
       </c>
-      <c r="C198" s="99" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="C198" s="99" t="n">
+        <v>10</v>
       </c>
       <c r="D198" s="99" t="inlineStr">
         <is>
@@ -22523,10 +22449,8 @@
           <t>Treaties &amp; executive agreements</t>
         </is>
       </c>
-      <c r="C199" s="99" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="C199" s="99" t="n">
+        <v>10</v>
       </c>
       <c r="D199" s="99" t="inlineStr">
         <is>
@@ -22582,10 +22506,8 @@
           <t>Treaties &amp; executive agreements</t>
         </is>
       </c>
-      <c r="C200" s="99" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="C200" s="99" t="n">
+        <v>10</v>
       </c>
       <c r="D200" s="99" t="inlineStr">
         <is>
@@ -22641,10 +22563,8 @@
           <t>Foundations &amp; interpretation</t>
         </is>
       </c>
-      <c r="C201" s="99" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="C201" s="99" t="n">
+        <v>10</v>
       </c>
       <c r="D201" s="99" t="inlineStr">
         <is>
@@ -22699,10 +22619,8 @@
           <t>Foundations &amp; interpretation</t>
         </is>
       </c>
-      <c r="C202" s="99" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="C202" s="99" t="n">
+        <v>11</v>
       </c>
       <c r="D202" s="99" t="inlineStr">
         <is>
@@ -22754,10 +22672,8 @@
         </is>
       </c>
       <c r="B203" s="99" t="n"/>
-      <c r="C203" s="99" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="C203" s="99" t="n">
+        <v>11</v>
       </c>
       <c r="D203" s="99" t="inlineStr">
         <is>
@@ -22808,10 +22724,8 @@
         </is>
       </c>
       <c r="B204" s="99" t="n"/>
-      <c r="C204" s="99" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="C204" s="99" t="n">
+        <v>11</v>
       </c>
       <c r="D204" s="99" t="inlineStr">
         <is>
@@ -22862,10 +22776,8 @@
         </is>
       </c>
       <c r="B205" s="99" t="n"/>
-      <c r="C205" s="99" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="C205" s="99" t="n">
+        <v>11</v>
       </c>
       <c r="D205" s="99" t="inlineStr">
         <is>
@@ -22918,10 +22830,8 @@
         </is>
       </c>
       <c r="B206" s="99" t="n"/>
-      <c r="C206" s="99" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="C206" s="99" t="n">
+        <v>11</v>
       </c>
       <c r="D206" s="99" t="inlineStr">
         <is>
@@ -22974,10 +22884,8 @@
         </is>
       </c>
       <c r="B207" s="99" t="n"/>
-      <c r="C207" s="99" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="C207" s="99" t="n">
+        <v>11</v>
       </c>
       <c r="D207" s="99" t="inlineStr">
         <is>
@@ -23033,10 +22941,8 @@
           <t>Separation of powers</t>
         </is>
       </c>
-      <c r="C208" s="99" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="C208" s="99" t="n">
+        <v>11</v>
       </c>
       <c r="D208" s="99" t="inlineStr">
         <is>
@@ -23093,10 +22999,8 @@
           <t>Major questions &amp; nondelegation</t>
         </is>
       </c>
-      <c r="C209" s="99" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="C209" s="99" t="n">
+        <v>11</v>
       </c>
       <c r="D209" s="99" t="inlineStr">
         <is>
@@ -23147,10 +23051,8 @@
         </is>
       </c>
       <c r="B210" s="99" t="n"/>
-      <c r="C210" s="99" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="C210" s="99" t="n">
+        <v>11</v>
       </c>
       <c r="D210" s="99" t="inlineStr">
         <is>
@@ -23202,10 +23104,8 @@
         </is>
       </c>
       <c r="B211" s="99" t="n"/>
-      <c r="C211" s="99" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="C211" s="99" t="n">
+        <v>11</v>
       </c>
       <c r="D211" s="99" t="inlineStr">
         <is>
@@ -23257,10 +23157,8 @@
         </is>
       </c>
       <c r="B212" s="99" t="n"/>
-      <c r="C212" s="99" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="C212" s="99" t="n">
+        <v>11</v>
       </c>
       <c r="D212" s="99" t="inlineStr">
         <is>
@@ -23314,10 +23212,8 @@
           <t>Judicial review &amp; federal jurisdiction</t>
         </is>
       </c>
-      <c r="C213" s="99" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="C213" s="99" t="n">
+        <v>11</v>
       </c>
       <c r="D213" s="99" t="inlineStr">
         <is>
@@ -23370,10 +23266,8 @@
         </is>
       </c>
       <c r="B214" s="99" t="n"/>
-      <c r="C214" s="99" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="C214" s="99" t="n">
+        <v>11</v>
       </c>
       <c r="D214" s="99" t="inlineStr">
         <is>
@@ -23423,10 +23317,8 @@
         </is>
       </c>
       <c r="B215" s="99" t="n"/>
-      <c r="C215" s="99" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="C215" s="99" t="n">
+        <v>11</v>
       </c>
       <c r="D215" s="99" t="inlineStr">
         <is>

--- a/Con_Law_Outline_Consolidated.xlsx
+++ b/Con_Law_Outline_Consolidated.xlsx
@@ -9508,7 +9508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -9530,13 +9530,283 @@
     <row r="2">
       <c r="A2" s="112" t="inlineStr">
         <is>
-          <t>No class notes on file yet</t>
+          <t>Commerce Clause after 1937: Lopez, Morrison, Raich</t>
         </is>
       </c>
       <c r="B2" s="111" t="inlineStr">
         <is>
-          <t>• Your outline has no class notes labeled Week 8.
-• Send them and they will be added here.</t>
+          <t>• After 1937 there seemed to be no real limit on the commerce power, other than other parts of the Constitution (like the First Amendment).
+• Lopez (1995): Congress went too far for the first time; people disagreed about whether it was a return to pre-1937 limits, a modest change, or meaningless.
+• Morrison followed and supported the idea of a sea change.
+• Gonzales v. Raich upheld regulating home-grown marijuana, like Wickard (never overruled): in the aggregate it substantially affects interstate commerce.
+• Difference: the Lopez law wasn't part of a larger economic regulation; Raich's was part of a comprehensive scheme.
+• After Raich, Lopez and Morrison look like a narrow change; the Gun-Free School Zones Act was easily amended, and lower courts accepted the fix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="112" t="inlineStr">
+        <is>
+          <t>NFIB v. Sebelius: how to read the opinion</t>
+        </is>
+      </c>
+      <c r="B3" s="111" t="inlineStr">
+        <is>
+          <t>• Multiple holdings; not a typical opinion, so you can't just count votes.
+• Five Justices (Roberts plus the four dissenters) agreed the Commerce Clause doesn't support the individual mandate, but the dissenters didn't join Roberts's opinion, so that point may be dicta.
+• Five Justices upheld the mandate under the taxing power.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="112" t="inlineStr">
+        <is>
+          <t>NFIB: the activity/inactivity line</t>
+        </is>
+      </c>
+      <c r="B4" s="111" t="inlineStr">
+        <is>
+          <t>• Roberts: Congress can regulate people already in a market, but can't force people into commerce they're not engaged in.
+• The target: young, healthy people who weren't buying insurance.
+• Ginsburg: everyone participates in health care eventually, so this market is different.
+• Roberts: everyone will buy food, clothing and shelter too, but that doesn't let Congress order purchases; the Commerce Clause isn't a license to regulate a person 'from cradle to grave.' Police power over individuals stays with the States.
+• The federal government has only enumerated powers; if Congress can make you buy this, maybe there's no line (though cases like Hodel suggest the limits were reached long ago).
+• The line is hard to draw, but the Court is trying to draw a practical one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="112" t="inlineStr">
+        <is>
+          <t>NFIB: the mandate as a tax (Drexel Furniture)</t>
+        </is>
+      </c>
+      <c r="B5" s="111" t="inlineStr">
+        <is>
+          <t>• Labels don't matter; the taxing power is very broad but not unlimited.
+• Drexel Furniture (child labor 'tax') was really a penalty: (1) a crushing burden (10% of net income) for any violation, (2) only on those who knowingly hired children (scienter), (3) enforced partly by the Labor Department.
+• Background: before 1937 (Hammer), Congress couldn't regulate child labor because manufacturing came before commerce, so it tried the taxing power to punish what it couldn't reach directly.
+• The shared responsibility payment is different: usually less than insurance (can never be more), no scienter requirement, and collected only by the IRS through normal tax means (no criminal prosecution).
+• So it's a tax, not a punishment; five votes uphold the mandate this way.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="112" t="inlineStr">
+        <is>
+          <t>NFIB: Medicaid expansion and Dole</t>
+        </is>
+      </c>
+      <c r="B6" s="111" t="inlineStr">
+        <is>
+          <t>• States had to change their Medicaid programs or lose ALL their existing Medicaid funds.
+• South Dakota v. Dole: raise the drinking age to 21 or lose 5% of highway funds; upheld. General welfare, clear terms, no other constitutional bar; the dissent said the link to highway funds was too attenuated, the majority found a plausible connection.
+• Incentives can go too far and become coercive: Roberts called the Medicaid threat 'a gun to the head.'
+• In Dole States could say no; as a practical matter, they couldn't refuse Medicaid funds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="112" t="inlineStr">
+        <is>
+          <t>The spectrum of views on federal power</t>
+        </is>
+      </c>
+      <c r="B7" s="111" t="inlineStr">
+        <is>
+          <t>• Broadest: Ginsburg (dissented in Lopez and Morrison, in the Raich majority).
+• Narrowest: Thomas (Lopez concurrence; narrowest view of the Commerce Clause of any Justice).
+• Underlying question: are there any real limits?</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="112" t="inlineStr">
+        <is>
+          <t>U.S. v. Phomma: the jurisdictional hook</t>
+        </is>
+      </c>
+      <c r="B8" s="111" t="inlineStr">
+        <is>
+          <t>• Not binding precedent. Civil disorder statute (18 U.S.C. §231): obstructing law enforcement or firefighters during a civil disorder; seems very broad (even 'delays').
+• Focus on Lopez category 3 (substantially affects commerce): can Congress criminalize obstructing or delaying a delivery vehicle? Yes, because of the jurisdictional hook (from Lopez), citing Dorsey.
+• Dorsey (9th Cir.): once Clinton's amendment added a commerce hook to the Gun-Free School Zones Act, prosecutions continued.
+• The hook must be substantive, not added just to ward off Commerce Clause challenges.
+• After Dorsey, Lopez looks like 'a big nothing' that is easy to get around.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="112" t="inlineStr">
+        <is>
+          <t>U.S. v. Protho (7th Cir. 2022): instrumentalities</t>
+        </is>
+      </c>
+      <c r="B9" s="111" t="inlineStr">
+        <is>
+          <t>• Protho argued the prosecution offered no evidence linking his act to interstate commerce.
+• Lopez category 1/2: protecting instrumentalities of interstate commerce. Federal Kidnapping Act; a car was used in the crime.
+• The court treated automobiles as a class as instrumentalities (many circuits agree; Morgan, 10th Cir.: cell phones, internet and GPS too).
+• Worry: if these courts are right, Congress could reach almost any crime, even without a gun that once crossed state lines. 'Motor vehicles' is broader than 'automobiles.'</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="112" t="inlineStr">
+        <is>
+          <t>U.S. v. Chavarria (10th Cir. 2025): the other side</t>
+        </is>
+      </c>
+      <c r="B10" s="111" t="inlineStr">
+        <is>
+          <t>• Kidnapping and murder in New Mexico; the problem was the indictment.
+• Some circuits treat motor vehicles as a class as instrumentalities (cars, even scooters); others don't. The Supreme Court has never defined 'instrumentalities of commerce.'
+• Tenth Circuit: instrumentalities are the means of interstate commerce (ships, railroads); motor vehicles are NOT always presumed to be instrumentalities.
+• Footnote: Congress might reach kidnapping under category 3 (aggregation, Wickard), but the statute didn't rely on that and the government didn't argue it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="112" t="inlineStr">
+        <is>
+          <t>Takeaway on Commerce Clause limits; Bonner</t>
+        </is>
+      </c>
+      <c r="B11" s="111" t="inlineStr">
+        <is>
+          <t>• Once the government jumps through jurisdictional hoops, there's little it can't regulate; a phone, the internet or a car can serve as the hook.
+• The Commerce Clause remains extraordinarily broad.
+• Bonner (Willett concurrence) worries lower courts have read the commerce power too broadly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="112" t="inlineStr">
+        <is>
+          <t>Brutus vs. Madison (Federalist 44) on Necessary and Proper</t>
+        </is>
+      </c>
+      <c r="B12" s="111" t="inlineStr">
+        <is>
+          <t>• Anti-Federalist fear (Brutus): Article I, §8 powers, especially Necessary and Proper, would be read so broadly they'd swallow the States.
+• Madison (Fed. 44): no part is more 'invulnerable.' The Convention's other options: (1) copy the Articles' 'expressly delegated' limit, (2) list every implied power, (3) list the excluded powers, or (4) say nothing and leave it to inference.
+• Copying the Articles meant a weak central government, which wasn't popular. No perfect solution to how explicit the grants must be.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="112" t="inlineStr">
+        <is>
+          <t>Tenth Amendment: 'expressly' left out</t>
+        </is>
+      </c>
+      <c r="B13" s="111" t="inlineStr">
+        <is>
+          <t>• Articles of Confederation, Art. II: States keep every power not 'expressly delegated.' The Tenth Amendment drops 'expressly.'
+• Not an oversight: proposals to add 'expressly' were voted down twice.
+• Madison: impossible to confine a government to express powers; implied powers are necessary unless the Constitution listed every detail.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="112" t="inlineStr">
+        <is>
+          <t>The bank debate (1791): Madison vs. Ames</t>
+        </is>
+      </c>
+      <c r="B14" s="111" t="inlineStr">
+        <is>
+          <t>• Madison (then in Congress) argued Congress lacked power to charter a bank: no clause (taxing/general welfare, borrowing, or Necessary and Proper) supports it. Article I, §8 lists subsidiary powers (e.g., raising armies alongside declaring war), which counsels against stretching implied powers. A bank might just be 'convenient.'
+• Fisher Ames (Federalist, Massachusetts): being at the Convention doesn't make Madison right; it's too late to deny powers 'plainly implied.' Congress may do what's necessary to the Constitution's ends unless it violates rights, express reservations, or States' powers (similar to Marshall later).
+• Privately, Ames said the constitutional argument was 'a dull piece of business'; the real fight was where the capital would be. Philadelphia (with the bank) vs. moving the capital south, favored by the Virginians (Washington, Jefferson, Madison).
+• 1816: President Madison signed the Second Bank bill to deal with economic and currency problems after the first bank expired.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="112" t="inlineStr">
+        <is>
+          <t>McCulloch v. Maryland (1819): who created the Union</t>
+        </is>
+      </c>
+      <c r="B15" s="111" t="inlineStr">
+        <is>
+          <t>• Second Bank; Maryland taxed it. Two questions: can Congress charter a bank, and can Maryland tax it?
+• Historical practice matters to Marshall: this was the second bank; Washington, persuaded by Hamilton, signed the first.
+• Maryland argued the States created the federal government, so federal power should be read narrowly and in subordination to the States.
+• Marshall rejected that: the people created the federal government, so its powers needn't be construed strictly. It's a government of enumerated powers, but how far those powers reach will always be debated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="112" t="inlineStr">
+        <is>
+          <t>McCulloch: 'necessary' and the test</t>
+        </is>
+      </c>
+      <c r="B16" s="111" t="inlineStr">
+        <is>
+          <t>• The power to charter a bank comes from Article I, §8 through the Necessary and Proper Clause.
+• 'Necessary' doesn't mean absolutely necessary; it means convenient, useful (para. 27). Textual point: if the ratifiers wanted a strict limit, they could have worded it differently.
+• The test (para. 38): 'Let the end be legitimate, let it be within the scope of the constitution, and all means which are appropriate, which are plainly adapted to that end, which are not prohibited, but consist with the letter and spirit of the constitution, are constitutional.' Much like Ames.
+• The Tenth Amendment's missing 'expressly' means it doesn't block this. The bank is constitutional.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="112" t="inlineStr">
+        <is>
+          <t>McCulloch: Maryland can't tax the bank; big picture</t>
+        </is>
+      </c>
+      <c r="B17" s="111" t="inlineStr">
+        <is>
+          <t>• 'The power to tax involves the power to destroy'; one government can't control the constitutional measures of the supreme one. Relying on 'confidence' that a State won't abuse the tax isn't enough.
+• Big takeaway: read federal power broadly. Hamiltonian view; broad Necessary and Proper Clause. Congress may do what's convenient to carry out its powers as long as it doesn't violate the Constitution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="112" t="inlineStr">
+        <is>
+          <t>Dormant Commerce Clause: origins and two tiers</t>
+        </is>
+      </c>
+      <c r="B18" s="111" t="inlineStr">
+        <is>
+          <t>• Hamilton (Fed. 11) wanted free trade within the U.S. and to avoid trade wars between States; Madison said giving Congress commerce power was uncontroversial.
+• Dormant Commerce Clause: even when Congress is silent, States can violate the Commerce Clause. Unusual for an Article I, §8 power.
+• Brown-Forman (1986): two tiers. (1) Laws that directly regulate or discriminate against interstate commerce, or favor in-state interests, are generally struck down. (2) Evenhanded laws with indirect effects get Pike balancing. No clear line between the two; the key is the overall effect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="112" t="inlineStr">
+        <is>
+          <t>Dean Milk and Pike</t>
+        </is>
+      </c>
+      <c r="B19" s="111" t="inlineStr">
+        <is>
+          <t>• Dean Milk (Madison, WI): milk had to be pasteurized within 5 miles and come from within 25 miles; an Illinois processor sued. Congress was silent, so it's a dormant Commerce Clause case. (If Congress authorizes discrimination, States and cities may do it.)
+• Calling it a health measure doesn't save it; it doesn't matter that other Wisconsin milk was also excluded. It plainly discriminates, which isn't allowed if reasonable nondiscriminatory alternatives exist.
+• Pike v. Bruce Church (1970): Arizona required cantaloupes to be packed in Arizona (to stamp 'Arizona' on them) when the grower already had a California packing plant. Evenhanded laws with incidental effects are upheld unless the burden is clearly excessive compared with local benefits (a cost-benefit test).
+• Outright discrimination: strict test. Evenhanded: weigh costs and benefits.
+• National Pork Producers v. Ross (2023): read with the handout on the course site.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="112" t="inlineStr">
+        <is>
+          <t>Two exceptions: Congress approves; market participant (Reeves)</t>
+        </is>
+      </c>
+      <c r="B20" s="111" t="inlineStr">
+        <is>
+          <t>• Exception 1: discrimination is allowed if Congress says so.
+• Exception 2 (Reeves v. Stake): South Dakota's state cement plant supplied in-state customers first during a shortage; allowed because the State acted as a market participant, not a regulator. In-state tuition is analogous.
+• Hoarding a limited natural resource could come out differently.</t>
         </is>
       </c>
     </row>
